--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.99</v>
+        <v>3.88</v>
       </c>
       <c r="F14" t="n">
-        <v>11.29</v>
+        <v>11.64</v>
       </c>
       <c r="G14" t="n">
-        <v>236</v>
+        <v>228.5</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>92.91</v>
+        <v>-238.2</v>
       </c>
       <c r="K14" t="n">
-        <v>-76.42</v>
+        <v>159.01</v>
       </c>
       <c r="L14" t="n">
-        <v>120.29</v>
+        <v>286.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:58:52</t>
+          <t>06:59:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.41</v>
+        <v>4.63</v>
       </c>
       <c r="F15" t="n">
-        <v>12.05</v>
+        <v>11.59</v>
       </c>
       <c r="G15" t="n">
-        <v>229.8</v>
+        <v>236</v>
       </c>
       <c r="H15" t="n">
-        <v>95.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>207.17</v>
+        <v>-85.5</v>
       </c>
       <c r="K15" t="n">
-        <v>143.75</v>
+        <v>34.16</v>
       </c>
       <c r="L15" t="n">
-        <v>252.16</v>
+        <v>92.06999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:00:53</t>
+          <t>07:00:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.82</v>
+        <v>4.14</v>
       </c>
       <c r="F16" t="n">
-        <v>11.57</v>
+        <v>12.14</v>
       </c>
       <c r="G16" t="n">
-        <v>212.2</v>
+        <v>231.1</v>
       </c>
       <c r="H16" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>214.3</v>
+        <v>275.92</v>
       </c>
       <c r="K16" t="n">
-        <v>7.06</v>
+        <v>-102.2</v>
       </c>
       <c r="L16" t="n">
-        <v>214.42</v>
+        <v>294.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:05:28</t>
+          <t>07:06:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.45</v>
+        <v>3.98</v>
       </c>
       <c r="F17" t="n">
-        <v>12.01</v>
+        <v>11.82</v>
       </c>
       <c r="G17" t="n">
-        <v>227.4</v>
+        <v>236.2</v>
       </c>
       <c r="H17" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-134.94</v>
+        <v>-96.83</v>
       </c>
       <c r="K17" t="n">
-        <v>-54.12</v>
+        <v>-251.18</v>
       </c>
       <c r="L17" t="n">
-        <v>145.39</v>
+        <v>269.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:07:05</t>
+          <t>07:08:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.85</v>
+        <v>4.09</v>
       </c>
       <c r="F18" t="n">
-        <v>11.43</v>
+        <v>11.42</v>
       </c>
       <c r="G18" t="n">
-        <v>236.4</v>
+        <v>231.3</v>
       </c>
       <c r="H18" t="n">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>113.5</v>
+        <v>-251.73</v>
       </c>
       <c r="K18" t="n">
-        <v>-52.01</v>
+        <v>-117.99</v>
       </c>
       <c r="L18" t="n">
-        <v>124.85</v>
+        <v>278.01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:09:41</t>
+          <t>07:09:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,28 +835,28 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.49</v>
+        <v>3.64</v>
       </c>
       <c r="F19" t="n">
-        <v>11.72</v>
+        <v>13.43</v>
       </c>
       <c r="G19" t="n">
-        <v>238.7</v>
+        <v>222.8</v>
       </c>
       <c r="H19" t="n">
-        <v>93.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>353.01</v>
+        <v>403.87</v>
       </c>
       <c r="K19" t="n">
-        <v>160.17</v>
+        <v>146.36</v>
       </c>
       <c r="L19" t="n">
-        <v>387.65</v>
+        <v>429.57</v>
       </c>
     </row>
     <row r="20">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.57</v>
+        <v>3.84</v>
       </c>
       <c r="F20" t="n">
-        <v>11.58</v>
+        <v>11.51</v>
       </c>
       <c r="G20" t="n">
-        <v>226</v>
+        <v>236.6</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-188.34</v>
+        <v>23.62</v>
       </c>
       <c r="K20" t="n">
-        <v>-15.76</v>
+        <v>-238.62</v>
       </c>
       <c r="L20" t="n">
-        <v>189</v>
+        <v>239.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:15:54</t>
+          <t>07:15:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.93</v>
+        <v>4.05</v>
       </c>
       <c r="F21" t="n">
-        <v>11.71</v>
+        <v>12.24</v>
       </c>
       <c r="G21" t="n">
-        <v>230.9</v>
+        <v>237.9</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>337.63</v>
+        <v>212.97</v>
       </c>
       <c r="K21" t="n">
-        <v>211.31</v>
+        <v>280.39</v>
       </c>
       <c r="L21" t="n">
-        <v>398.31</v>
+        <v>352.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:18:20</t>
+          <t>07:17:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="F22" t="n">
-        <v>11.83</v>
+        <v>11.72</v>
       </c>
       <c r="G22" t="n">
-        <v>235.1</v>
+        <v>240.9</v>
       </c>
       <c r="H22" t="n">
-        <v>94.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>640.8200000000001</v>
+        <v>-188.43</v>
       </c>
       <c r="K22" t="n">
-        <v>47.58</v>
+        <v>-170.01</v>
       </c>
       <c r="L22" t="n">
-        <v>642.58</v>
+        <v>253.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:22:15</t>
+          <t>07:21:39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.41</v>
+        <v>3.65</v>
       </c>
       <c r="F23" t="n">
-        <v>11.62</v>
+        <v>11.37</v>
       </c>
       <c r="G23" t="n">
-        <v>233.1</v>
+        <v>238.3</v>
       </c>
       <c r="H23" t="n">
-        <v>95.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-475.17</v>
+        <v>-30.03</v>
       </c>
       <c r="K23" t="n">
-        <v>-106.44</v>
+        <v>469.16</v>
       </c>
       <c r="L23" t="n">
-        <v>486.95</v>
+        <v>470.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:24:21</t>
+          <t>07:23:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.78</v>
+        <v>3.67</v>
       </c>
       <c r="F24" t="n">
-        <v>11.5</v>
+        <v>11.54</v>
       </c>
       <c r="G24" t="n">
-        <v>229.7</v>
+        <v>226.9</v>
       </c>
       <c r="H24" t="n">
-        <v>92.7</v>
+        <v>93.3</v>
       </c>
       <c r="I24" t="n">
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-25.13</v>
+        <v>283.49</v>
       </c>
       <c r="K24" t="n">
-        <v>176.14</v>
+        <v>-133.16</v>
       </c>
       <c r="L24" t="n">
-        <v>177.92</v>
+        <v>313.21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:26:12</t>
+          <t>07:26:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.36</v>
+        <v>4.64</v>
       </c>
       <c r="F25" t="n">
-        <v>11.28</v>
+        <v>11.77</v>
       </c>
       <c r="G25" t="n">
-        <v>235.4</v>
+        <v>242</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-76.90000000000001</v>
+        <v>104.15</v>
       </c>
       <c r="K25" t="n">
-        <v>-1100.36</v>
+        <v>305.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1103.05</v>
+        <v>322.48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:30:31</t>
+          <t>07:29:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.17</v>
+        <v>3.27</v>
       </c>
       <c r="F26" t="n">
-        <v>11.59</v>
+        <v>11.18</v>
       </c>
       <c r="G26" t="n">
-        <v>221.9</v>
+        <v>230.4</v>
       </c>
       <c r="H26" t="n">
-        <v>96.8</v>
+        <v>91.8</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-142.51</v>
+        <v>-138.54</v>
       </c>
       <c r="K26" t="n">
-        <v>125.19</v>
+        <v>219.76</v>
       </c>
       <c r="L26" t="n">
-        <v>189.69</v>
+        <v>259.78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:32:44</t>
+          <t>07:30:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.48</v>
+        <v>3.78</v>
       </c>
       <c r="F27" t="n">
-        <v>12.22</v>
+        <v>12.03</v>
       </c>
       <c r="G27" t="n">
-        <v>231.6</v>
+        <v>237.8</v>
       </c>
       <c r="H27" t="n">
-        <v>94.8</v>
+        <v>98.3</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>155.84</v>
+        <v>-684.5</v>
       </c>
       <c r="K27" t="n">
-        <v>-84.56999999999999</v>
+        <v>334.15</v>
       </c>
       <c r="L27" t="n">
-        <v>177.31</v>
+        <v>761.71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:32:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.4</v>
+        <v>3.83</v>
       </c>
       <c r="F28" t="n">
-        <v>11.55</v>
+        <v>11.59</v>
       </c>
       <c r="G28" t="n">
-        <v>222.7</v>
+        <v>234.6</v>
       </c>
       <c r="H28" t="n">
-        <v>94.5</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>135.16</v>
+        <v>214.46</v>
       </c>
       <c r="K28" t="n">
-        <v>-406.29</v>
+        <v>-405.85</v>
       </c>
       <c r="L28" t="n">
-        <v>428.18</v>
+        <v>459.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:44:58</t>
+          <t>07:46:13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="F29" t="n">
-        <v>11.5</v>
+        <v>11.53</v>
       </c>
       <c r="G29" t="n">
-        <v>232.5</v>
+        <v>233.2</v>
       </c>
       <c r="H29" t="n">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-165.74</v>
+        <v>47.86</v>
       </c>
       <c r="K29" t="n">
-        <v>27.03</v>
+        <v>53.07</v>
       </c>
       <c r="L29" t="n">
-        <v>167.93</v>
+        <v>71.45999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:47:06</t>
+          <t>07:48:41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.64</v>
+        <v>4.42</v>
       </c>
       <c r="F30" t="n">
-        <v>12.36</v>
+        <v>11.94</v>
       </c>
       <c r="G30" t="n">
-        <v>226.9</v>
+        <v>229.2</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-207.8</v>
+        <v>142.99</v>
       </c>
       <c r="K30" t="n">
-        <v>179.3</v>
+        <v>-149.76</v>
       </c>
       <c r="L30" t="n">
-        <v>274.47</v>
+        <v>207.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:49:20</t>
+          <t>07:49:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.56</v>
+        <v>4.41</v>
       </c>
       <c r="F31" t="n">
-        <v>12.02</v>
+        <v>11.26</v>
       </c>
       <c r="G31" t="n">
-        <v>235.7</v>
+        <v>221.4</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>111.26</v>
+        <v>21</v>
       </c>
       <c r="K31" t="n">
-        <v>-12.81</v>
+        <v>-62.17</v>
       </c>
       <c r="L31" t="n">
-        <v>111.99</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:54:00</t>
+          <t>07:54:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.31</v>
+        <v>3.9</v>
       </c>
       <c r="F32" t="n">
-        <v>12.07</v>
+        <v>11.95</v>
       </c>
       <c r="G32" t="n">
-        <v>229.8</v>
+        <v>226.1</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>241.49</v>
+        <v>-66.48</v>
       </c>
       <c r="K32" t="n">
-        <v>-250.38</v>
+        <v>171.91</v>
       </c>
       <c r="L32" t="n">
-        <v>347.86</v>
+        <v>184.32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:55:58</t>
+          <t>07:55:56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.32</v>
+        <v>4.45</v>
       </c>
       <c r="F33" t="n">
-        <v>11.47</v>
+        <v>12.38</v>
       </c>
       <c r="G33" t="n">
-        <v>241</v>
+        <v>222.3</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-158.3</v>
+        <v>-157.21</v>
       </c>
       <c r="K33" t="n">
-        <v>-163.64</v>
+        <v>-7.67</v>
       </c>
       <c r="L33" t="n">
-        <v>227.68</v>
+        <v>157.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:58:33</t>
+          <t>07:57:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.53</v>
+        <v>4.61</v>
       </c>
       <c r="F34" t="n">
-        <v>11.48</v>
+        <v>11.67</v>
       </c>
       <c r="G34" t="n">
-        <v>233.7</v>
+        <v>243.4</v>
       </c>
       <c r="H34" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-114.14</v>
+        <v>16.36</v>
       </c>
       <c r="K34" t="n">
-        <v>-269.45</v>
+        <v>135.16</v>
       </c>
       <c r="L34" t="n">
-        <v>292.63</v>
+        <v>136.14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:04:06</t>
+          <t>08:02:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.01</v>
+        <v>3.85</v>
       </c>
       <c r="F35" t="n">
-        <v>11.77</v>
+        <v>11.51</v>
       </c>
       <c r="G35" t="n">
-        <v>226.7</v>
+        <v>255.2</v>
       </c>
       <c r="H35" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-85.23999999999999</v>
+        <v>-199.33</v>
       </c>
       <c r="K35" t="n">
-        <v>-61.31</v>
+        <v>-119.97</v>
       </c>
       <c r="L35" t="n">
-        <v>105</v>
+        <v>232.65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:06:11</t>
+          <t>08:04:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.02</v>
+        <v>3.73</v>
       </c>
       <c r="F36" t="n">
-        <v>12.25</v>
+        <v>11.84</v>
       </c>
       <c r="G36" t="n">
-        <v>219.2</v>
+        <v>236.6</v>
       </c>
       <c r="H36" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>721.41</v>
+        <v>-34.55</v>
       </c>
       <c r="K36" t="n">
-        <v>-368.77</v>
+        <v>-275.05</v>
       </c>
       <c r="L36" t="n">
-        <v>810.2</v>
+        <v>277.21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:07:36</t>
+          <t>08:05:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1594,31 +1594,31 @@
         <v>4.13</v>
       </c>
       <c r="F37" t="n">
-        <v>11.78</v>
+        <v>12.13</v>
       </c>
       <c r="G37" t="n">
-        <v>241.4</v>
+        <v>229.9</v>
       </c>
       <c r="H37" t="n">
-        <v>92.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-380.87</v>
+        <v>-386.35</v>
       </c>
       <c r="K37" t="n">
-        <v>-257.31</v>
+        <v>150.89</v>
       </c>
       <c r="L37" t="n">
-        <v>459.64</v>
+        <v>414.77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:13:01</t>
+          <t>08:09:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.81</v>
+        <v>4.36</v>
       </c>
       <c r="F38" t="n">
-        <v>12.18</v>
+        <v>11.97</v>
       </c>
       <c r="G38" t="n">
-        <v>226.2</v>
+        <v>234</v>
       </c>
       <c r="H38" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-345.77</v>
+        <v>242.23</v>
       </c>
       <c r="K38" t="n">
-        <v>124.8</v>
+        <v>-102.93</v>
       </c>
       <c r="L38" t="n">
-        <v>367.6</v>
+        <v>263.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:15:13</t>
+          <t>08:10:25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.34</v>
+        <v>3.92</v>
       </c>
       <c r="F39" t="n">
-        <v>12.47</v>
+        <v>11.14</v>
       </c>
       <c r="G39" t="n">
-        <v>235.9</v>
+        <v>237.1</v>
       </c>
       <c r="H39" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-12.06</v>
+        <v>-27.84</v>
       </c>
       <c r="K39" t="n">
-        <v>-368.57</v>
+        <v>364.76</v>
       </c>
       <c r="L39" t="n">
-        <v>368.76</v>
+        <v>365.82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:17:19</t>
+          <t>08:11:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.43</v>
+        <v>4.57</v>
       </c>
       <c r="F40" t="n">
-        <v>11.91</v>
+        <v>11.65</v>
       </c>
       <c r="G40" t="n">
-        <v>241.4</v>
+        <v>227.2</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>90.2</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>67.09999999999999</v>
+        <v>15.25</v>
       </c>
       <c r="K40" t="n">
-        <v>-237.91</v>
+        <v>483.55</v>
       </c>
       <c r="L40" t="n">
-        <v>247.19</v>
+        <v>483.79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:22:02</t>
+          <t>08:16:31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.74</v>
+        <v>4.48</v>
       </c>
       <c r="F41" t="n">
-        <v>11.41</v>
+        <v>12.12</v>
       </c>
       <c r="G41" t="n">
-        <v>222.2</v>
+        <v>232.9</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>94.8</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-154.8</v>
+        <v>-279.94</v>
       </c>
       <c r="K41" t="n">
-        <v>752.03</v>
+        <v>-82.73999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>767.8</v>
+        <v>291.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:23:06</t>
+          <t>08:17:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.43</v>
+        <v>4.82</v>
       </c>
       <c r="F42" t="n">
-        <v>12.54</v>
+        <v>11.68</v>
       </c>
       <c r="G42" t="n">
-        <v>237.1</v>
+        <v>238</v>
       </c>
       <c r="H42" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>367.01</v>
+        <v>128.09</v>
       </c>
       <c r="K42" t="n">
-        <v>688.6</v>
+        <v>-245.84</v>
       </c>
       <c r="L42" t="n">
-        <v>780.29</v>
+        <v>277.21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:24:43</t>
+          <t>08:19:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.01</v>
+        <v>3.96</v>
       </c>
       <c r="F43" t="n">
-        <v>12.43</v>
+        <v>12.11</v>
       </c>
       <c r="G43" t="n">
-        <v>241.6</v>
+        <v>235.4</v>
       </c>
       <c r="H43" t="n">
-        <v>92.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>240.94</v>
+        <v>-66.7</v>
       </c>
       <c r="K43" t="n">
-        <v>-456.95</v>
+        <v>209.72</v>
       </c>
       <c r="L43" t="n">
-        <v>516.58</v>
+        <v>220.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:34:37</t>
+          <t>08:30:37</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.87</v>
+        <v>3.93</v>
       </c>
       <c r="F44" t="n">
-        <v>11.76</v>
+        <v>11.57</v>
       </c>
       <c r="G44" t="n">
-        <v>232.1</v>
+        <v>247.6</v>
       </c>
       <c r="H44" t="n">
-        <v>97.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>109.11</v>
+        <v>-191.28</v>
       </c>
       <c r="K44" t="n">
-        <v>413.03</v>
+        <v>188.23</v>
       </c>
       <c r="L44" t="n">
-        <v>427.2</v>
+        <v>268.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:36:38</t>
+          <t>08:32:34</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="F45" t="n">
-        <v>11.46</v>
+        <v>11.74</v>
       </c>
       <c r="G45" t="n">
-        <v>251.8</v>
+        <v>237.3</v>
       </c>
       <c r="H45" t="n">
-        <v>93.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.98</v>
+        <v>174.41</v>
       </c>
       <c r="K45" t="n">
-        <v>-151.86</v>
+        <v>-93.48999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>152.07</v>
+        <v>197.89</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:38:39</t>
+          <t>08:35:08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.04</v>
+        <v>3.95</v>
       </c>
       <c r="F46" t="n">
-        <v>11.65</v>
+        <v>11.19</v>
       </c>
       <c r="G46" t="n">
-        <v>251.2</v>
+        <v>233.5</v>
       </c>
       <c r="H46" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>275.68</v>
+        <v>-123.29</v>
       </c>
       <c r="K46" t="n">
-        <v>-100.06</v>
+        <v>49.35</v>
       </c>
       <c r="L46" t="n">
-        <v>293.28</v>
+        <v>132.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:42:43</t>
+          <t>08:38:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="F47" t="n">
-        <v>11.83</v>
+        <v>11.78</v>
       </c>
       <c r="G47" t="n">
-        <v>231.9</v>
+        <v>233.1</v>
       </c>
       <c r="H47" t="n">
         <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-260.68</v>
+        <v>-296.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-608.5700000000001</v>
+        <v>37.36</v>
       </c>
       <c r="L47" t="n">
-        <v>662.05</v>
+        <v>298.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:44:12</t>
+          <t>08:40:23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.28</v>
+        <v>4.19</v>
       </c>
       <c r="F48" t="n">
-        <v>11.42</v>
+        <v>11.82</v>
       </c>
       <c r="G48" t="n">
-        <v>242</v>
+        <v>218.3</v>
       </c>
       <c r="H48" t="n">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>311.06</v>
+        <v>-36.51</v>
       </c>
       <c r="K48" t="n">
-        <v>-86.79000000000001</v>
+        <v>-247.78</v>
       </c>
       <c r="L48" t="n">
-        <v>322.94</v>
+        <v>250.46</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:45:44</t>
+          <t>08:41:49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.81</v>
+        <v>4.05</v>
       </c>
       <c r="F49" t="n">
-        <v>11.92</v>
+        <v>11.54</v>
       </c>
       <c r="G49" t="n">
-        <v>216.5</v>
+        <v>233.8</v>
       </c>
       <c r="H49" t="n">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-190.39</v>
+        <v>-85.67</v>
       </c>
       <c r="K49" t="n">
-        <v>373.25</v>
+        <v>221.02</v>
       </c>
       <c r="L49" t="n">
-        <v>419.01</v>
+        <v>237.04</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:50:30</t>
+          <t>08:46:23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="F50" t="n">
-        <v>11.32</v>
+        <v>11.37</v>
       </c>
       <c r="G50" t="n">
-        <v>227.6</v>
+        <v>234.5</v>
       </c>
       <c r="H50" t="n">
-        <v>98.2</v>
+        <v>94.8</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-118.79</v>
+        <v>-123.96</v>
       </c>
       <c r="K50" t="n">
-        <v>-96.38</v>
+        <v>-123.63</v>
       </c>
       <c r="L50" t="n">
-        <v>152.97</v>
+        <v>175.07</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:52:02</t>
+          <t>08:47:41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.67</v>
+        <v>4.31</v>
       </c>
       <c r="F51" t="n">
-        <v>11.97</v>
+        <v>11.32</v>
       </c>
       <c r="G51" t="n">
-        <v>213.3</v>
+        <v>237.4</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>264.45</v>
+        <v>-66.31999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>272.22</v>
+        <v>121.58</v>
       </c>
       <c r="L51" t="n">
-        <v>379.52</v>
+        <v>138.49</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:52:41</t>
+          <t>08:49:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.01</v>
+        <v>4.65</v>
       </c>
       <c r="F52" t="n">
-        <v>11.95</v>
+        <v>11.78</v>
       </c>
       <c r="G52" t="n">
-        <v>233.9</v>
+        <v>225.5</v>
       </c>
       <c r="H52" t="n">
-        <v>95.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-460.04</v>
+        <v>-19.88</v>
       </c>
       <c r="K52" t="n">
-        <v>231.29</v>
+        <v>-139.36</v>
       </c>
       <c r="L52" t="n">
-        <v>514.91</v>
+        <v>140.77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:57:14</t>
+          <t>08:55:28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="F53" t="n">
-        <v>12.33</v>
+        <v>11.88</v>
       </c>
       <c r="G53" t="n">
-        <v>223.2</v>
+        <v>229.4</v>
       </c>
       <c r="H53" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>-546.16</v>
+        <v>-51.06</v>
       </c>
       <c r="K53" t="n">
-        <v>105.92</v>
+        <v>111.98</v>
       </c>
       <c r="L53" t="n">
-        <v>556.33</v>
+        <v>123.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:58:45</t>
+          <t>08:57:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.12</v>
+        <v>5.07</v>
       </c>
       <c r="F54" t="n">
-        <v>10.8</v>
+        <v>12.16</v>
       </c>
       <c r="G54" t="n">
-        <v>235.6</v>
+        <v>230.5</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>49.07</v>
+        <v>183.81</v>
       </c>
       <c r="K54" t="n">
-        <v>128.48</v>
+        <v>-897.02</v>
       </c>
       <c r="L54" t="n">
-        <v>137.53</v>
+        <v>915.66</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:00:40</t>
+          <t>08:59:25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.77</v>
+        <v>3.64</v>
       </c>
       <c r="F55" t="n">
-        <v>11.97</v>
+        <v>11.63</v>
       </c>
       <c r="G55" t="n">
-        <v>231.6</v>
+        <v>223.9</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>340.47</v>
+        <v>-416.22</v>
       </c>
       <c r="K55" t="n">
-        <v>5.68</v>
+        <v>-226.14</v>
       </c>
       <c r="L55" t="n">
-        <v>340.52</v>
+        <v>473.69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:06:01</t>
+          <t>09:03:17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="F56" t="n">
-        <v>11.73</v>
+        <v>12.18</v>
       </c>
       <c r="G56" t="n">
-        <v>237.4</v>
+        <v>241.7</v>
       </c>
       <c r="H56" t="n">
-        <v>97.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>580.16</v>
+        <v>642.53</v>
       </c>
       <c r="K56" t="n">
-        <v>-87.88</v>
+        <v>472.79</v>
       </c>
       <c r="L56" t="n">
-        <v>586.78</v>
+        <v>797.73</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:07:54</t>
+          <t>09:04:41</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.23</v>
+        <v>4.48</v>
       </c>
       <c r="F57" t="n">
-        <v>11.64</v>
+        <v>12.44</v>
       </c>
       <c r="G57" t="n">
-        <v>231.4</v>
+        <v>231.6</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-440.41</v>
+        <v>-411.71</v>
       </c>
       <c r="K57" t="n">
-        <v>-679.55</v>
+        <v>152.74</v>
       </c>
       <c r="L57" t="n">
-        <v>809.78</v>
+        <v>439.13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:09:30</t>
+          <t>09:05:41</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.84</v>
+        <v>4.39</v>
       </c>
       <c r="F58" t="n">
-        <v>11.16</v>
+        <v>12.26</v>
       </c>
       <c r="G58" t="n">
-        <v>220.5</v>
+        <v>231.8</v>
       </c>
       <c r="H58" t="n">
-        <v>99.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>-705.5</v>
+        <v>-180.95</v>
       </c>
       <c r="K58" t="n">
-        <v>177.11</v>
+        <v>-293.03</v>
       </c>
       <c r="L58" t="n">
-        <v>727.39</v>
+        <v>344.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:19:49</t>
+          <t>09:16:08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.82</v>
+        <v>4.58</v>
       </c>
       <c r="F59" t="n">
-        <v>11.93</v>
+        <v>11.73</v>
       </c>
       <c r="G59" t="n">
-        <v>231.9</v>
+        <v>234.3</v>
       </c>
       <c r="H59" t="n">
-        <v>92.5</v>
+        <v>97.3</v>
       </c>
       <c r="I59" t="n">
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>31.83</v>
+        <v>235.87</v>
       </c>
       <c r="K59" t="n">
-        <v>-80.77</v>
+        <v>-201.63</v>
       </c>
       <c r="L59" t="n">
-        <v>86.81</v>
+        <v>310.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:22:21</t>
+          <t>09:18:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.3</v>
+        <v>4.58</v>
       </c>
       <c r="F60" t="n">
-        <v>11.49</v>
+        <v>11.29</v>
       </c>
       <c r="G60" t="n">
-        <v>238.3</v>
+        <v>234.5</v>
       </c>
       <c r="H60" t="n">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>97.98</v>
+        <v>-248.5</v>
       </c>
       <c r="K60" t="n">
-        <v>57.17</v>
+        <v>-109.15</v>
       </c>
       <c r="L60" t="n">
-        <v>113.44</v>
+        <v>271.42</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:24:08</t>
+          <t>09:19:02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.78</v>
+        <v>4.69</v>
       </c>
       <c r="F61" t="n">
-        <v>11.3</v>
+        <v>12.12</v>
       </c>
       <c r="G61" t="n">
-        <v>235.6</v>
+        <v>238.4</v>
       </c>
       <c r="H61" t="n">
-        <v>93.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-20.8</v>
+        <v>-103.41</v>
       </c>
       <c r="K61" t="n">
-        <v>-18.88</v>
+        <v>243.43</v>
       </c>
       <c r="L61" t="n">
-        <v>28.09</v>
+        <v>264.48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:28:28</t>
+          <t>09:23:29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.84</v>
+        <v>4.06</v>
       </c>
       <c r="F62" t="n">
-        <v>11.44</v>
+        <v>11.69</v>
       </c>
       <c r="G62" t="n">
-        <v>226.3</v>
+        <v>228.3</v>
       </c>
       <c r="H62" t="n">
-        <v>96.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>126.16</v>
+        <v>63.34</v>
       </c>
       <c r="K62" t="n">
-        <v>-192.31</v>
+        <v>194.44</v>
       </c>
       <c r="L62" t="n">
-        <v>230</v>
+        <v>204.49</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:29:06</t>
+          <t>09:25:19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="F63" t="n">
-        <v>12.2</v>
+        <v>11.73</v>
       </c>
       <c r="G63" t="n">
-        <v>237.5</v>
+        <v>245.2</v>
       </c>
       <c r="H63" t="n">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-151.68</v>
+        <v>-253.6</v>
       </c>
       <c r="K63" t="n">
-        <v>26.76</v>
+        <v>295.47</v>
       </c>
       <c r="L63" t="n">
-        <v>154.02</v>
+        <v>389.38</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:31:15</t>
+          <t>09:27:09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.5</v>
+        <v>4.99</v>
       </c>
       <c r="F64" t="n">
-        <v>12.09</v>
+        <v>11.6</v>
       </c>
       <c r="G64" t="n">
-        <v>231.2</v>
+        <v>224.9</v>
       </c>
       <c r="H64" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>93.33</v>
+        <v>-424.18</v>
       </c>
       <c r="K64" t="n">
-        <v>126.54</v>
+        <v>-18.49</v>
       </c>
       <c r="L64" t="n">
-        <v>157.24</v>
+        <v>424.58</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:36:51</t>
+          <t>09:31:11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.62</v>
+        <v>5.22</v>
       </c>
       <c r="F65" t="n">
-        <v>11.77</v>
+        <v>12.6</v>
       </c>
       <c r="G65" t="n">
-        <v>227.4</v>
+        <v>239.6</v>
       </c>
       <c r="H65" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>34.19</v>
+        <v>477.61</v>
       </c>
       <c r="K65" t="n">
-        <v>-29.6</v>
+        <v>-341.77</v>
       </c>
       <c r="L65" t="n">
-        <v>45.22</v>
+        <v>587.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:38:44</t>
+          <t>09:32:14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.93</v>
+        <v>4.79</v>
       </c>
       <c r="F66" t="n">
-        <v>11.94</v>
+        <v>11.29</v>
       </c>
       <c r="G66" t="n">
-        <v>225</v>
+        <v>205.9</v>
       </c>
       <c r="H66" t="n">
-        <v>96</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-412.09</v>
+        <v>136.21</v>
       </c>
       <c r="K66" t="n">
-        <v>189.04</v>
+        <v>-179.73</v>
       </c>
       <c r="L66" t="n">
-        <v>453.38</v>
+        <v>225.51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:40:08</t>
+          <t>09:33:46</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.97</v>
+        <v>4.51</v>
       </c>
       <c r="F67" t="n">
-        <v>11.62</v>
+        <v>12.13</v>
       </c>
       <c r="G67" t="n">
-        <v>239.3</v>
+        <v>228.7</v>
       </c>
       <c r="H67" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>172.8</v>
+        <v>-320.62</v>
       </c>
       <c r="K67" t="n">
-        <v>239.1</v>
+        <v>37.48</v>
       </c>
       <c r="L67" t="n">
-        <v>295.01</v>
+        <v>322.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:43:52</t>
+          <t>09:39:22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.67</v>
+        <v>3.99</v>
       </c>
       <c r="F68" t="n">
-        <v>11.27</v>
+        <v>11.67</v>
       </c>
       <c r="G68" t="n">
-        <v>228.5</v>
+        <v>249.9</v>
       </c>
       <c r="H68" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>347.8</v>
+        <v>-278.26</v>
       </c>
       <c r="K68" t="n">
-        <v>-280.63</v>
+        <v>-100.87</v>
       </c>
       <c r="L68" t="n">
-        <v>446.9</v>
+        <v>295.98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:45:43</t>
+          <t>09:40:51</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.01</v>
+        <v>5.17</v>
       </c>
       <c r="F69" t="n">
-        <v>11.36</v>
+        <v>11.6</v>
       </c>
       <c r="G69" t="n">
         <v>228</v>
       </c>
       <c r="H69" t="n">
-        <v>92.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>217.51</v>
+        <v>443.02</v>
       </c>
       <c r="K69" t="n">
-        <v>-241.67</v>
+        <v>39.02</v>
       </c>
       <c r="L69" t="n">
-        <v>325.14</v>
+        <v>444.73</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:47:41</t>
+          <t>09:43:16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="F70" t="n">
-        <v>12.12</v>
+        <v>11.69</v>
       </c>
       <c r="G70" t="n">
-        <v>251.8</v>
+        <v>240.9</v>
       </c>
       <c r="H70" t="n">
-        <v>98.8</v>
+        <v>99.7</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-74.92</v>
+        <v>68.88</v>
       </c>
       <c r="K70" t="n">
-        <v>-199.51</v>
+        <v>-92.03</v>
       </c>
       <c r="L70" t="n">
-        <v>213.11</v>
+        <v>114.95</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:50:55</t>
+          <t>09:48:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.33</v>
+        <v>4.91</v>
       </c>
       <c r="F71" t="n">
-        <v>11.77</v>
+        <v>11.71</v>
       </c>
       <c r="G71" t="n">
-        <v>232.2</v>
+        <v>234.1</v>
       </c>
       <c r="H71" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I71" t="n">
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-534.37</v>
+        <v>194.33</v>
       </c>
       <c r="K71" t="n">
-        <v>156.97</v>
+        <v>-163.79</v>
       </c>
       <c r="L71" t="n">
-        <v>556.95</v>
+        <v>254.15</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:51:46</t>
+          <t>09:49:44</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.53</v>
+        <v>4.57</v>
       </c>
       <c r="F72" t="n">
-        <v>12.16</v>
+        <v>11.74</v>
       </c>
       <c r="G72" t="n">
-        <v>229.5</v>
+        <v>234.2</v>
       </c>
       <c r="H72" t="n">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-257.64</v>
+        <v>-450.96</v>
       </c>
       <c r="K72" t="n">
-        <v>-368.63</v>
+        <v>73.48</v>
       </c>
       <c r="L72" t="n">
-        <v>449.74</v>
+        <v>456.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:54:01</t>
+          <t>09:51:33</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.77</v>
+        <v>4.65</v>
       </c>
       <c r="F73" t="n">
-        <v>11.62</v>
+        <v>11.9</v>
       </c>
       <c r="G73" t="n">
-        <v>243.4</v>
+        <v>244.7</v>
       </c>
       <c r="H73" t="n">
-        <v>96.3</v>
+        <v>94.8</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>557.96</v>
+        <v>-130.9</v>
       </c>
       <c r="K73" t="n">
-        <v>225.58</v>
+        <v>-346.37</v>
       </c>
       <c r="L73" t="n">
-        <v>601.83</v>
+        <v>370.28</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:06:58</t>
+          <t>10:01:29</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.11</v>
+        <v>4.44</v>
       </c>
       <c r="F74" t="n">
-        <v>12.03</v>
+        <v>11.86</v>
       </c>
       <c r="G74" t="n">
-        <v>242.2</v>
+        <v>237.8</v>
       </c>
       <c r="H74" t="n">
-        <v>99.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-380.48</v>
+        <v>56.23</v>
       </c>
       <c r="K74" t="n">
-        <v>67.73</v>
+        <v>-95.89</v>
       </c>
       <c r="L74" t="n">
-        <v>386.46</v>
+        <v>111.16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:09:26</t>
+          <t>10:03:16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.86</v>
+        <v>4.49</v>
       </c>
       <c r="F75" t="n">
-        <v>11.15</v>
+        <v>11.5</v>
       </c>
       <c r="G75" t="n">
-        <v>221.1</v>
+        <v>211.5</v>
       </c>
       <c r="H75" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>70.04000000000001</v>
+        <v>-189.72</v>
       </c>
       <c r="K75" t="n">
-        <v>295.23</v>
+        <v>-199.56</v>
       </c>
       <c r="L75" t="n">
-        <v>303.43</v>
+        <v>275.35</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:11:32</t>
+          <t>10:04:09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="F76" t="n">
-        <v>11.61</v>
+        <v>11.62</v>
       </c>
       <c r="G76" t="n">
-        <v>208.7</v>
+        <v>230.9</v>
       </c>
       <c r="H76" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="I76" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>49.93</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>232.01</v>
+        <v>70.41</v>
       </c>
       <c r="L76" t="n">
-        <v>237.32</v>
+        <v>107.25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:17:36</t>
+          <t>10:08:36</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.93</v>
+        <v>4.97</v>
       </c>
       <c r="F77" t="n">
-        <v>11.6</v>
+        <v>11.11</v>
       </c>
       <c r="G77" t="n">
-        <v>244.5</v>
+        <v>240.7</v>
       </c>
       <c r="H77" t="n">
-        <v>94.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>-10.83</v>
+        <v>43.1</v>
       </c>
       <c r="K77" t="n">
-        <v>-126.73</v>
+        <v>366.94</v>
       </c>
       <c r="L77" t="n">
-        <v>127.19</v>
+        <v>369.46</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:18:55</t>
+          <t>10:10:42</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.5</v>
+        <v>4.41</v>
       </c>
       <c r="F78" t="n">
-        <v>12.05</v>
+        <v>12.23</v>
       </c>
       <c r="G78" t="n">
-        <v>240.4</v>
+        <v>229.1</v>
       </c>
       <c r="H78" t="n">
         <v>100</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-185.83</v>
+        <v>-53.94</v>
       </c>
       <c r="K78" t="n">
-        <v>67.94</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>197.86</v>
+        <v>101.22</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:20:19</t>
+          <t>10:11:30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5</v>
+        <v>4.58</v>
       </c>
       <c r="F79" t="n">
-        <v>10.96</v>
+        <v>11.75</v>
       </c>
       <c r="G79" t="n">
-        <v>242.1</v>
+        <v>231.8</v>
       </c>
       <c r="H79" t="n">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-426.47</v>
+        <v>-105.13</v>
       </c>
       <c r="K79" t="n">
-        <v>7.2</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>426.53</v>
+        <v>143.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:25:08</t>
+          <t>10:16:06</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.33</v>
+        <v>4.74</v>
       </c>
       <c r="F80" t="n">
-        <v>11.64</v>
+        <v>11.75</v>
       </c>
       <c r="G80" t="n">
-        <v>235.8</v>
+        <v>236.4</v>
       </c>
       <c r="H80" t="n">
-        <v>97.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>-69.31999999999999</v>
+        <v>414.85</v>
       </c>
       <c r="K80" t="n">
-        <v>-190.69</v>
+        <v>-228.37</v>
       </c>
       <c r="L80" t="n">
-        <v>202.9</v>
+        <v>473.55</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:26:06</t>
+          <t>10:17:27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.75</v>
+        <v>4.47</v>
       </c>
       <c r="F81" t="n">
-        <v>12.11</v>
+        <v>12.01</v>
       </c>
       <c r="G81" t="n">
-        <v>240.1</v>
+        <v>245.9</v>
       </c>
       <c r="H81" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-5.61</v>
+        <v>-314.49</v>
       </c>
       <c r="K81" t="n">
-        <v>309.12</v>
+        <v>-48.45</v>
       </c>
       <c r="L81" t="n">
-        <v>309.17</v>
+        <v>318.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:27:04</t>
+          <t>10:19:27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.58</v>
+        <v>5.68</v>
       </c>
       <c r="F82" t="n">
-        <v>11.27</v>
+        <v>11.72</v>
       </c>
       <c r="G82" t="n">
-        <v>227.2</v>
+        <v>251.7</v>
       </c>
       <c r="H82" t="n">
-        <v>96.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>158.61</v>
+        <v>-349.63</v>
       </c>
       <c r="K82" t="n">
-        <v>29.75</v>
+        <v>-112.32</v>
       </c>
       <c r="L82" t="n">
-        <v>161.37</v>
+        <v>367.23</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:30:45</t>
+          <t>10:24:01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.71</v>
+        <v>5.41</v>
       </c>
       <c r="F83" t="n">
-        <v>11.74</v>
+        <v>12.06</v>
       </c>
       <c r="G83" t="n">
-        <v>240.1</v>
+        <v>241.1</v>
       </c>
       <c r="H83" t="n">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>431.4</v>
+        <v>-563.12</v>
       </c>
       <c r="K83" t="n">
-        <v>172.26</v>
+        <v>-373.1</v>
       </c>
       <c r="L83" t="n">
-        <v>464.52</v>
+        <v>675.51</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:32:14</t>
+          <t>10:26:05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.8</v>
+        <v>4.08</v>
       </c>
       <c r="F84" t="n">
-        <v>12.08</v>
+        <v>11.91</v>
       </c>
       <c r="G84" t="n">
-        <v>238.8</v>
+        <v>229.6</v>
       </c>
       <c r="H84" t="n">
-        <v>99.2</v>
+        <v>96.8</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>11.19</v>
+        <v>-162.06</v>
       </c>
       <c r="K84" t="n">
-        <v>-453.63</v>
+        <v>-207.91</v>
       </c>
       <c r="L84" t="n">
-        <v>453.77</v>
+        <v>263.61</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:34:55</t>
+          <t>10:28:05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.78</v>
+        <v>4.67</v>
       </c>
       <c r="F85" t="n">
-        <v>11.41</v>
+        <v>11.97</v>
       </c>
       <c r="G85" t="n">
-        <v>225</v>
+        <v>235.9</v>
       </c>
       <c r="H85" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>242.57</v>
+        <v>88.5</v>
       </c>
       <c r="K85" t="n">
-        <v>-149</v>
+        <v>-207.24</v>
       </c>
       <c r="L85" t="n">
-        <v>284.67</v>
+        <v>225.34</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:39:21</t>
+          <t>10:32:02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="F86" t="n">
-        <v>12.14</v>
+        <v>12.05</v>
       </c>
       <c r="G86" t="n">
-        <v>238.6</v>
+        <v>230.1</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>96.5</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.72</v>
+        <v>-489.45</v>
       </c>
       <c r="K86" t="n">
-        <v>134.36</v>
+        <v>145.68</v>
       </c>
       <c r="L86" t="n">
-        <v>135.16</v>
+        <v>510.67</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:40:54</t>
+          <t>10:34:16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.69</v>
+        <v>4.54</v>
       </c>
       <c r="F87" t="n">
-        <v>12.13</v>
+        <v>11.8</v>
       </c>
       <c r="G87" t="n">
-        <v>234.2</v>
+        <v>227.2</v>
       </c>
       <c r="H87" t="n">
-        <v>91.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-26.3</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>-243.91</v>
+        <v>228.39</v>
       </c>
       <c r="L87" t="n">
-        <v>245.33</v>
+        <v>246.32</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:42:01</t>
+          <t>10:35:53</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.13</v>
+        <v>4.49</v>
       </c>
       <c r="F88" t="n">
-        <v>11.62</v>
+        <v>11.82</v>
       </c>
       <c r="G88" t="n">
-        <v>223.3</v>
+        <v>227.6</v>
       </c>
       <c r="H88" t="n">
-        <v>95.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-375.8</v>
+        <v>-218.74</v>
       </c>
       <c r="K88" t="n">
-        <v>727.73</v>
+        <v>-522.98</v>
       </c>
       <c r="L88" t="n">
-        <v>819.04</v>
+        <v>566.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-238.2</v>
+        <v>-214.61</v>
       </c>
       <c r="K14" t="n">
-        <v>159.01</v>
+        <v>143.26</v>
       </c>
       <c r="L14" t="n">
-        <v>286.4</v>
+        <v>258.03</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-85.5</v>
+        <v>-149.02</v>
       </c>
       <c r="K15" t="n">
-        <v>34.16</v>
+        <v>59.54</v>
       </c>
       <c r="L15" t="n">
-        <v>92.06999999999999</v>
+        <v>160.47</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>275.92</v>
+        <v>303.43</v>
       </c>
       <c r="K16" t="n">
-        <v>-102.2</v>
+        <v>-112.39</v>
       </c>
       <c r="L16" t="n">
-        <v>294.24</v>
+        <v>323.58</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-96.83</v>
+        <v>-106.26</v>
       </c>
       <c r="K17" t="n">
-        <v>-251.18</v>
+        <v>-275.66</v>
       </c>
       <c r="L17" t="n">
-        <v>269.2</v>
+        <v>295.43</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-251.73</v>
+        <v>-286.53</v>
       </c>
       <c r="K18" t="n">
-        <v>-117.99</v>
+        <v>-134.3</v>
       </c>
       <c r="L18" t="n">
-        <v>278.01</v>
+        <v>316.45</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>403.87</v>
+        <v>363.58</v>
       </c>
       <c r="K19" t="n">
-        <v>146.36</v>
+        <v>131.76</v>
       </c>
       <c r="L19" t="n">
-        <v>429.57</v>
+        <v>386.72</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>23.62</v>
+        <v>30.78</v>
       </c>
       <c r="K20" t="n">
-        <v>-238.62</v>
+        <v>-311.01</v>
       </c>
       <c r="L20" t="n">
-        <v>239.79</v>
+        <v>312.52</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>212.97</v>
+        <v>279.42</v>
       </c>
       <c r="K21" t="n">
-        <v>280.39</v>
+        <v>367.88</v>
       </c>
       <c r="L21" t="n">
-        <v>352.1</v>
+        <v>461.96</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-188.43</v>
+        <v>-268.03</v>
       </c>
       <c r="K22" t="n">
-        <v>-170.01</v>
+        <v>-241.84</v>
       </c>
       <c r="L22" t="n">
-        <v>253.79</v>
+        <v>361.01</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-30.03</v>
+        <v>-34.66</v>
       </c>
       <c r="K23" t="n">
-        <v>469.16</v>
+        <v>541.4299999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>470.12</v>
+        <v>542.54</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>283.49</v>
+        <v>437.21</v>
       </c>
       <c r="K24" t="n">
-        <v>-133.16</v>
+        <v>-205.36</v>
       </c>
       <c r="L24" t="n">
-        <v>313.21</v>
+        <v>483.04</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>104.15</v>
+        <v>164.32</v>
       </c>
       <c r="K25" t="n">
-        <v>305.2</v>
+        <v>481.55</v>
       </c>
       <c r="L25" t="n">
-        <v>322.48</v>
+        <v>508.81</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-138.54</v>
+        <v>-245.08</v>
       </c>
       <c r="K26" t="n">
-        <v>219.76</v>
+        <v>388.76</v>
       </c>
       <c r="L26" t="n">
-        <v>259.78</v>
+        <v>459.56</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-684.5</v>
+        <v>-791.62</v>
       </c>
       <c r="K27" t="n">
-        <v>334.15</v>
+        <v>386.45</v>
       </c>
       <c r="L27" t="n">
-        <v>761.71</v>
+        <v>880.91</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>214.46</v>
+        <v>329.88</v>
       </c>
       <c r="K28" t="n">
-        <v>-405.85</v>
+        <v>-624.29</v>
       </c>
       <c r="L28" t="n">
-        <v>459.03</v>
+        <v>706.09</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>47.86</v>
+        <v>91.13</v>
       </c>
       <c r="K29" t="n">
-        <v>53.07</v>
+        <v>101.07</v>
       </c>
       <c r="L29" t="n">
-        <v>71.45999999999999</v>
+        <v>136.09</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>142.99</v>
+        <v>177.15</v>
       </c>
       <c r="K30" t="n">
-        <v>-149.76</v>
+        <v>-185.54</v>
       </c>
       <c r="L30" t="n">
-        <v>207.06</v>
+        <v>256.53</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>21</v>
+        <v>40.61</v>
       </c>
       <c r="K31" t="n">
-        <v>-62.17</v>
+        <v>-120.26</v>
       </c>
       <c r="L31" t="n">
-        <v>65.62</v>
+        <v>126.93</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-66.48</v>
+        <v>-73.5</v>
       </c>
       <c r="K32" t="n">
-        <v>171.91</v>
+        <v>190.07</v>
       </c>
       <c r="L32" t="n">
-        <v>184.32</v>
+        <v>203.79</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-157.21</v>
+        <v>-206.82</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.67</v>
+        <v>-10.09</v>
       </c>
       <c r="L33" t="n">
-        <v>157.39</v>
+        <v>207.06</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>16.36</v>
+        <v>23.92</v>
       </c>
       <c r="K34" t="n">
-        <v>135.16</v>
+        <v>197.63</v>
       </c>
       <c r="L34" t="n">
-        <v>136.14</v>
+        <v>199.07</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-199.33</v>
+        <v>-278.33</v>
       </c>
       <c r="K35" t="n">
-        <v>-119.97</v>
+        <v>-167.52</v>
       </c>
       <c r="L35" t="n">
-        <v>232.65</v>
+        <v>324.86</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-34.55</v>
+        <v>-45.6</v>
       </c>
       <c r="K36" t="n">
-        <v>-275.05</v>
+        <v>-362.97</v>
       </c>
       <c r="L36" t="n">
-        <v>277.21</v>
+        <v>365.83</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-386.35</v>
+        <v>-460.91</v>
       </c>
       <c r="K37" t="n">
-        <v>150.89</v>
+        <v>180.02</v>
       </c>
       <c r="L37" t="n">
-        <v>414.77</v>
+        <v>494.82</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>242.23</v>
+        <v>370.72</v>
       </c>
       <c r="K38" t="n">
-        <v>-102.93</v>
+        <v>-157.53</v>
       </c>
       <c r="L38" t="n">
-        <v>263.19</v>
+        <v>402.8</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-27.84</v>
+        <v>-40.85</v>
       </c>
       <c r="K39" t="n">
-        <v>364.76</v>
+        <v>535.22</v>
       </c>
       <c r="L39" t="n">
-        <v>365.82</v>
+        <v>536.78</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>15.25</v>
+        <v>22.24</v>
       </c>
       <c r="K40" t="n">
-        <v>483.55</v>
+        <v>705.3</v>
       </c>
       <c r="L40" t="n">
-        <v>483.79</v>
+        <v>705.65</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-279.94</v>
+        <v>-552.58</v>
       </c>
       <c r="K41" t="n">
-        <v>-82.73999999999999</v>
+        <v>-163.32</v>
       </c>
       <c r="L41" t="n">
-        <v>291.91</v>
+        <v>576.21</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>128.09</v>
+        <v>293.72</v>
       </c>
       <c r="K42" t="n">
-        <v>-245.84</v>
+        <v>-563.74</v>
       </c>
       <c r="L42" t="n">
-        <v>277.21</v>
+        <v>635.66</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-66.7</v>
+        <v>-151.51</v>
       </c>
       <c r="K43" t="n">
-        <v>209.72</v>
+        <v>476.39</v>
       </c>
       <c r="L43" t="n">
-        <v>220.07</v>
+        <v>499.9</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-191.28</v>
+        <v>-208.57</v>
       </c>
       <c r="K44" t="n">
-        <v>188.23</v>
+        <v>205.24</v>
       </c>
       <c r="L44" t="n">
-        <v>268.37</v>
+        <v>292.61</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>174.41</v>
+        <v>180.99</v>
       </c>
       <c r="K45" t="n">
-        <v>-93.48999999999999</v>
+        <v>-97.02</v>
       </c>
       <c r="L45" t="n">
-        <v>197.89</v>
+        <v>205.35</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-123.29</v>
+        <v>-157.95</v>
       </c>
       <c r="K46" t="n">
-        <v>49.35</v>
+        <v>63.22</v>
       </c>
       <c r="L46" t="n">
-        <v>132.8</v>
+        <v>170.13</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-296.64</v>
+        <v>-294.93</v>
       </c>
       <c r="K47" t="n">
-        <v>37.36</v>
+        <v>37.15</v>
       </c>
       <c r="L47" t="n">
-        <v>298.98</v>
+        <v>297.26</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-36.51</v>
+        <v>-43.5</v>
       </c>
       <c r="K48" t="n">
-        <v>-247.78</v>
+        <v>-295.22</v>
       </c>
       <c r="L48" t="n">
-        <v>250.46</v>
+        <v>298.4</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-85.67</v>
+        <v>-92.75</v>
       </c>
       <c r="K49" t="n">
-        <v>221.02</v>
+        <v>239.28</v>
       </c>
       <c r="L49" t="n">
-        <v>237.04</v>
+        <v>256.62</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-123.96</v>
+        <v>-194.81</v>
       </c>
       <c r="K50" t="n">
-        <v>-123.63</v>
+        <v>-194.28</v>
       </c>
       <c r="L50" t="n">
-        <v>175.07</v>
+        <v>275.13</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-66.31999999999999</v>
+        <v>-110.21</v>
       </c>
       <c r="K51" t="n">
-        <v>121.58</v>
+        <v>202.04</v>
       </c>
       <c r="L51" t="n">
-        <v>138.49</v>
+        <v>230.14</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-19.88</v>
+        <v>-39.93</v>
       </c>
       <c r="K52" t="n">
-        <v>-139.36</v>
+        <v>-279.84</v>
       </c>
       <c r="L52" t="n">
-        <v>140.77</v>
+        <v>282.67</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>-51.06</v>
+        <v>-149.37</v>
       </c>
       <c r="K53" t="n">
-        <v>111.98</v>
+        <v>327.59</v>
       </c>
       <c r="L53" t="n">
-        <v>123.07</v>
+        <v>360.04</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>183.81</v>
+        <v>204.66</v>
       </c>
       <c r="K54" t="n">
-        <v>-897.02</v>
+        <v>-998.75</v>
       </c>
       <c r="L54" t="n">
-        <v>915.66</v>
+        <v>1019.5</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-416.22</v>
+        <v>-521.6</v>
       </c>
       <c r="K55" t="n">
-        <v>-226.14</v>
+        <v>-283.4</v>
       </c>
       <c r="L55" t="n">
-        <v>473.69</v>
+        <v>593.62</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>642.53</v>
+        <v>889.79</v>
       </c>
       <c r="K56" t="n">
-        <v>472.79</v>
+        <v>654.73</v>
       </c>
       <c r="L56" t="n">
-        <v>797.73</v>
+        <v>1104.71</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-411.71</v>
+        <v>-714.52</v>
       </c>
       <c r="K57" t="n">
-        <v>152.74</v>
+        <v>265.07</v>
       </c>
       <c r="L57" t="n">
-        <v>439.13</v>
+        <v>762.11</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>-180.95</v>
+        <v>-294.92</v>
       </c>
       <c r="K58" t="n">
-        <v>-293.03</v>
+        <v>-477.6</v>
       </c>
       <c r="L58" t="n">
-        <v>344.4</v>
+        <v>561.3200000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>235.87</v>
+        <v>271.07</v>
       </c>
       <c r="K59" t="n">
-        <v>-201.63</v>
+        <v>-231.72</v>
       </c>
       <c r="L59" t="n">
-        <v>310.3</v>
+        <v>356.62</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-248.5</v>
+        <v>-296.81</v>
       </c>
       <c r="K60" t="n">
-        <v>-109.15</v>
+        <v>-130.36</v>
       </c>
       <c r="L60" t="n">
-        <v>271.42</v>
+        <v>324.18</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-103.41</v>
+        <v>-119.91</v>
       </c>
       <c r="K61" t="n">
-        <v>243.43</v>
+        <v>282.29</v>
       </c>
       <c r="L61" t="n">
-        <v>264.48</v>
+        <v>306.7</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>63.34</v>
+        <v>74.64</v>
       </c>
       <c r="K62" t="n">
-        <v>194.44</v>
+        <v>229.12</v>
       </c>
       <c r="L62" t="n">
-        <v>204.49</v>
+        <v>240.97</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-253.6</v>
+        <v>-259.39</v>
       </c>
       <c r="K63" t="n">
-        <v>295.47</v>
+        <v>302.21</v>
       </c>
       <c r="L63" t="n">
-        <v>389.38</v>
+        <v>398.27</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-424.18</v>
+        <v>-499.23</v>
       </c>
       <c r="K64" t="n">
-        <v>-18.49</v>
+        <v>-21.76</v>
       </c>
       <c r="L64" t="n">
-        <v>424.58</v>
+        <v>499.7</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>477.61</v>
+        <v>596.88</v>
       </c>
       <c r="K65" t="n">
-        <v>-341.77</v>
+        <v>-427.12</v>
       </c>
       <c r="L65" t="n">
-        <v>587.3</v>
+        <v>733.96</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>136.21</v>
+        <v>200.03</v>
       </c>
       <c r="K66" t="n">
-        <v>-179.73</v>
+        <v>-263.93</v>
       </c>
       <c r="L66" t="n">
-        <v>225.51</v>
+        <v>331.17</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-320.62</v>
+        <v>-434.71</v>
       </c>
       <c r="K67" t="n">
-        <v>37.48</v>
+        <v>50.82</v>
       </c>
       <c r="L67" t="n">
-        <v>322.8</v>
+        <v>437.67</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-278.26</v>
+        <v>-464.51</v>
       </c>
       <c r="K68" t="n">
-        <v>-100.87</v>
+        <v>-168.38</v>
       </c>
       <c r="L68" t="n">
-        <v>295.98</v>
+        <v>494.09</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>443.02</v>
+        <v>672.8200000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>39.02</v>
+        <v>59.25</v>
       </c>
       <c r="L69" t="n">
-        <v>444.73</v>
+        <v>675.4299999999999</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>68.88</v>
+        <v>186.2</v>
       </c>
       <c r="K70" t="n">
-        <v>-92.03</v>
+        <v>-248.77</v>
       </c>
       <c r="L70" t="n">
-        <v>114.95</v>
+        <v>310.73</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>194.33</v>
+        <v>479.4</v>
       </c>
       <c r="K71" t="n">
-        <v>-163.79</v>
+        <v>-404.06</v>
       </c>
       <c r="L71" t="n">
-        <v>254.15</v>
+        <v>626.97</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-450.96</v>
+        <v>-784.15</v>
       </c>
       <c r="K72" t="n">
-        <v>73.48</v>
+        <v>127.78</v>
       </c>
       <c r="L72" t="n">
-        <v>456.9</v>
+        <v>794.49</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-130.9</v>
+        <v>-223.78</v>
       </c>
       <c r="K73" t="n">
-        <v>-346.37</v>
+        <v>-592.11</v>
       </c>
       <c r="L73" t="n">
-        <v>370.28</v>
+        <v>632.98</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>56.23</v>
+        <v>83.58</v>
       </c>
       <c r="K74" t="n">
-        <v>-95.89</v>
+        <v>-142.51</v>
       </c>
       <c r="L74" t="n">
-        <v>111.16</v>
+        <v>165.21</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-189.72</v>
+        <v>-223.64</v>
       </c>
       <c r="K75" t="n">
-        <v>-199.56</v>
+        <v>-235.23</v>
       </c>
       <c r="L75" t="n">
-        <v>275.35</v>
+        <v>324.58</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>80.90000000000001</v>
+        <v>113.97</v>
       </c>
       <c r="K76" t="n">
-        <v>70.41</v>
+        <v>99.19</v>
       </c>
       <c r="L76" t="n">
-        <v>107.25</v>
+        <v>151.09</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>43.1</v>
+        <v>44.44</v>
       </c>
       <c r="K77" t="n">
-        <v>366.94</v>
+        <v>378.41</v>
       </c>
       <c r="L77" t="n">
-        <v>369.46</v>
+        <v>381.01</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-53.94</v>
+        <v>-86.94</v>
       </c>
       <c r="K78" t="n">
-        <v>85.65000000000001</v>
+        <v>138.05</v>
       </c>
       <c r="L78" t="n">
-        <v>101.22</v>
+        <v>163.14</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-105.13</v>
+        <v>-162.59</v>
       </c>
       <c r="K79" t="n">
-        <v>97.81999999999999</v>
+        <v>151.29</v>
       </c>
       <c r="L79" t="n">
-        <v>143.6</v>
+        <v>222.09</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>414.85</v>
+        <v>526.34</v>
       </c>
       <c r="K80" t="n">
-        <v>-228.37</v>
+        <v>-289.75</v>
       </c>
       <c r="L80" t="n">
-        <v>473.55</v>
+        <v>600.8200000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-314.49</v>
+        <v>-327.62</v>
       </c>
       <c r="K81" t="n">
-        <v>-48.45</v>
+        <v>-50.47</v>
       </c>
       <c r="L81" t="n">
-        <v>318.2</v>
+        <v>331.48</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-349.63</v>
+        <v>-452.93</v>
       </c>
       <c r="K82" t="n">
-        <v>-112.32</v>
+        <v>-145.5</v>
       </c>
       <c r="L82" t="n">
-        <v>367.23</v>
+        <v>475.73</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-563.12</v>
+        <v>-828.7</v>
       </c>
       <c r="K83" t="n">
-        <v>-373.1</v>
+        <v>-549.0599999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>675.51</v>
+        <v>994.08</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-162.06</v>
+        <v>-266.81</v>
       </c>
       <c r="K84" t="n">
-        <v>-207.91</v>
+        <v>-342.29</v>
       </c>
       <c r="L84" t="n">
-        <v>263.61</v>
+        <v>433.99</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>88.5</v>
+        <v>161.1</v>
       </c>
       <c r="K85" t="n">
-        <v>-207.24</v>
+        <v>-377.25</v>
       </c>
       <c r="L85" t="n">
-        <v>225.34</v>
+        <v>410.21</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-489.45</v>
+        <v>-857.3200000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>145.68</v>
+        <v>255.17</v>
       </c>
       <c r="L86" t="n">
-        <v>510.67</v>
+        <v>894.49</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>92.23999999999999</v>
+        <v>205.78</v>
       </c>
       <c r="K87" t="n">
-        <v>228.39</v>
+        <v>509.51</v>
       </c>
       <c r="L87" t="n">
-        <v>246.32</v>
+        <v>549.49</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-218.74</v>
+        <v>-318.99</v>
       </c>
       <c r="K88" t="n">
-        <v>-522.98</v>
+        <v>-762.66</v>
       </c>
       <c r="L88" t="n">
-        <v>566.88</v>
+        <v>826.6799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-214.61</v>
+        <v>-170.9</v>
       </c>
       <c r="K14" t="n">
-        <v>143.26</v>
+        <v>114.08</v>
       </c>
       <c r="L14" t="n">
-        <v>258.03</v>
+        <v>205.47</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-149.02</v>
+        <v>-103.73</v>
       </c>
       <c r="K15" t="n">
-        <v>59.54</v>
+        <v>41.44</v>
       </c>
       <c r="L15" t="n">
-        <v>160.47</v>
+        <v>111.7</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>303.43</v>
+        <v>197.89</v>
       </c>
       <c r="K16" t="n">
-        <v>-112.39</v>
+        <v>-73.3</v>
       </c>
       <c r="L16" t="n">
-        <v>323.58</v>
+        <v>211.03</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-106.26</v>
+        <v>-72.37</v>
       </c>
       <c r="K17" t="n">
-        <v>-275.66</v>
+        <v>-187.73</v>
       </c>
       <c r="L17" t="n">
-        <v>295.43</v>
+        <v>201.19</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-286.53</v>
+        <v>-188.33</v>
       </c>
       <c r="K18" t="n">
-        <v>-134.3</v>
+        <v>-88.27</v>
       </c>
       <c r="L18" t="n">
-        <v>316.45</v>
+        <v>207.99</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>363.58</v>
+        <v>260.67</v>
       </c>
       <c r="K19" t="n">
-        <v>131.76</v>
+        <v>94.47</v>
       </c>
       <c r="L19" t="n">
-        <v>386.72</v>
+        <v>277.26</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>30.78</v>
+        <v>19.05</v>
       </c>
       <c r="K20" t="n">
-        <v>-311.01</v>
+        <v>-192.46</v>
       </c>
       <c r="L20" t="n">
-        <v>312.52</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>279.42</v>
+        <v>152.48</v>
       </c>
       <c r="K21" t="n">
-        <v>367.88</v>
+        <v>200.76</v>
       </c>
       <c r="L21" t="n">
-        <v>461.96</v>
+        <v>252.1</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-268.03</v>
+        <v>-157.26</v>
       </c>
       <c r="K22" t="n">
-        <v>-241.84</v>
+        <v>-141.89</v>
       </c>
       <c r="L22" t="n">
-        <v>361.01</v>
+        <v>211.8</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-34.66</v>
+        <v>-19.79</v>
       </c>
       <c r="K23" t="n">
-        <v>541.4299999999999</v>
+        <v>309.23</v>
       </c>
       <c r="L23" t="n">
-        <v>542.54</v>
+        <v>309.87</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>437.21</v>
+        <v>214.53</v>
       </c>
       <c r="K24" t="n">
-        <v>-205.36</v>
+        <v>-100.76</v>
       </c>
       <c r="L24" t="n">
-        <v>483.04</v>
+        <v>237.02</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>164.32</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>481.55</v>
+        <v>256.13</v>
       </c>
       <c r="L25" t="n">
-        <v>508.81</v>
+        <v>270.63</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-245.08</v>
+        <v>-118.67</v>
       </c>
       <c r="K26" t="n">
-        <v>388.76</v>
+        <v>188.24</v>
       </c>
       <c r="L26" t="n">
-        <v>459.56</v>
+        <v>222.52</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-791.62</v>
+        <v>-413.21</v>
       </c>
       <c r="K27" t="n">
-        <v>386.45</v>
+        <v>201.72</v>
       </c>
       <c r="L27" t="n">
-        <v>880.91</v>
+        <v>459.82</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>329.88</v>
+        <v>151.83</v>
       </c>
       <c r="K28" t="n">
-        <v>-624.29</v>
+        <v>-287.33</v>
       </c>
       <c r="L28" t="n">
-        <v>706.09</v>
+        <v>324.98</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>91.13</v>
+        <v>62.55</v>
       </c>
       <c r="K29" t="n">
-        <v>101.07</v>
+        <v>69.37</v>
       </c>
       <c r="L29" t="n">
-        <v>136.09</v>
+        <v>93.41</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>177.15</v>
+        <v>117.29</v>
       </c>
       <c r="K30" t="n">
-        <v>-185.54</v>
+        <v>-122.84</v>
       </c>
       <c r="L30" t="n">
-        <v>256.53</v>
+        <v>169.84</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>40.61</v>
+        <v>29.44</v>
       </c>
       <c r="K31" t="n">
-        <v>-120.26</v>
+        <v>-87.17</v>
       </c>
       <c r="L31" t="n">
-        <v>126.93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-73.5</v>
+        <v>-55.66</v>
       </c>
       <c r="K32" t="n">
-        <v>190.07</v>
+        <v>143.94</v>
       </c>
       <c r="L32" t="n">
-        <v>203.79</v>
+        <v>154.33</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-206.82</v>
+        <v>-133.83</v>
       </c>
       <c r="K33" t="n">
-        <v>-10.09</v>
+        <v>-6.53</v>
       </c>
       <c r="L33" t="n">
-        <v>207.06</v>
+        <v>133.98</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>23.92</v>
+        <v>17.03</v>
       </c>
       <c r="K34" t="n">
-        <v>197.63</v>
+        <v>140.66</v>
       </c>
       <c r="L34" t="n">
-        <v>199.07</v>
+        <v>141.69</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-278.33</v>
+        <v>-161.84</v>
       </c>
       <c r="K35" t="n">
-        <v>-167.52</v>
+        <v>-97.41</v>
       </c>
       <c r="L35" t="n">
-        <v>324.86</v>
+        <v>188.9</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-45.6</v>
+        <v>-25.91</v>
       </c>
       <c r="K36" t="n">
-        <v>-362.97</v>
+        <v>-206.29</v>
       </c>
       <c r="L36" t="n">
-        <v>365.83</v>
+        <v>207.91</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-460.91</v>
+        <v>-264.93</v>
       </c>
       <c r="K37" t="n">
-        <v>180.02</v>
+        <v>103.47</v>
       </c>
       <c r="L37" t="n">
-        <v>494.82</v>
+        <v>284.42</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>370.72</v>
+        <v>212.82</v>
       </c>
       <c r="K38" t="n">
-        <v>-157.53</v>
+        <v>-90.43000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>402.8</v>
+        <v>231.24</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-40.85</v>
+        <v>-20.34</v>
       </c>
       <c r="K39" t="n">
-        <v>535.22</v>
+        <v>266.5</v>
       </c>
       <c r="L39" t="n">
-        <v>536.78</v>
+        <v>267.28</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>22.24</v>
+        <v>10.82</v>
       </c>
       <c r="K40" t="n">
-        <v>705.3</v>
+        <v>343.15</v>
       </c>
       <c r="L40" t="n">
-        <v>705.65</v>
+        <v>343.32</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-552.58</v>
+        <v>-255.97</v>
       </c>
       <c r="K41" t="n">
-        <v>-163.32</v>
+        <v>-75.65000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>576.21</v>
+        <v>266.91</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>293.72</v>
+        <v>125.81</v>
       </c>
       <c r="K42" t="n">
-        <v>-563.74</v>
+        <v>-241.46</v>
       </c>
       <c r="L42" t="n">
-        <v>635.66</v>
+        <v>272.27</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-151.51</v>
+        <v>-67.58</v>
       </c>
       <c r="K43" t="n">
-        <v>476.39</v>
+        <v>212.5</v>
       </c>
       <c r="L43" t="n">
-        <v>499.9</v>
+        <v>222.98</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-208.57</v>
+        <v>-137.4</v>
       </c>
       <c r="K44" t="n">
-        <v>205.24</v>
+        <v>135.21</v>
       </c>
       <c r="L44" t="n">
-        <v>292.61</v>
+        <v>192.77</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>180.99</v>
+        <v>142.25</v>
       </c>
       <c r="K45" t="n">
-        <v>-97.02</v>
+        <v>-76.25</v>
       </c>
       <c r="L45" t="n">
-        <v>205.35</v>
+        <v>161.39</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-157.95</v>
+        <v>-113.18</v>
       </c>
       <c r="K46" t="n">
-        <v>63.22</v>
+        <v>45.3</v>
       </c>
       <c r="L46" t="n">
-        <v>170.13</v>
+        <v>121.91</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-294.93</v>
+        <v>-220.66</v>
       </c>
       <c r="K47" t="n">
-        <v>37.15</v>
+        <v>27.79</v>
       </c>
       <c r="L47" t="n">
-        <v>297.26</v>
+        <v>222.41</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-43.5</v>
+        <v>-28.45</v>
       </c>
       <c r="K48" t="n">
-        <v>-295.22</v>
+        <v>-193.13</v>
       </c>
       <c r="L48" t="n">
-        <v>298.4</v>
+        <v>195.22</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-92.75</v>
+        <v>-67.22</v>
       </c>
       <c r="K49" t="n">
-        <v>239.28</v>
+        <v>173.41</v>
       </c>
       <c r="L49" t="n">
-        <v>256.62</v>
+        <v>185.98</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-194.81</v>
+        <v>-118.71</v>
       </c>
       <c r="K50" t="n">
-        <v>-194.28</v>
+        <v>-118.39</v>
       </c>
       <c r="L50" t="n">
-        <v>275.13</v>
+        <v>167.66</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-110.21</v>
+        <v>-71.8</v>
       </c>
       <c r="K51" t="n">
-        <v>202.04</v>
+        <v>131.63</v>
       </c>
       <c r="L51" t="n">
-        <v>230.14</v>
+        <v>149.94</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-39.93</v>
+        <v>-22.53</v>
       </c>
       <c r="K52" t="n">
-        <v>-279.84</v>
+        <v>-157.91</v>
       </c>
       <c r="L52" t="n">
-        <v>282.67</v>
+        <v>159.5</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>-149.37</v>
+        <v>-70.95</v>
       </c>
       <c r="K53" t="n">
-        <v>327.59</v>
+        <v>155.59</v>
       </c>
       <c r="L53" t="n">
-        <v>360.04</v>
+        <v>171.01</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>204.66</v>
+        <v>115.55</v>
       </c>
       <c r="K54" t="n">
-        <v>-998.75</v>
+        <v>-563.89</v>
       </c>
       <c r="L54" t="n">
-        <v>1019.5</v>
+        <v>575.6</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-521.6</v>
+        <v>-270.85</v>
       </c>
       <c r="K55" t="n">
-        <v>-283.4</v>
+        <v>-147.16</v>
       </c>
       <c r="L55" t="n">
-        <v>593.62</v>
+        <v>308.25</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>889.79</v>
+        <v>398.71</v>
       </c>
       <c r="K56" t="n">
-        <v>654.73</v>
+        <v>293.38</v>
       </c>
       <c r="L56" t="n">
-        <v>1104.71</v>
+        <v>495.02</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-714.52</v>
+        <v>-313.25</v>
       </c>
       <c r="K57" t="n">
-        <v>265.07</v>
+        <v>116.21</v>
       </c>
       <c r="L57" t="n">
-        <v>762.11</v>
+        <v>334.11</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>-294.92</v>
+        <v>-150.9</v>
       </c>
       <c r="K58" t="n">
-        <v>-477.6</v>
+        <v>-244.37</v>
       </c>
       <c r="L58" t="n">
-        <v>561.3200000000001</v>
+        <v>287.2</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>271.07</v>
+        <v>173.63</v>
       </c>
       <c r="K59" t="n">
-        <v>-231.72</v>
+        <v>-148.42</v>
       </c>
       <c r="L59" t="n">
-        <v>356.62</v>
+        <v>228.42</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-296.81</v>
+        <v>-190.11</v>
       </c>
       <c r="K60" t="n">
-        <v>-130.36</v>
+        <v>-83.5</v>
       </c>
       <c r="L60" t="n">
-        <v>324.18</v>
+        <v>207.64</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-119.91</v>
+        <v>-80.81999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>282.29</v>
+        <v>190.25</v>
       </c>
       <c r="L61" t="n">
-        <v>306.7</v>
+        <v>206.71</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>74.64</v>
+        <v>52.27</v>
       </c>
       <c r="K62" t="n">
-        <v>229.12</v>
+        <v>160.44</v>
       </c>
       <c r="L62" t="n">
-        <v>240.97</v>
+        <v>168.74</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-259.39</v>
+        <v>-165.03</v>
       </c>
       <c r="K63" t="n">
-        <v>302.21</v>
+        <v>192.28</v>
       </c>
       <c r="L63" t="n">
-        <v>398.27</v>
+        <v>253.39</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-499.23</v>
+        <v>-303.36</v>
       </c>
       <c r="K64" t="n">
-        <v>-21.76</v>
+        <v>-13.22</v>
       </c>
       <c r="L64" t="n">
-        <v>499.7</v>
+        <v>303.65</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>596.88</v>
+        <v>322.15</v>
       </c>
       <c r="K65" t="n">
-        <v>-427.12</v>
+        <v>-230.53</v>
       </c>
       <c r="L65" t="n">
-        <v>733.96</v>
+        <v>396.14</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>200.03</v>
+        <v>123.66</v>
       </c>
       <c r="K66" t="n">
-        <v>-263.93</v>
+        <v>-163.16</v>
       </c>
       <c r="L66" t="n">
-        <v>331.17</v>
+        <v>204.73</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-434.71</v>
+        <v>-246.48</v>
       </c>
       <c r="K67" t="n">
-        <v>50.82</v>
+        <v>28.81</v>
       </c>
       <c r="L67" t="n">
-        <v>437.67</v>
+        <v>248.16</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-464.51</v>
+        <v>-224.48</v>
       </c>
       <c r="K68" t="n">
-        <v>-168.38</v>
+        <v>-81.37</v>
       </c>
       <c r="L68" t="n">
-        <v>494.09</v>
+        <v>238.78</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>672.8200000000001</v>
+        <v>342.18</v>
       </c>
       <c r="K69" t="n">
-        <v>59.25</v>
+        <v>30.14</v>
       </c>
       <c r="L69" t="n">
-        <v>675.4299999999999</v>
+        <v>343.5</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>186.2</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>-248.77</v>
+        <v>-132.61</v>
       </c>
       <c r="L70" t="n">
-        <v>310.73</v>
+        <v>165.64</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>479.4</v>
+        <v>204.8</v>
       </c>
       <c r="K71" t="n">
-        <v>-404.06</v>
+        <v>-172.62</v>
       </c>
       <c r="L71" t="n">
-        <v>626.97</v>
+        <v>267.84</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-784.15</v>
+        <v>-341.27</v>
       </c>
       <c r="K72" t="n">
-        <v>127.78</v>
+        <v>55.61</v>
       </c>
       <c r="L72" t="n">
-        <v>794.49</v>
+        <v>345.78</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-223.78</v>
+        <v>-108.79</v>
       </c>
       <c r="K73" t="n">
-        <v>-592.11</v>
+        <v>-287.85</v>
       </c>
       <c r="L73" t="n">
-        <v>632.98</v>
+        <v>307.72</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>83.58</v>
+        <v>60.51</v>
       </c>
       <c r="K74" t="n">
-        <v>-142.51</v>
+        <v>-103.18</v>
       </c>
       <c r="L74" t="n">
-        <v>165.21</v>
+        <v>119.61</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-223.64</v>
+        <v>-143.76</v>
       </c>
       <c r="K75" t="n">
-        <v>-235.23</v>
+        <v>-151.21</v>
       </c>
       <c r="L75" t="n">
-        <v>324.58</v>
+        <v>208.64</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>113.97</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>99.19</v>
+        <v>76.97</v>
       </c>
       <c r="L76" t="n">
-        <v>151.09</v>
+        <v>117.24</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>44.44</v>
+        <v>32.58</v>
       </c>
       <c r="K77" t="n">
-        <v>378.41</v>
+        <v>277.39</v>
       </c>
       <c r="L77" t="n">
-        <v>381.01</v>
+        <v>279.3</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-86.94</v>
+        <v>-64.29000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>138.05</v>
+        <v>102.08</v>
       </c>
       <c r="L78" t="n">
-        <v>163.14</v>
+        <v>120.64</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-162.59</v>
+        <v>-108.36</v>
       </c>
       <c r="K79" t="n">
-        <v>151.29</v>
+        <v>100.83</v>
       </c>
       <c r="L79" t="n">
-        <v>222.09</v>
+        <v>148.01</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>526.34</v>
+        <v>287.86</v>
       </c>
       <c r="K80" t="n">
-        <v>-289.75</v>
+        <v>-158.46</v>
       </c>
       <c r="L80" t="n">
-        <v>600.8200000000001</v>
+        <v>328.59</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-327.62</v>
+        <v>-212.26</v>
       </c>
       <c r="K81" t="n">
-        <v>-50.47</v>
+        <v>-32.7</v>
       </c>
       <c r="L81" t="n">
-        <v>331.48</v>
+        <v>214.76</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-452.93</v>
+        <v>-283.9</v>
       </c>
       <c r="K82" t="n">
-        <v>-145.5</v>
+        <v>-91.2</v>
       </c>
       <c r="L82" t="n">
-        <v>475.73</v>
+        <v>298.19</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-828.7</v>
+        <v>-384.84</v>
       </c>
       <c r="K83" t="n">
-        <v>-549.0599999999999</v>
+        <v>-254.98</v>
       </c>
       <c r="L83" t="n">
-        <v>994.08</v>
+        <v>461.64</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-266.81</v>
+        <v>-139.85</v>
       </c>
       <c r="K84" t="n">
-        <v>-342.29</v>
+        <v>-179.41</v>
       </c>
       <c r="L84" t="n">
-        <v>433.99</v>
+        <v>227.48</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>161.1</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>-377.25</v>
+        <v>-207.49</v>
       </c>
       <c r="L85" t="n">
-        <v>410.21</v>
+        <v>225.61</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-857.3200000000001</v>
+        <v>-366.78</v>
       </c>
       <c r="K86" t="n">
-        <v>255.17</v>
+        <v>109.17</v>
       </c>
       <c r="L86" t="n">
-        <v>894.49</v>
+        <v>382.69</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>205.78</v>
+        <v>94.86</v>
       </c>
       <c r="K87" t="n">
-        <v>509.51</v>
+        <v>234.86</v>
       </c>
       <c r="L87" t="n">
-        <v>549.49</v>
+        <v>253.3</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-318.99</v>
+        <v>-152.14</v>
       </c>
       <c r="K88" t="n">
-        <v>-762.66</v>
+        <v>-363.74</v>
       </c>
       <c r="L88" t="n">
-        <v>826.6799999999999</v>
+        <v>394.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-170.9</v>
+        <v>-181.43</v>
       </c>
       <c r="K14" t="n">
-        <v>114.08</v>
+        <v>121.11</v>
       </c>
       <c r="L14" t="n">
-        <v>205.47</v>
+        <v>218.14</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-103.73</v>
+        <v>-113.51</v>
       </c>
       <c r="K15" t="n">
-        <v>41.44</v>
+        <v>45.35</v>
       </c>
       <c r="L15" t="n">
-        <v>111.7</v>
+        <v>122.24</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>197.89</v>
+        <v>217.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-73.3</v>
+        <v>-80.67</v>
       </c>
       <c r="L16" t="n">
-        <v>211.03</v>
+        <v>232.26</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-72.37</v>
+        <v>-79.94</v>
       </c>
       <c r="K17" t="n">
-        <v>-187.73</v>
+        <v>-207.38</v>
       </c>
       <c r="L17" t="n">
-        <v>201.19</v>
+        <v>222.26</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-188.33</v>
+        <v>-208.83</v>
       </c>
       <c r="K18" t="n">
-        <v>-88.27</v>
+        <v>-97.88</v>
       </c>
       <c r="L18" t="n">
-        <v>207.99</v>
+        <v>230.63</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>260.67</v>
+        <v>287.44</v>
       </c>
       <c r="K19" t="n">
-        <v>94.47</v>
+        <v>104.17</v>
       </c>
       <c r="L19" t="n">
-        <v>277.26</v>
+        <v>305.73</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>19.05</v>
+        <v>21.63</v>
       </c>
       <c r="K20" t="n">
-        <v>-192.46</v>
+        <v>-218.51</v>
       </c>
       <c r="L20" t="n">
-        <v>193.4</v>
+        <v>219.58</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>152.48</v>
+        <v>176.23</v>
       </c>
       <c r="K21" t="n">
-        <v>200.76</v>
+        <v>232.02</v>
       </c>
       <c r="L21" t="n">
-        <v>252.1</v>
+        <v>291.36</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-157.26</v>
+        <v>-178.89</v>
       </c>
       <c r="K22" t="n">
-        <v>-141.89</v>
+        <v>-161.41</v>
       </c>
       <c r="L22" t="n">
-        <v>211.8</v>
+        <v>240.95</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-19.79</v>
+        <v>-22.81</v>
       </c>
       <c r="K23" t="n">
-        <v>309.23</v>
+        <v>356.31</v>
       </c>
       <c r="L23" t="n">
-        <v>309.87</v>
+        <v>357.04</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>214.53</v>
+        <v>252.62</v>
       </c>
       <c r="K24" t="n">
-        <v>-100.76</v>
+        <v>-118.65</v>
       </c>
       <c r="L24" t="n">
-        <v>237.02</v>
+        <v>279.09</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>87.40000000000001</v>
+        <v>102.23</v>
       </c>
       <c r="K25" t="n">
-        <v>256.13</v>
+        <v>299.57</v>
       </c>
       <c r="L25" t="n">
-        <v>270.63</v>
+        <v>316.53</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-118.67</v>
+        <v>-139.47</v>
       </c>
       <c r="K26" t="n">
-        <v>188.24</v>
+        <v>221.24</v>
       </c>
       <c r="L26" t="n">
-        <v>222.52</v>
+        <v>261.53</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-413.21</v>
+        <v>-488.07</v>
       </c>
       <c r="K27" t="n">
-        <v>201.72</v>
+        <v>238.26</v>
       </c>
       <c r="L27" t="n">
-        <v>459.82</v>
+        <v>543.12</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>151.83</v>
+        <v>183.3</v>
       </c>
       <c r="K28" t="n">
-        <v>-287.33</v>
+        <v>-346.88</v>
       </c>
       <c r="L28" t="n">
-        <v>324.98</v>
+        <v>392.33</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>62.55</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>69.37</v>
+        <v>75.8</v>
       </c>
       <c r="L29" t="n">
-        <v>93.41</v>
+        <v>102.07</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>117.29</v>
+        <v>129.12</v>
       </c>
       <c r="K30" t="n">
-        <v>-122.84</v>
+        <v>-135.24</v>
       </c>
       <c r="L30" t="n">
-        <v>169.84</v>
+        <v>186.98</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>29.44</v>
+        <v>31.96</v>
       </c>
       <c r="K31" t="n">
-        <v>-87.17</v>
+        <v>-94.64</v>
       </c>
       <c r="L31" t="n">
-        <v>92</v>
+        <v>99.89</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-55.66</v>
+        <v>-60.61</v>
       </c>
       <c r="K32" t="n">
-        <v>143.94</v>
+        <v>156.74</v>
       </c>
       <c r="L32" t="n">
-        <v>154.33</v>
+        <v>168.05</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-133.83</v>
+        <v>-148.04</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.53</v>
+        <v>-7.22</v>
       </c>
       <c r="L33" t="n">
-        <v>133.98</v>
+        <v>148.21</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>17.03</v>
+        <v>18.55</v>
       </c>
       <c r="K34" t="n">
-        <v>140.66</v>
+        <v>153.25</v>
       </c>
       <c r="L34" t="n">
-        <v>141.69</v>
+        <v>154.37</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-161.84</v>
+        <v>-186.2</v>
       </c>
       <c r="K35" t="n">
-        <v>-97.41</v>
+        <v>-112.06</v>
       </c>
       <c r="L35" t="n">
-        <v>188.9</v>
+        <v>217.32</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>-25.91</v>
+        <v>-29.95</v>
       </c>
       <c r="K36" t="n">
-        <v>-206.29</v>
+        <v>-238.38</v>
       </c>
       <c r="L36" t="n">
-        <v>207.91</v>
+        <v>240.25</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-264.93</v>
+        <v>-303.01</v>
       </c>
       <c r="K37" t="n">
-        <v>103.47</v>
+        <v>118.35</v>
       </c>
       <c r="L37" t="n">
-        <v>284.42</v>
+        <v>325.3</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>212.82</v>
+        <v>247.11</v>
       </c>
       <c r="K38" t="n">
-        <v>-90.43000000000001</v>
+        <v>-105</v>
       </c>
       <c r="L38" t="n">
-        <v>231.24</v>
+        <v>268.49</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-20.34</v>
+        <v>-24.11</v>
       </c>
       <c r="K39" t="n">
-        <v>266.5</v>
+        <v>315.88</v>
       </c>
       <c r="L39" t="n">
-        <v>267.28</v>
+        <v>316.8</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>10.82</v>
+        <v>12.72</v>
       </c>
       <c r="K40" t="n">
-        <v>343.15</v>
+        <v>403.35</v>
       </c>
       <c r="L40" t="n">
-        <v>343.32</v>
+        <v>403.55</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-255.97</v>
+        <v>-308.93</v>
       </c>
       <c r="K41" t="n">
-        <v>-75.65000000000001</v>
+        <v>-91.3</v>
       </c>
       <c r="L41" t="n">
-        <v>266.91</v>
+        <v>322.14</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>125.81</v>
+        <v>154.66</v>
       </c>
       <c r="K42" t="n">
-        <v>-241.46</v>
+        <v>-296.85</v>
       </c>
       <c r="L42" t="n">
-        <v>272.27</v>
+        <v>334.72</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-67.58</v>
+        <v>-81.78</v>
       </c>
       <c r="K43" t="n">
-        <v>212.5</v>
+        <v>257.15</v>
       </c>
       <c r="L43" t="n">
-        <v>222.98</v>
+        <v>269.84</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-137.4</v>
+        <v>-149.76</v>
       </c>
       <c r="K44" t="n">
-        <v>135.21</v>
+        <v>147.38</v>
       </c>
       <c r="L44" t="n">
-        <v>192.77</v>
+        <v>210.12</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>142.25</v>
+        <v>152.24</v>
       </c>
       <c r="K45" t="n">
-        <v>-76.25</v>
+        <v>-81.61</v>
       </c>
       <c r="L45" t="n">
-        <v>161.39</v>
+        <v>172.74</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-113.18</v>
+        <v>-122.48</v>
       </c>
       <c r="K46" t="n">
-        <v>45.3</v>
+        <v>49.02</v>
       </c>
       <c r="L46" t="n">
-        <v>121.91</v>
+        <v>131.92</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-220.66</v>
+        <v>-239.91</v>
       </c>
       <c r="K47" t="n">
-        <v>27.79</v>
+        <v>30.22</v>
       </c>
       <c r="L47" t="n">
-        <v>222.41</v>
+        <v>241.81</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-28.45</v>
+        <v>-31.53</v>
       </c>
       <c r="K48" t="n">
-        <v>-193.13</v>
+        <v>-214</v>
       </c>
       <c r="L48" t="n">
-        <v>195.22</v>
+        <v>216.31</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-67.22</v>
+        <v>-73.5</v>
       </c>
       <c r="K49" t="n">
-        <v>173.41</v>
+        <v>189.62</v>
       </c>
       <c r="L49" t="n">
-        <v>185.98</v>
+        <v>203.37</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-118.71</v>
+        <v>-134.39</v>
       </c>
       <c r="K50" t="n">
-        <v>-118.39</v>
+        <v>-134.03</v>
       </c>
       <c r="L50" t="n">
-        <v>167.66</v>
+        <v>189.8</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-71.8</v>
+        <v>-80.93000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>131.63</v>
+        <v>148.38</v>
       </c>
       <c r="L51" t="n">
-        <v>149.94</v>
+        <v>169.01</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-22.53</v>
+        <v>-25.72</v>
       </c>
       <c r="K52" t="n">
-        <v>-157.91</v>
+        <v>-180.27</v>
       </c>
       <c r="L52" t="n">
-        <v>159.5</v>
+        <v>182.1</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>-70.95</v>
+        <v>-84.76000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>155.59</v>
+        <v>185.89</v>
       </c>
       <c r="L53" t="n">
-        <v>171.01</v>
+        <v>204.3</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>115.55</v>
+        <v>133.19</v>
       </c>
       <c r="K54" t="n">
-        <v>-563.89</v>
+        <v>-650</v>
       </c>
       <c r="L54" t="n">
-        <v>575.6</v>
+        <v>663.5</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-270.85</v>
+        <v>-318.81</v>
       </c>
       <c r="K55" t="n">
-        <v>-147.16</v>
+        <v>-173.22</v>
       </c>
       <c r="L55" t="n">
-        <v>308.25</v>
+        <v>362.83</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>398.71</v>
+        <v>484.79</v>
       </c>
       <c r="K56" t="n">
-        <v>293.38</v>
+        <v>356.72</v>
       </c>
       <c r="L56" t="n">
-        <v>495.02</v>
+        <v>601.89</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-313.25</v>
+        <v>-383.97</v>
       </c>
       <c r="K57" t="n">
-        <v>116.21</v>
+        <v>142.44</v>
       </c>
       <c r="L57" t="n">
-        <v>334.11</v>
+        <v>409.54</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>-150.9</v>
+        <v>-178.85</v>
       </c>
       <c r="K58" t="n">
-        <v>-244.37</v>
+        <v>-289.63</v>
       </c>
       <c r="L58" t="n">
-        <v>287.2</v>
+        <v>340.4</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>173.63</v>
+        <v>191.75</v>
       </c>
       <c r="K59" t="n">
-        <v>-148.42</v>
+        <v>-163.91</v>
       </c>
       <c r="L59" t="n">
-        <v>228.42</v>
+        <v>252.26</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-190.11</v>
+        <v>-210.69</v>
       </c>
       <c r="K60" t="n">
-        <v>-83.5</v>
+        <v>-92.54000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>207.64</v>
+        <v>230.12</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-80.81999999999999</v>
+        <v>-88.7</v>
       </c>
       <c r="K61" t="n">
-        <v>190.25</v>
+        <v>208.82</v>
       </c>
       <c r="L61" t="n">
-        <v>206.71</v>
+        <v>226.88</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>52.27</v>
+        <v>57.13</v>
       </c>
       <c r="K62" t="n">
-        <v>160.44</v>
+        <v>175.37</v>
       </c>
       <c r="L62" t="n">
-        <v>168.74</v>
+        <v>184.44</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-165.03</v>
+        <v>-185.22</v>
       </c>
       <c r="K63" t="n">
-        <v>192.28</v>
+        <v>215.81</v>
       </c>
       <c r="L63" t="n">
-        <v>253.39</v>
+        <v>284.39</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-303.36</v>
+        <v>-338.77</v>
       </c>
       <c r="K64" t="n">
-        <v>-13.22</v>
+        <v>-14.76</v>
       </c>
       <c r="L64" t="n">
-        <v>303.65</v>
+        <v>339.1</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>322.15</v>
+        <v>372.27</v>
       </c>
       <c r="K65" t="n">
-        <v>-230.53</v>
+        <v>-266.39</v>
       </c>
       <c r="L65" t="n">
-        <v>396.14</v>
+        <v>457.77</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>123.66</v>
+        <v>139.41</v>
       </c>
       <c r="K66" t="n">
-        <v>-163.16</v>
+        <v>-183.95</v>
       </c>
       <c r="L66" t="n">
-        <v>204.73</v>
+        <v>230.81</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-246.48</v>
+        <v>-282.91</v>
       </c>
       <c r="K67" t="n">
-        <v>28.81</v>
+        <v>33.07</v>
       </c>
       <c r="L67" t="n">
-        <v>248.16</v>
+        <v>284.83</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-224.48</v>
+        <v>-267.37</v>
       </c>
       <c r="K68" t="n">
-        <v>-81.37</v>
+        <v>-96.92</v>
       </c>
       <c r="L68" t="n">
-        <v>238.78</v>
+        <v>284.39</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>342.18</v>
+        <v>401.51</v>
       </c>
       <c r="K69" t="n">
-        <v>30.14</v>
+        <v>35.36</v>
       </c>
       <c r="L69" t="n">
-        <v>343.5</v>
+        <v>403.06</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>99.26000000000001</v>
+        <v>116.46</v>
       </c>
       <c r="K70" t="n">
-        <v>-132.61</v>
+        <v>-155.59</v>
       </c>
       <c r="L70" t="n">
-        <v>165.64</v>
+        <v>194.34</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>204.8</v>
+        <v>250.91</v>
       </c>
       <c r="K71" t="n">
-        <v>-172.62</v>
+        <v>-211.48</v>
       </c>
       <c r="L71" t="n">
-        <v>267.84</v>
+        <v>328.15</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-341.27</v>
+        <v>-418.88</v>
       </c>
       <c r="K72" t="n">
-        <v>55.61</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>345.78</v>
+        <v>424.41</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-108.79</v>
+        <v>-130.4</v>
       </c>
       <c r="K73" t="n">
-        <v>-287.85</v>
+        <v>-345.03</v>
       </c>
       <c r="L73" t="n">
-        <v>307.72</v>
+        <v>368.85</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>60.51</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-103.18</v>
+        <v>-111.7</v>
       </c>
       <c r="L74" t="n">
-        <v>119.61</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-143.76</v>
+        <v>-159.12</v>
       </c>
       <c r="K75" t="n">
-        <v>-151.21</v>
+        <v>-167.36</v>
       </c>
       <c r="L75" t="n">
-        <v>208.64</v>
+        <v>230.93</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>88.43000000000001</v>
+        <v>95.13</v>
       </c>
       <c r="K76" t="n">
-        <v>76.97</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>117.24</v>
+        <v>126.11</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>32.58</v>
+        <v>35.23</v>
       </c>
       <c r="K77" t="n">
-        <v>277.39</v>
+        <v>300</v>
       </c>
       <c r="L77" t="n">
-        <v>279.3</v>
+        <v>302.06</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-64.29000000000001</v>
+        <v>-69.77</v>
       </c>
       <c r="K78" t="n">
-        <v>102.08</v>
+        <v>110.79</v>
       </c>
       <c r="L78" t="n">
-        <v>120.64</v>
+        <v>130.93</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-108.36</v>
+        <v>-118.82</v>
       </c>
       <c r="K79" t="n">
-        <v>100.83</v>
+        <v>110.56</v>
       </c>
       <c r="L79" t="n">
-        <v>148.01</v>
+        <v>162.31</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>287.86</v>
+        <v>331.78</v>
       </c>
       <c r="K80" t="n">
-        <v>-158.46</v>
+        <v>-182.64</v>
       </c>
       <c r="L80" t="n">
-        <v>328.59</v>
+        <v>378.73</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-212.26</v>
+        <v>-238.46</v>
       </c>
       <c r="K81" t="n">
-        <v>-32.7</v>
+        <v>-36.74</v>
       </c>
       <c r="L81" t="n">
-        <v>214.76</v>
+        <v>241.27</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-283.9</v>
+        <v>-318.03</v>
       </c>
       <c r="K82" t="n">
-        <v>-91.2</v>
+        <v>-102.17</v>
       </c>
       <c r="L82" t="n">
-        <v>298.19</v>
+        <v>334.04</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-384.84</v>
+        <v>-458.7</v>
       </c>
       <c r="K83" t="n">
-        <v>-254.98</v>
+        <v>-303.91</v>
       </c>
       <c r="L83" t="n">
-        <v>461.64</v>
+        <v>550.24</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-139.85</v>
+        <v>-163.79</v>
       </c>
       <c r="K84" t="n">
-        <v>-179.41</v>
+        <v>-210.13</v>
       </c>
       <c r="L84" t="n">
-        <v>227.48</v>
+        <v>266.42</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>88.59999999999999</v>
+        <v>103.6</v>
       </c>
       <c r="K85" t="n">
-        <v>-207.49</v>
+        <v>-242.6</v>
       </c>
       <c r="L85" t="n">
-        <v>225.61</v>
+        <v>263.8</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-366.78</v>
+        <v>-448.61</v>
       </c>
       <c r="K86" t="n">
-        <v>109.17</v>
+        <v>133.52</v>
       </c>
       <c r="L86" t="n">
-        <v>382.69</v>
+        <v>468.06</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>94.86</v>
+        <v>114.86</v>
       </c>
       <c r="K87" t="n">
-        <v>234.86</v>
+        <v>284.38</v>
       </c>
       <c r="L87" t="n">
-        <v>253.3</v>
+        <v>306.7</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-152.14</v>
+        <v>-182.11</v>
       </c>
       <c r="K88" t="n">
-        <v>-363.74</v>
+        <v>-435.39</v>
       </c>
       <c r="L88" t="n">
-        <v>394.27</v>
+        <v>471.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="F14" t="n">
-        <v>11.64</v>
+        <v>11.78</v>
       </c>
       <c r="G14" t="n">
-        <v>228.5</v>
+        <v>231.1</v>
       </c>
       <c r="H14" t="n">
-        <v>97.7</v>
+        <v>96</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-181.43</v>
+        <v>-51.77</v>
       </c>
       <c r="K14" t="n">
-        <v>121.11</v>
+        <v>63.44</v>
       </c>
       <c r="L14" t="n">
-        <v>218.14</v>
+        <v>81.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:59:20</t>
+          <t>06:58:51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.63</v>
+        <v>3.88</v>
       </c>
       <c r="F15" t="n">
-        <v>11.59</v>
+        <v>12.19</v>
       </c>
       <c r="G15" t="n">
-        <v>236</v>
+        <v>231.4</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-113.51</v>
+        <v>62.65</v>
       </c>
       <c r="K15" t="n">
-        <v>45.35</v>
+        <v>-2.04</v>
       </c>
       <c r="L15" t="n">
-        <v>122.24</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:00:40</t>
+          <t>06:59:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.14</v>
+        <v>3.86</v>
       </c>
       <c r="F16" t="n">
-        <v>12.14</v>
+        <v>11.77</v>
       </c>
       <c r="G16" t="n">
-        <v>231.1</v>
+        <v>228.3</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>217.8</v>
+        <v>-33.37</v>
       </c>
       <c r="K16" t="n">
-        <v>-80.67</v>
+        <v>53.68</v>
       </c>
       <c r="L16" t="n">
-        <v>232.26</v>
+        <v>63.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:06:06</t>
+          <t>07:04:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.98</v>
+        <v>3.29</v>
       </c>
       <c r="F17" t="n">
-        <v>11.82</v>
+        <v>11.99</v>
       </c>
       <c r="G17" t="n">
-        <v>236.2</v>
+        <v>227.7</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-79.94</v>
+        <v>18.26</v>
       </c>
       <c r="K17" t="n">
-        <v>-207.38</v>
+        <v>2.4</v>
       </c>
       <c r="L17" t="n">
-        <v>222.26</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:08:04</t>
+          <t>07:05:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.09</v>
+        <v>3.47</v>
       </c>
       <c r="F18" t="n">
-        <v>11.42</v>
+        <v>11.3</v>
       </c>
       <c r="G18" t="n">
-        <v>231.3</v>
+        <v>233.4</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-208.83</v>
+        <v>59.29</v>
       </c>
       <c r="K18" t="n">
-        <v>-97.88</v>
+        <v>15.84</v>
       </c>
       <c r="L18" t="n">
-        <v>230.63</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:09:12</t>
+          <t>07:08:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="F19" t="n">
-        <v>13.43</v>
+        <v>11.89</v>
       </c>
       <c r="G19" t="n">
-        <v>222.8</v>
+        <v>237</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>287.44</v>
+        <v>-27.83</v>
       </c>
       <c r="K19" t="n">
-        <v>104.17</v>
+        <v>43.16</v>
       </c>
       <c r="L19" t="n">
-        <v>305.73</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:14:39</t>
+          <t>07:12:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.84</v>
+        <v>3.63</v>
       </c>
       <c r="F20" t="n">
-        <v>11.51</v>
+        <v>12.52</v>
       </c>
       <c r="G20" t="n">
-        <v>236.6</v>
+        <v>237.1</v>
       </c>
       <c r="H20" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>21.63</v>
+        <v>180.5</v>
       </c>
       <c r="K20" t="n">
-        <v>-218.51</v>
+        <v>2.4</v>
       </c>
       <c r="L20" t="n">
-        <v>219.58</v>
+        <v>180.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:15:25</t>
+          <t>07:14:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.05</v>
+        <v>4.31</v>
       </c>
       <c r="F21" t="n">
-        <v>12.24</v>
+        <v>12.19</v>
       </c>
       <c r="G21" t="n">
-        <v>237.9</v>
+        <v>229.9</v>
       </c>
       <c r="H21" t="n">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>176.23</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>232.02</v>
+        <v>90.61</v>
       </c>
       <c r="L21" t="n">
-        <v>291.36</v>
+        <v>121.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:17:33</t>
+          <t>07:16:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="F22" t="n">
-        <v>11.72</v>
+        <v>11.79</v>
       </c>
       <c r="G22" t="n">
-        <v>240.9</v>
+        <v>231.2</v>
       </c>
       <c r="H22" t="n">
-        <v>94.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="I22" t="n">
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-178.89</v>
+        <v>144.48</v>
       </c>
       <c r="K22" t="n">
-        <v>-161.41</v>
+        <v>125.09</v>
       </c>
       <c r="L22" t="n">
-        <v>240.95</v>
+        <v>191.11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:21:39</t>
+          <t>07:20:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.65</v>
+        <v>3.86</v>
       </c>
       <c r="F23" t="n">
-        <v>11.37</v>
+        <v>11.18</v>
       </c>
       <c r="G23" t="n">
-        <v>238.3</v>
+        <v>225.1</v>
       </c>
       <c r="H23" t="n">
-        <v>94.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-22.81</v>
+        <v>127.41</v>
       </c>
       <c r="K23" t="n">
-        <v>356.31</v>
+        <v>89.48</v>
       </c>
       <c r="L23" t="n">
-        <v>357.04</v>
+        <v>155.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:23:43</t>
+          <t>07:21:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.67</v>
+        <v>3.58</v>
       </c>
       <c r="F24" t="n">
-        <v>11.54</v>
+        <v>12.51</v>
       </c>
       <c r="G24" t="n">
-        <v>226.9</v>
+        <v>217.5</v>
       </c>
       <c r="H24" t="n">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>252.62</v>
+        <v>91.42</v>
       </c>
       <c r="K24" t="n">
-        <v>-118.65</v>
+        <v>137.4</v>
       </c>
       <c r="L24" t="n">
-        <v>279.09</v>
+        <v>165.04</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:26:03</t>
+          <t>07:23:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.64</v>
+        <v>3.16</v>
       </c>
       <c r="F25" t="n">
-        <v>11.77</v>
+        <v>12.38</v>
       </c>
       <c r="G25" t="n">
-        <v>242</v>
+        <v>239.7</v>
       </c>
       <c r="H25" t="n">
-        <v>96.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>102.23</v>
+        <v>-60.44</v>
       </c>
       <c r="K25" t="n">
-        <v>299.57</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>316.53</v>
+        <v>106.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:29:35</t>
+          <t>07:28:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="F26" t="n">
-        <v>11.18</v>
+        <v>12.26</v>
       </c>
       <c r="G26" t="n">
-        <v>230.4</v>
+        <v>235</v>
       </c>
       <c r="H26" t="n">
-        <v>91.8</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-139.47</v>
+        <v>1.96</v>
       </c>
       <c r="K26" t="n">
-        <v>221.24</v>
+        <v>260.15</v>
       </c>
       <c r="L26" t="n">
-        <v>261.53</v>
+        <v>260.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:30:21</t>
+          <t>07:30:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="F27" t="n">
-        <v>12.03</v>
+        <v>11.94</v>
       </c>
       <c r="G27" t="n">
-        <v>237.8</v>
+        <v>230.6</v>
       </c>
       <c r="H27" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-488.07</v>
+        <v>-157.39</v>
       </c>
       <c r="K27" t="n">
-        <v>238.26</v>
+        <v>4.27</v>
       </c>
       <c r="L27" t="n">
-        <v>543.12</v>
+        <v>157.44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:32:58</t>
+          <t>07:33:20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.83</v>
+        <v>3.64</v>
       </c>
       <c r="F28" t="n">
-        <v>11.59</v>
+        <v>12.45</v>
       </c>
       <c r="G28" t="n">
-        <v>234.6</v>
+        <v>239</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>183.3</v>
+        <v>-180.32</v>
       </c>
       <c r="K28" t="n">
-        <v>-346.88</v>
+        <v>-144.32</v>
       </c>
       <c r="L28" t="n">
-        <v>392.33</v>
+        <v>230.96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:46:13</t>
+          <t>07:43:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.23</v>
+        <v>4.01</v>
       </c>
       <c r="F29" t="n">
-        <v>11.53</v>
+        <v>12.06</v>
       </c>
       <c r="G29" t="n">
-        <v>233.2</v>
+        <v>242.4</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>68.34999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="K29" t="n">
-        <v>75.8</v>
+        <v>-65.42</v>
       </c>
       <c r="L29" t="n">
-        <v>102.07</v>
+        <v>65.93000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:48:41</t>
+          <t>07:44:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.42</v>
+        <v>3.86</v>
       </c>
       <c r="F30" t="n">
-        <v>11.94</v>
+        <v>11.66</v>
       </c>
       <c r="G30" t="n">
-        <v>229.2</v>
+        <v>234.5</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>129.12</v>
+        <v>-49.69</v>
       </c>
       <c r="K30" t="n">
-        <v>-135.24</v>
+        <v>23.72</v>
       </c>
       <c r="L30" t="n">
-        <v>186.98</v>
+        <v>55.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:49:59</t>
+          <t>07:46:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="F31" t="n">
-        <v>11.26</v>
+        <v>12.26</v>
       </c>
       <c r="G31" t="n">
-        <v>221.4</v>
+        <v>239.7</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>31.96</v>
+        <v>-72.91</v>
       </c>
       <c r="K31" t="n">
-        <v>-94.64</v>
+        <v>6.2</v>
       </c>
       <c r="L31" t="n">
-        <v>99.89</v>
+        <v>73.17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:54:51</t>
+          <t>07:50:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.9</v>
+        <v>4.68</v>
       </c>
       <c r="F32" t="n">
-        <v>11.95</v>
+        <v>12.28</v>
       </c>
       <c r="G32" t="n">
-        <v>226.1</v>
+        <v>235.2</v>
       </c>
       <c r="H32" t="n">
-        <v>99.8</v>
+        <v>97.7</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-60.61</v>
+        <v>36.47</v>
       </c>
       <c r="K32" t="n">
-        <v>156.74</v>
+        <v>97.84</v>
       </c>
       <c r="L32" t="n">
-        <v>168.05</v>
+        <v>104.41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:55:56</t>
+          <t>07:51:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.45</v>
+        <v>3.55</v>
       </c>
       <c r="F33" t="n">
-        <v>12.38</v>
+        <v>12.27</v>
       </c>
       <c r="G33" t="n">
-        <v>222.3</v>
+        <v>237.3</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-148.04</v>
+        <v>20.07</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.22</v>
+        <v>-132</v>
       </c>
       <c r="L33" t="n">
-        <v>148.21</v>
+        <v>133.52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:57:38</t>
+          <t>07:53:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="F34" t="n">
-        <v>11.67</v>
+        <v>11.76</v>
       </c>
       <c r="G34" t="n">
-        <v>243.4</v>
+        <v>216.2</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>18.55</v>
+        <v>27.09</v>
       </c>
       <c r="K34" t="n">
-        <v>153.25</v>
+        <v>105.63</v>
       </c>
       <c r="L34" t="n">
-        <v>154.37</v>
+        <v>109.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:02:34</t>
+          <t>07:57:44</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.85</v>
+        <v>4.03</v>
       </c>
       <c r="F35" t="n">
-        <v>11.51</v>
+        <v>12.14</v>
       </c>
       <c r="G35" t="n">
-        <v>255.2</v>
+        <v>224.3</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-186.2</v>
+        <v>101.36</v>
       </c>
       <c r="K35" t="n">
-        <v>-112.06</v>
+        <v>70.16</v>
       </c>
       <c r="L35" t="n">
-        <v>217.32</v>
+        <v>123.27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:04:57</t>
+          <t>08:00:29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.73</v>
+        <v>4.22</v>
       </c>
       <c r="F36" t="n">
-        <v>11.84</v>
+        <v>11.64</v>
       </c>
       <c r="G36" t="n">
-        <v>236.6</v>
+        <v>239.5</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>94.7</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-29.95</v>
+        <v>142.33</v>
       </c>
       <c r="K36" t="n">
-        <v>-238.38</v>
+        <v>-24.46</v>
       </c>
       <c r="L36" t="n">
-        <v>240.25</v>
+        <v>144.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:05:32</t>
+          <t>08:02:49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.13</v>
+        <v>4.66</v>
       </c>
       <c r="F37" t="n">
-        <v>12.13</v>
+        <v>11.56</v>
       </c>
       <c r="G37" t="n">
-        <v>229.9</v>
+        <v>229.1</v>
       </c>
       <c r="H37" t="n">
-        <v>95.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-303.01</v>
+        <v>-43.1</v>
       </c>
       <c r="K37" t="n">
-        <v>118.35</v>
+        <v>84.05</v>
       </c>
       <c r="L37" t="n">
-        <v>325.3</v>
+        <v>94.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:09:01</t>
+          <t>08:07:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.36</v>
+        <v>4.16</v>
       </c>
       <c r="F38" t="n">
-        <v>11.97</v>
+        <v>11.71</v>
       </c>
       <c r="G38" t="n">
-        <v>234</v>
+        <v>219.3</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>247.11</v>
+        <v>-124.2</v>
       </c>
       <c r="K38" t="n">
-        <v>-105</v>
+        <v>18.17</v>
       </c>
       <c r="L38" t="n">
-        <v>268.49</v>
+        <v>125.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:10:25</t>
+          <t>08:10:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.92</v>
+        <v>4.94</v>
       </c>
       <c r="F39" t="n">
-        <v>11.14</v>
+        <v>11.92</v>
       </c>
       <c r="G39" t="n">
-        <v>237.1</v>
+        <v>239.4</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-24.11</v>
+        <v>58.64</v>
       </c>
       <c r="K39" t="n">
-        <v>315.88</v>
+        <v>20.08</v>
       </c>
       <c r="L39" t="n">
-        <v>316.8</v>
+        <v>61.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:11:45</t>
+          <t>08:12:39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.57</v>
+        <v>3.95</v>
       </c>
       <c r="F40" t="n">
-        <v>11.65</v>
+        <v>10.99</v>
       </c>
       <c r="G40" t="n">
-        <v>227.2</v>
+        <v>236.3</v>
       </c>
       <c r="H40" t="n">
-        <v>90.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>12.72</v>
+        <v>-116.69</v>
       </c>
       <c r="K40" t="n">
-        <v>403.35</v>
+        <v>137.88</v>
       </c>
       <c r="L40" t="n">
-        <v>403.55</v>
+        <v>180.63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:16:31</t>
+          <t>08:16:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.48</v>
+        <v>4.24</v>
       </c>
       <c r="F41" t="n">
-        <v>12.12</v>
+        <v>12.1</v>
       </c>
       <c r="G41" t="n">
-        <v>232.9</v>
+        <v>243.2</v>
       </c>
       <c r="H41" t="n">
-        <v>94.8</v>
+        <v>95.2</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-308.93</v>
+        <v>-225.02</v>
       </c>
       <c r="K41" t="n">
-        <v>-91.3</v>
+        <v>-87.88</v>
       </c>
       <c r="L41" t="n">
-        <v>322.14</v>
+        <v>241.57</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:17:17</t>
+          <t>08:18:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.82</v>
+        <v>4.16</v>
       </c>
       <c r="F42" t="n">
-        <v>11.68</v>
+        <v>11.72</v>
       </c>
       <c r="G42" t="n">
-        <v>238</v>
+        <v>229.1</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>154.66</v>
+        <v>132.54</v>
       </c>
       <c r="K42" t="n">
-        <v>-296.85</v>
+        <v>-40.9</v>
       </c>
       <c r="L42" t="n">
-        <v>334.72</v>
+        <v>138.71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:19:25</t>
+          <t>08:20:16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.96</v>
+        <v>4.36</v>
       </c>
       <c r="F43" t="n">
-        <v>12.11</v>
+        <v>11.66</v>
       </c>
       <c r="G43" t="n">
-        <v>235.4</v>
+        <v>211.8</v>
       </c>
       <c r="H43" t="n">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-81.78</v>
+        <v>1.5</v>
       </c>
       <c r="K43" t="n">
-        <v>257.15</v>
+        <v>-195.53</v>
       </c>
       <c r="L43" t="n">
-        <v>269.84</v>
+        <v>195.53</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:30:37</t>
+          <t>08:30:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.93</v>
+        <v>4.46</v>
       </c>
       <c r="F44" t="n">
-        <v>11.57</v>
+        <v>11.29</v>
       </c>
       <c r="G44" t="n">
-        <v>247.6</v>
+        <v>235.6</v>
       </c>
       <c r="H44" t="n">
-        <v>95.59999999999999</v>
+        <v>93</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-149.76</v>
+        <v>-30.29</v>
       </c>
       <c r="K44" t="n">
-        <v>147.38</v>
+        <v>-50.48</v>
       </c>
       <c r="L44" t="n">
-        <v>210.12</v>
+        <v>58.87</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:32:34</t>
+          <t>08:31:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.15</v>
+        <v>3.61</v>
       </c>
       <c r="F45" t="n">
-        <v>11.74</v>
+        <v>12.19</v>
       </c>
       <c r="G45" t="n">
-        <v>237.3</v>
+        <v>235.3</v>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>152.24</v>
+        <v>-72.04000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-81.61</v>
+        <v>-7.53</v>
       </c>
       <c r="L45" t="n">
-        <v>172.74</v>
+        <v>72.43000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:35:08</t>
+          <t>08:33:52</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.95</v>
+        <v>4.53</v>
       </c>
       <c r="F46" t="n">
-        <v>11.19</v>
+        <v>11.63</v>
       </c>
       <c r="G46" t="n">
-        <v>233.5</v>
+        <v>236.4</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-122.48</v>
+        <v>-43.99</v>
       </c>
       <c r="K46" t="n">
-        <v>49.02</v>
+        <v>37.98</v>
       </c>
       <c r="L46" t="n">
-        <v>131.92</v>
+        <v>58.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:38:30</t>
+          <t>08:37:08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.14</v>
+        <v>4.54</v>
       </c>
       <c r="F47" t="n">
-        <v>11.78</v>
+        <v>11.26</v>
       </c>
       <c r="G47" t="n">
-        <v>233.1</v>
+        <v>232.4</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-239.91</v>
+        <v>-84.33</v>
       </c>
       <c r="K47" t="n">
-        <v>30.22</v>
+        <v>-41.26</v>
       </c>
       <c r="L47" t="n">
-        <v>241.81</v>
+        <v>93.88</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:40:23</t>
+          <t>08:38:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.19</v>
+        <v>4.52</v>
       </c>
       <c r="F48" t="n">
-        <v>11.82</v>
+        <v>10.98</v>
       </c>
       <c r="G48" t="n">
-        <v>218.3</v>
+        <v>232.4</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-31.53</v>
+        <v>-119.42</v>
       </c>
       <c r="K48" t="n">
-        <v>-214</v>
+        <v>-38.62</v>
       </c>
       <c r="L48" t="n">
-        <v>216.31</v>
+        <v>125.51</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:41:49</t>
+          <t>08:40:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.05</v>
+        <v>4.27</v>
       </c>
       <c r="F49" t="n">
-        <v>11.54</v>
+        <v>12.61</v>
       </c>
       <c r="G49" t="n">
-        <v>233.8</v>
+        <v>245.5</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-73.5</v>
+        <v>-25.01</v>
       </c>
       <c r="K49" t="n">
-        <v>189.62</v>
+        <v>-30.7</v>
       </c>
       <c r="L49" t="n">
-        <v>203.37</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:46:23</t>
+          <t>08:44:54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.22</v>
+        <v>4.09</v>
       </c>
       <c r="F50" t="n">
-        <v>11.37</v>
+        <v>11.73</v>
       </c>
       <c r="G50" t="n">
-        <v>234.5</v>
+        <v>213.9</v>
       </c>
       <c r="H50" t="n">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-134.39</v>
+        <v>58.9</v>
       </c>
       <c r="K50" t="n">
-        <v>-134.03</v>
+        <v>57.72</v>
       </c>
       <c r="L50" t="n">
-        <v>189.8</v>
+        <v>82.45999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:47:41</t>
+          <t>08:45:45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.31</v>
+        <v>3.72</v>
       </c>
       <c r="F51" t="n">
-        <v>11.32</v>
+        <v>11.98</v>
       </c>
       <c r="G51" t="n">
-        <v>237.4</v>
+        <v>228.6</v>
       </c>
       <c r="H51" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-80.93000000000001</v>
+        <v>-101.63</v>
       </c>
       <c r="K51" t="n">
-        <v>148.38</v>
+        <v>60.84</v>
       </c>
       <c r="L51" t="n">
-        <v>169.01</v>
+        <v>118.45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:49:58</t>
+          <t>08:47:06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.65</v>
+        <v>4.74</v>
       </c>
       <c r="F52" t="n">
-        <v>11.78</v>
+        <v>11.88</v>
       </c>
       <c r="G52" t="n">
-        <v>225.5</v>
+        <v>226.8</v>
       </c>
       <c r="H52" t="n">
-        <v>94.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-25.72</v>
+        <v>121.16</v>
       </c>
       <c r="K52" t="n">
-        <v>-180.27</v>
+        <v>-55.06</v>
       </c>
       <c r="L52" t="n">
-        <v>182.1</v>
+        <v>133.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:55:28</t>
+          <t>08:51:24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.43</v>
+        <v>4.48</v>
       </c>
       <c r="F53" t="n">
-        <v>11.88</v>
+        <v>11.53</v>
       </c>
       <c r="G53" t="n">
-        <v>229.4</v>
+        <v>220.4</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-84.76000000000001</v>
+        <v>-96.52</v>
       </c>
       <c r="K53" t="n">
-        <v>185.89</v>
+        <v>113.81</v>
       </c>
       <c r="L53" t="n">
-        <v>204.3</v>
+        <v>149.23</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:57:47</t>
+          <t>08:52:39</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.07</v>
+        <v>4.13</v>
       </c>
       <c r="F54" t="n">
-        <v>12.16</v>
+        <v>12.1</v>
       </c>
       <c r="G54" t="n">
-        <v>230.5</v>
+        <v>232.9</v>
       </c>
       <c r="H54" t="n">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>133.19</v>
+        <v>-26.55</v>
       </c>
       <c r="K54" t="n">
-        <v>-650</v>
+        <v>-125.47</v>
       </c>
       <c r="L54" t="n">
-        <v>663.5</v>
+        <v>128.25</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:59:25</t>
+          <t>08:55:03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.64</v>
+        <v>4.32</v>
       </c>
       <c r="F55" t="n">
-        <v>11.63</v>
+        <v>11.87</v>
       </c>
       <c r="G55" t="n">
-        <v>223.9</v>
+        <v>234.9</v>
       </c>
       <c r="H55" t="n">
-        <v>99.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-318.81</v>
+        <v>-155.88</v>
       </c>
       <c r="K55" t="n">
-        <v>-173.22</v>
+        <v>46.86</v>
       </c>
       <c r="L55" t="n">
-        <v>362.83</v>
+        <v>162.78</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:03:17</t>
+          <t>09:00:02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.54</v>
+        <v>3.81</v>
       </c>
       <c r="F56" t="n">
-        <v>12.18</v>
+        <v>11.62</v>
       </c>
       <c r="G56" t="n">
-        <v>241.7</v>
+        <v>226.3</v>
       </c>
       <c r="H56" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>484.79</v>
+        <v>-157.49</v>
       </c>
       <c r="K56" t="n">
-        <v>356.72</v>
+        <v>20.61</v>
       </c>
       <c r="L56" t="n">
-        <v>601.89</v>
+        <v>158.83</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:04:41</t>
+          <t>09:01:13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2434,31 +2434,31 @@
         <v>4.48</v>
       </c>
       <c r="F57" t="n">
-        <v>12.44</v>
+        <v>11.85</v>
       </c>
       <c r="G57" t="n">
-        <v>231.6</v>
+        <v>235.7</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-383.97</v>
+        <v>-56.39</v>
       </c>
       <c r="K57" t="n">
-        <v>142.44</v>
+        <v>245.55</v>
       </c>
       <c r="L57" t="n">
-        <v>409.54</v>
+        <v>251.95</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:05:41</t>
+          <t>09:03:23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
       <c r="F58" t="n">
-        <v>12.26</v>
+        <v>11.98</v>
       </c>
       <c r="G58" t="n">
-        <v>231.8</v>
+        <v>220.7</v>
       </c>
       <c r="H58" t="n">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-178.85</v>
+        <v>-195.96</v>
       </c>
       <c r="K58" t="n">
-        <v>-289.63</v>
+        <v>-99.90000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>340.4</v>
+        <v>219.95</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:16:08</t>
+          <t>09:15:54</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.58</v>
+        <v>4.51</v>
       </c>
       <c r="F59" t="n">
-        <v>11.73</v>
+        <v>11.55</v>
       </c>
       <c r="G59" t="n">
-        <v>234.3</v>
+        <v>242.1</v>
       </c>
       <c r="H59" t="n">
-        <v>97.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>191.75</v>
+        <v>44.48</v>
       </c>
       <c r="K59" t="n">
-        <v>-163.91</v>
+        <v>-6.11</v>
       </c>
       <c r="L59" t="n">
-        <v>252.26</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:18:00</t>
+          <t>09:17:56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.58</v>
+        <v>4.93</v>
       </c>
       <c r="F60" t="n">
-        <v>11.29</v>
+        <v>11.97</v>
       </c>
       <c r="G60" t="n">
-        <v>234.5</v>
+        <v>227.9</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-210.69</v>
+        <v>-72.18000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>-92.54000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="L60" t="n">
-        <v>230.12</v>
+        <v>100.34</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:19:02</t>
+          <t>09:19:17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="F61" t="n">
-        <v>12.12</v>
+        <v>11.48</v>
       </c>
       <c r="G61" t="n">
-        <v>238.4</v>
+        <v>238.8</v>
       </c>
       <c r="H61" t="n">
-        <v>98.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="I61" t="n">
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-88.7</v>
+        <v>-50.07</v>
       </c>
       <c r="K61" t="n">
-        <v>208.82</v>
+        <v>-27.02</v>
       </c>
       <c r="L61" t="n">
-        <v>226.88</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:23:29</t>
+          <t>09:23:33</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.06</v>
+        <v>3.79</v>
       </c>
       <c r="F62" t="n">
-        <v>11.69</v>
+        <v>11.55</v>
       </c>
       <c r="G62" t="n">
-        <v>228.3</v>
+        <v>250.5</v>
       </c>
       <c r="H62" t="n">
-        <v>96</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>57.13</v>
+        <v>-3.85</v>
       </c>
       <c r="K62" t="n">
-        <v>175.37</v>
+        <v>-55.62</v>
       </c>
       <c r="L62" t="n">
-        <v>184.44</v>
+        <v>55.75</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:25:19</t>
+          <t>09:25:10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="F63" t="n">
-        <v>11.73</v>
+        <v>12.06</v>
       </c>
       <c r="G63" t="n">
-        <v>245.2</v>
+        <v>251</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-185.22</v>
+        <v>-23.09</v>
       </c>
       <c r="K63" t="n">
-        <v>215.81</v>
+        <v>-88.23</v>
       </c>
       <c r="L63" t="n">
-        <v>284.39</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:27:09</t>
+          <t>09:26:03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.99</v>
+        <v>4.38</v>
       </c>
       <c r="F64" t="n">
-        <v>11.6</v>
+        <v>11.13</v>
       </c>
       <c r="G64" t="n">
-        <v>224.9</v>
+        <v>229.8</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-338.77</v>
+        <v>-23.65</v>
       </c>
       <c r="K64" t="n">
-        <v>-14.76</v>
+        <v>-47.42</v>
       </c>
       <c r="L64" t="n">
-        <v>339.1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:31:11</t>
+          <t>09:30:21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.22</v>
+        <v>4.08</v>
       </c>
       <c r="F65" t="n">
-        <v>12.6</v>
+        <v>11.61</v>
       </c>
       <c r="G65" t="n">
-        <v>239.6</v>
+        <v>235.1</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>93.7</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>372.27</v>
+        <v>-80.88</v>
       </c>
       <c r="K65" t="n">
-        <v>-266.39</v>
+        <v>10.47</v>
       </c>
       <c r="L65" t="n">
-        <v>457.77</v>
+        <v>81.56</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:32:14</t>
+          <t>09:32:26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.79</v>
+        <v>4.54</v>
       </c>
       <c r="F66" t="n">
-        <v>11.29</v>
+        <v>11.33</v>
       </c>
       <c r="G66" t="n">
-        <v>205.9</v>
+        <v>241</v>
       </c>
       <c r="H66" t="n">
-        <v>95.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>139.41</v>
+        <v>-141.03</v>
       </c>
       <c r="K66" t="n">
-        <v>-183.95</v>
+        <v>-18.94</v>
       </c>
       <c r="L66" t="n">
-        <v>230.81</v>
+        <v>142.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:33:46</t>
+          <t>09:33:10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.51</v>
+        <v>4.85</v>
       </c>
       <c r="F67" t="n">
-        <v>12.13</v>
+        <v>11.52</v>
       </c>
       <c r="G67" t="n">
-        <v>228.7</v>
+        <v>241.1</v>
       </c>
       <c r="H67" t="n">
-        <v>98.2</v>
+        <v>97.3</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-282.91</v>
+        <v>3.35</v>
       </c>
       <c r="K67" t="n">
-        <v>33.07</v>
+        <v>104.14</v>
       </c>
       <c r="L67" t="n">
-        <v>284.83</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:39:22</t>
+          <t>09:36:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.99</v>
+        <v>4.32</v>
       </c>
       <c r="F68" t="n">
-        <v>11.67</v>
+        <v>11.46</v>
       </c>
       <c r="G68" t="n">
-        <v>249.9</v>
+        <v>236.5</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-267.37</v>
+        <v>-63.39</v>
       </c>
       <c r="K68" t="n">
-        <v>-96.92</v>
+        <v>69.77</v>
       </c>
       <c r="L68" t="n">
-        <v>284.39</v>
+        <v>94.27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:40:51</t>
+          <t>09:38:09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.17</v>
+        <v>4.22</v>
       </c>
       <c r="F69" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="G69" t="n">
-        <v>228</v>
+        <v>241.4</v>
       </c>
       <c r="H69" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>401.51</v>
+        <v>-64.54000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>35.36</v>
+        <v>143.47</v>
       </c>
       <c r="L69" t="n">
-        <v>403.06</v>
+        <v>157.32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:43:16</t>
+          <t>09:40:31</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="F70" t="n">
-        <v>11.69</v>
+        <v>12.11</v>
       </c>
       <c r="G70" t="n">
-        <v>240.9</v>
+        <v>228.3</v>
       </c>
       <c r="H70" t="n">
-        <v>99.7</v>
+        <v>96.8</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>116.46</v>
+        <v>-172.06</v>
       </c>
       <c r="K70" t="n">
-        <v>-155.59</v>
+        <v>127.69</v>
       </c>
       <c r="L70" t="n">
-        <v>194.34</v>
+        <v>214.27</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:48:41</t>
+          <t>09:46:12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.91</v>
+        <v>4.19</v>
       </c>
       <c r="F71" t="n">
-        <v>11.71</v>
+        <v>11.01</v>
       </c>
       <c r="G71" t="n">
-        <v>234.1</v>
+        <v>221.7</v>
       </c>
       <c r="H71" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>250.91</v>
+        <v>-135.87</v>
       </c>
       <c r="K71" t="n">
-        <v>-211.48</v>
+        <v>215.68</v>
       </c>
       <c r="L71" t="n">
-        <v>328.15</v>
+        <v>254.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:49:44</t>
+          <t>09:47:08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="F72" t="n">
-        <v>11.74</v>
+        <v>11.44</v>
       </c>
       <c r="G72" t="n">
-        <v>234.2</v>
+        <v>246.3</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-418.88</v>
+        <v>-299.53</v>
       </c>
       <c r="K72" t="n">
-        <v>68.26000000000001</v>
+        <v>121.72</v>
       </c>
       <c r="L72" t="n">
-        <v>424.41</v>
+        <v>323.32</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:51:33</t>
+          <t>09:49:50</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.65</v>
+        <v>4.99</v>
       </c>
       <c r="F73" t="n">
-        <v>11.9</v>
+        <v>11.53</v>
       </c>
       <c r="G73" t="n">
-        <v>244.7</v>
+        <v>233.1</v>
       </c>
       <c r="H73" t="n">
-        <v>94.8</v>
+        <v>92.5</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-130.4</v>
+        <v>-152.59</v>
       </c>
       <c r="K73" t="n">
-        <v>-345.03</v>
+        <v>-145.83</v>
       </c>
       <c r="L73" t="n">
-        <v>368.85</v>
+        <v>211.06</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:01:29</t>
+          <t>09:58:07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.44</v>
+        <v>5.42</v>
       </c>
       <c r="F74" t="n">
-        <v>11.86</v>
+        <v>11.36</v>
       </c>
       <c r="G74" t="n">
-        <v>237.8</v>
+        <v>229.7</v>
       </c>
       <c r="H74" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>65.51000000000001</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-111.7</v>
+        <v>-75.81</v>
       </c>
       <c r="L74" t="n">
-        <v>129.5</v>
+        <v>113.47</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:03:16</t>
+          <t>10:00:34</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.49</v>
+        <v>4.41</v>
       </c>
       <c r="F75" t="n">
-        <v>11.5</v>
+        <v>11.65</v>
       </c>
       <c r="G75" t="n">
-        <v>211.5</v>
+        <v>230.9</v>
       </c>
       <c r="H75" t="n">
         <v>100</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-159.12</v>
+        <v>-52.46</v>
       </c>
       <c r="K75" t="n">
-        <v>-167.36</v>
+        <v>79.63</v>
       </c>
       <c r="L75" t="n">
-        <v>230.93</v>
+        <v>95.36</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:04:09</t>
+          <t>10:01:49</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.46</v>
+        <v>4.79</v>
       </c>
       <c r="F76" t="n">
-        <v>11.62</v>
+        <v>11.81</v>
       </c>
       <c r="G76" t="n">
-        <v>230.9</v>
+        <v>231.6</v>
       </c>
       <c r="H76" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>95.13</v>
+        <v>76.03</v>
       </c>
       <c r="K76" t="n">
-        <v>82.79000000000001</v>
+        <v>-39.17</v>
       </c>
       <c r="L76" t="n">
-        <v>126.11</v>
+        <v>85.53</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:08:36</t>
+          <t>10:07:48</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.97</v>
+        <v>4.57</v>
       </c>
       <c r="F77" t="n">
-        <v>11.11</v>
+        <v>12.11</v>
       </c>
       <c r="G77" t="n">
-        <v>240.7</v>
+        <v>247.8</v>
       </c>
       <c r="H77" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>35.23</v>
+        <v>111.29</v>
       </c>
       <c r="K77" t="n">
-        <v>300</v>
+        <v>27.04</v>
       </c>
       <c r="L77" t="n">
-        <v>302.06</v>
+        <v>114.53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:10:42</t>
+          <t>10:10:03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.41</v>
+        <v>4.94</v>
       </c>
       <c r="F78" t="n">
-        <v>12.23</v>
+        <v>12.13</v>
       </c>
       <c r="G78" t="n">
-        <v>229.1</v>
+        <v>232.7</v>
       </c>
       <c r="H78" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="I78" t="n">
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-69.77</v>
+        <v>31.44</v>
       </c>
       <c r="K78" t="n">
-        <v>110.79</v>
+        <v>-75.44</v>
       </c>
       <c r="L78" t="n">
-        <v>130.93</v>
+        <v>81.73</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:11:30</t>
+          <t>10:12:26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.58</v>
+        <v>4.83</v>
       </c>
       <c r="F79" t="n">
-        <v>11.75</v>
+        <v>10.87</v>
       </c>
       <c r="G79" t="n">
-        <v>231.8</v>
+        <v>241</v>
       </c>
       <c r="H79" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-118.82</v>
+        <v>22.75</v>
       </c>
       <c r="K79" t="n">
-        <v>110.56</v>
+        <v>-121.72</v>
       </c>
       <c r="L79" t="n">
-        <v>162.31</v>
+        <v>123.83</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:16:06</t>
+          <t>10:17:55</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.74</v>
+        <v>4.55</v>
       </c>
       <c r="F80" t="n">
-        <v>11.75</v>
+        <v>12.33</v>
       </c>
       <c r="G80" t="n">
-        <v>236.4</v>
+        <v>226</v>
       </c>
       <c r="H80" t="n">
-        <v>98</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>331.78</v>
+        <v>22.81</v>
       </c>
       <c r="K80" t="n">
-        <v>-182.64</v>
+        <v>129.73</v>
       </c>
       <c r="L80" t="n">
-        <v>378.73</v>
+        <v>131.72</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:17:27</t>
+          <t>10:19:50</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.47</v>
+        <v>4.65</v>
       </c>
       <c r="F81" t="n">
-        <v>12.01</v>
+        <v>11.65</v>
       </c>
       <c r="G81" t="n">
-        <v>245.9</v>
+        <v>233.7</v>
       </c>
       <c r="H81" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-238.46</v>
+        <v>-32.39</v>
       </c>
       <c r="K81" t="n">
-        <v>-36.74</v>
+        <v>-102.1</v>
       </c>
       <c r="L81" t="n">
-        <v>241.27</v>
+        <v>107.11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:19:27</t>
+          <t>10:22:04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.68</v>
+        <v>4.35</v>
       </c>
       <c r="F82" t="n">
-        <v>11.72</v>
+        <v>11.3</v>
       </c>
       <c r="G82" t="n">
-        <v>251.7</v>
+        <v>225.8</v>
       </c>
       <c r="H82" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-318.03</v>
+        <v>19.55</v>
       </c>
       <c r="K82" t="n">
-        <v>-102.17</v>
+        <v>90.2</v>
       </c>
       <c r="L82" t="n">
-        <v>334.04</v>
+        <v>92.29000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:24:01</t>
+          <t>10:27:37</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.41</v>
+        <v>5.77</v>
       </c>
       <c r="F83" t="n">
-        <v>12.06</v>
+        <v>11.51</v>
       </c>
       <c r="G83" t="n">
-        <v>241.1</v>
+        <v>237.3</v>
       </c>
       <c r="H83" t="n">
         <v>100</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-458.7</v>
+        <v>204.2</v>
       </c>
       <c r="K83" t="n">
-        <v>-303.91</v>
+        <v>1.79</v>
       </c>
       <c r="L83" t="n">
-        <v>550.24</v>
+        <v>204.21</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:26:05</t>
+          <t>10:28:54</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.08</v>
+        <v>5.08</v>
       </c>
       <c r="F84" t="n">
-        <v>11.91</v>
+        <v>12.06</v>
       </c>
       <c r="G84" t="n">
-        <v>229.6</v>
+        <v>222.8</v>
       </c>
       <c r="H84" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-163.79</v>
+        <v>-86.65000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>-210.13</v>
+        <v>231.11</v>
       </c>
       <c r="L84" t="n">
-        <v>266.42</v>
+        <v>246.82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:28:05</t>
+          <t>10:30:13</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.67</v>
+        <v>4.94</v>
       </c>
       <c r="F85" t="n">
-        <v>11.97</v>
+        <v>10.9</v>
       </c>
       <c r="G85" t="n">
-        <v>235.9</v>
+        <v>241.6</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>103.6</v>
+        <v>-133.38</v>
       </c>
       <c r="K85" t="n">
-        <v>-242.6</v>
+        <v>-138.84</v>
       </c>
       <c r="L85" t="n">
-        <v>263.8</v>
+        <v>192.53</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:32:02</t>
+          <t>10:35:11</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.86</v>
+        <v>4.53</v>
       </c>
       <c r="F86" t="n">
-        <v>12.05</v>
+        <v>12.23</v>
       </c>
       <c r="G86" t="n">
-        <v>230.1</v>
+        <v>235.8</v>
       </c>
       <c r="H86" t="n">
-        <v>96.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-448.61</v>
+        <v>3.9</v>
       </c>
       <c r="K86" t="n">
-        <v>133.52</v>
+        <v>146.32</v>
       </c>
       <c r="L86" t="n">
-        <v>468.06</v>
+        <v>146.38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:34:16</t>
+          <t>10:36:21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.54</v>
+        <v>4.87</v>
       </c>
       <c r="F87" t="n">
-        <v>11.8</v>
+        <v>11.04</v>
       </c>
       <c r="G87" t="n">
-        <v>227.2</v>
+        <v>236.5</v>
       </c>
       <c r="H87" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>114.86</v>
+        <v>-31.8</v>
       </c>
       <c r="K87" t="n">
-        <v>284.38</v>
+        <v>-269.92</v>
       </c>
       <c r="L87" t="n">
-        <v>306.7</v>
+        <v>271.78</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:35:53</t>
+          <t>10:37:22</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.49</v>
+        <v>4.61</v>
       </c>
       <c r="F88" t="n">
-        <v>11.82</v>
+        <v>11.4</v>
       </c>
       <c r="G88" t="n">
-        <v>227.6</v>
+        <v>235.7</v>
       </c>
       <c r="H88" t="n">
-        <v>91.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="I88" t="n">
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-182.11</v>
+        <v>92.83</v>
       </c>
       <c r="K88" t="n">
-        <v>-435.39</v>
+        <v>226.84</v>
       </c>
       <c r="L88" t="n">
-        <v>471.94</v>
+        <v>245.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-51.77</v>
+        <v>-49.8</v>
       </c>
       <c r="K14" t="n">
-        <v>63.44</v>
+        <v>61.03</v>
       </c>
       <c r="L14" t="n">
-        <v>81.88</v>
+        <v>78.77</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>62.65</v>
+        <v>62.54</v>
       </c>
       <c r="K15" t="n">
         <v>-2.04</v>
       </c>
       <c r="L15" t="n">
-        <v>62.69</v>
+        <v>62.57</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-33.37</v>
+        <v>-33.47</v>
       </c>
       <c r="K16" t="n">
-        <v>53.68</v>
+        <v>53.84</v>
       </c>
       <c r="L16" t="n">
-        <v>63.21</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>18.26</v>
+        <v>17.87</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="L17" t="n">
-        <v>18.42</v>
+        <v>18.03</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>59.29</v>
+        <v>60.45</v>
       </c>
       <c r="K18" t="n">
-        <v>15.84</v>
+        <v>16.15</v>
       </c>
       <c r="L18" t="n">
-        <v>61.37</v>
+        <v>62.57</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-27.83</v>
+        <v>-29.85</v>
       </c>
       <c r="K19" t="n">
-        <v>43.16</v>
+        <v>46.3</v>
       </c>
       <c r="L19" t="n">
-        <v>51.35</v>
+        <v>55.09</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>180.5</v>
+        <v>172.4</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="L20" t="n">
-        <v>180.52</v>
+        <v>172.42</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>81.26000000000001</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>90.61</v>
+        <v>90.27</v>
       </c>
       <c r="L21" t="n">
-        <v>121.71</v>
+        <v>121.26</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>144.48</v>
+        <v>130.78</v>
       </c>
       <c r="K22" t="n">
-        <v>125.09</v>
+        <v>113.23</v>
       </c>
       <c r="L22" t="n">
-        <v>191.11</v>
+        <v>172.98</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>127.41</v>
+        <v>129.08</v>
       </c>
       <c r="K23" t="n">
-        <v>89.48</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>155.7</v>
+        <v>157.73</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>91.42</v>
+        <v>91.34</v>
       </c>
       <c r="K24" t="n">
-        <v>137.4</v>
+        <v>137.28</v>
       </c>
       <c r="L24" t="n">
-        <v>165.04</v>
+        <v>164.9</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-60.44</v>
+        <v>-63.39</v>
       </c>
       <c r="K25" t="n">
-        <v>87.15000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>106.06</v>
+        <v>111.23</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="K26" t="n">
-        <v>260.15</v>
+        <v>255.44</v>
       </c>
       <c r="L26" t="n">
-        <v>260.16</v>
+        <v>255.44</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-157.39</v>
+        <v>-167.18</v>
       </c>
       <c r="K27" t="n">
-        <v>4.27</v>
+        <v>4.53</v>
       </c>
       <c r="L27" t="n">
-        <v>157.44</v>
+        <v>167.24</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-180.32</v>
+        <v>-181.87</v>
       </c>
       <c r="K28" t="n">
-        <v>-144.32</v>
+        <v>-145.56</v>
       </c>
       <c r="L28" t="n">
-        <v>230.96</v>
+        <v>232.95</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>8.23</v>
+        <v>8.08</v>
       </c>
       <c r="K29" t="n">
-        <v>-65.42</v>
+        <v>-64.25</v>
       </c>
       <c r="L29" t="n">
-        <v>65.93000000000001</v>
+        <v>64.76000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-49.69</v>
+        <v>-49.91</v>
       </c>
       <c r="K30" t="n">
-        <v>23.72</v>
+        <v>23.83</v>
       </c>
       <c r="L30" t="n">
-        <v>55.06</v>
+        <v>55.31</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-72.91</v>
+        <v>-70.54000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>73.17</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>36.47</v>
+        <v>34.41</v>
       </c>
       <c r="K32" t="n">
-        <v>97.84</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>104.41</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>20.07</v>
+        <v>18.87</v>
       </c>
       <c r="K33" t="n">
-        <v>-132</v>
+        <v>-124.09</v>
       </c>
       <c r="L33" t="n">
-        <v>133.52</v>
+        <v>125.52</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>27.09</v>
+        <v>25.21</v>
       </c>
       <c r="K34" t="n">
-        <v>105.63</v>
+        <v>98.28</v>
       </c>
       <c r="L34" t="n">
-        <v>109.04</v>
+        <v>101.46</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>101.36</v>
+        <v>100.36</v>
       </c>
       <c r="K35" t="n">
-        <v>70.16</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>123.27</v>
+        <v>122.05</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>142.33</v>
+        <v>138.87</v>
       </c>
       <c r="K36" t="n">
-        <v>-24.46</v>
+        <v>-23.87</v>
       </c>
       <c r="L36" t="n">
-        <v>144.41</v>
+        <v>140.91</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-43.1</v>
+        <v>-44.08</v>
       </c>
       <c r="K37" t="n">
-        <v>84.05</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>94.45</v>
+        <v>96.61</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-124.2</v>
+        <v>-128.18</v>
       </c>
       <c r="K38" t="n">
-        <v>18.17</v>
+        <v>18.75</v>
       </c>
       <c r="L38" t="n">
-        <v>125.52</v>
+        <v>129.55</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>58.64</v>
+        <v>60.95</v>
       </c>
       <c r="K39" t="n">
-        <v>20.08</v>
+        <v>20.87</v>
       </c>
       <c r="L39" t="n">
-        <v>61.98</v>
+        <v>64.42</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-116.69</v>
+        <v>-115.23</v>
       </c>
       <c r="K40" t="n">
-        <v>137.88</v>
+        <v>136.15</v>
       </c>
       <c r="L40" t="n">
-        <v>180.63</v>
+        <v>178.36</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-225.02</v>
+        <v>-236.28</v>
       </c>
       <c r="K41" t="n">
-        <v>-87.88</v>
+        <v>-92.28</v>
       </c>
       <c r="L41" t="n">
-        <v>241.57</v>
+        <v>253.66</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>132.54</v>
+        <v>150.86</v>
       </c>
       <c r="K42" t="n">
-        <v>-40.9</v>
+        <v>-46.55</v>
       </c>
       <c r="L42" t="n">
-        <v>138.71</v>
+        <v>157.87</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="K43" t="n">
-        <v>-195.53</v>
+        <v>-214.05</v>
       </c>
       <c r="L43" t="n">
-        <v>195.53</v>
+        <v>214.05</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-30.29</v>
+        <v>-29.73</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.48</v>
+        <v>-49.55</v>
       </c>
       <c r="L44" t="n">
-        <v>58.87</v>
+        <v>57.79</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-72.04000000000001</v>
+        <v>-70.45</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.53</v>
+        <v>-7.37</v>
       </c>
       <c r="L45" t="n">
-        <v>72.43000000000001</v>
+        <v>70.83</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-43.99</v>
+        <v>-43.26</v>
       </c>
       <c r="K46" t="n">
-        <v>37.98</v>
+        <v>37.35</v>
       </c>
       <c r="L46" t="n">
-        <v>58.12</v>
+        <v>57.15</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-84.33</v>
+        <v>-79.84</v>
       </c>
       <c r="K47" t="n">
-        <v>-41.26</v>
+        <v>-39.06</v>
       </c>
       <c r="L47" t="n">
-        <v>93.88</v>
+        <v>88.88</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-119.42</v>
+        <v>-110.04</v>
       </c>
       <c r="K48" t="n">
-        <v>-38.62</v>
+        <v>-35.59</v>
       </c>
       <c r="L48" t="n">
-        <v>125.51</v>
+        <v>115.65</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-25.01</v>
+        <v>-23.65</v>
       </c>
       <c r="K49" t="n">
-        <v>-30.7</v>
+        <v>-29.02</v>
       </c>
       <c r="L49" t="n">
-        <v>39.6</v>
+        <v>37.44</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>58.9</v>
+        <v>62.3</v>
       </c>
       <c r="K50" t="n">
-        <v>57.72</v>
+        <v>61.05</v>
       </c>
       <c r="L50" t="n">
-        <v>82.45999999999999</v>
+        <v>87.23</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-101.63</v>
+        <v>-100.08</v>
       </c>
       <c r="K51" t="n">
-        <v>60.84</v>
+        <v>59.91</v>
       </c>
       <c r="L51" t="n">
-        <v>118.45</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>121.16</v>
+        <v>118.92</v>
       </c>
       <c r="K52" t="n">
-        <v>-55.06</v>
+        <v>-54.04</v>
       </c>
       <c r="L52" t="n">
-        <v>133.08</v>
+        <v>130.63</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-96.52</v>
+        <v>-99.15000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>113.81</v>
+        <v>116.9</v>
       </c>
       <c r="L53" t="n">
-        <v>149.23</v>
+        <v>153.28</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-26.55</v>
+        <v>-27.39</v>
       </c>
       <c r="K54" t="n">
-        <v>-125.47</v>
+        <v>-129.45</v>
       </c>
       <c r="L54" t="n">
-        <v>128.25</v>
+        <v>132.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-155.88</v>
+        <v>-155.58</v>
       </c>
       <c r="K55" t="n">
-        <v>46.86</v>
+        <v>46.77</v>
       </c>
       <c r="L55" t="n">
-        <v>162.78</v>
+        <v>162.46</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-157.49</v>
+        <v>-170.91</v>
       </c>
       <c r="K56" t="n">
-        <v>20.61</v>
+        <v>22.36</v>
       </c>
       <c r="L56" t="n">
-        <v>158.83</v>
+        <v>172.36</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-56.39</v>
+        <v>-60.93</v>
       </c>
       <c r="K57" t="n">
-        <v>245.55</v>
+        <v>265.29</v>
       </c>
       <c r="L57" t="n">
-        <v>251.95</v>
+        <v>272.2</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-195.96</v>
+        <v>-206.18</v>
       </c>
       <c r="K58" t="n">
-        <v>-99.90000000000001</v>
+        <v>-105.12</v>
       </c>
       <c r="L58" t="n">
-        <v>219.95</v>
+        <v>231.43</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>44.48</v>
+        <v>46.38</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.11</v>
+        <v>-6.37</v>
       </c>
       <c r="L59" t="n">
-        <v>44.89</v>
+        <v>46.81</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-72.18000000000001</v>
+        <v>-64.66</v>
       </c>
       <c r="K60" t="n">
-        <v>69.7</v>
+        <v>62.44</v>
       </c>
       <c r="L60" t="n">
-        <v>100.34</v>
+        <v>89.88</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-50.07</v>
+        <v>-50.23</v>
       </c>
       <c r="K61" t="n">
-        <v>-27.02</v>
+        <v>-27.11</v>
       </c>
       <c r="L61" t="n">
-        <v>56.9</v>
+        <v>57.08</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-3.85</v>
+        <v>-3.99</v>
       </c>
       <c r="K62" t="n">
-        <v>-55.62</v>
+        <v>-57.69</v>
       </c>
       <c r="L62" t="n">
-        <v>55.75</v>
+        <v>57.83</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-23.09</v>
+        <v>-22.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-88.23</v>
+        <v>-86.56</v>
       </c>
       <c r="L63" t="n">
-        <v>91.2</v>
+        <v>89.47</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-23.65</v>
+        <v>-24.6</v>
       </c>
       <c r="K64" t="n">
-        <v>-47.42</v>
+        <v>-49.32</v>
       </c>
       <c r="L64" t="n">
-        <v>53</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-80.88</v>
+        <v>-85.84</v>
       </c>
       <c r="K65" t="n">
-        <v>10.47</v>
+        <v>11.12</v>
       </c>
       <c r="L65" t="n">
-        <v>81.56</v>
+        <v>86.56</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-141.03</v>
+        <v>-138.68</v>
       </c>
       <c r="K66" t="n">
-        <v>-18.94</v>
+        <v>-18.62</v>
       </c>
       <c r="L66" t="n">
-        <v>142.3</v>
+        <v>139.92</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="K67" t="n">
-        <v>104.14</v>
+        <v>105.36</v>
       </c>
       <c r="L67" t="n">
-        <v>104.2</v>
+        <v>105.41</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-63.39</v>
+        <v>-69.52</v>
       </c>
       <c r="K68" t="n">
-        <v>69.77</v>
+        <v>76.52</v>
       </c>
       <c r="L68" t="n">
-        <v>94.27</v>
+        <v>103.38</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-64.54000000000001</v>
+        <v>-65.03</v>
       </c>
       <c r="K69" t="n">
-        <v>143.47</v>
+        <v>144.55</v>
       </c>
       <c r="L69" t="n">
-        <v>157.32</v>
+        <v>158.51</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-172.06</v>
+        <v>-169.84</v>
       </c>
       <c r="K70" t="n">
-        <v>127.69</v>
+        <v>126.04</v>
       </c>
       <c r="L70" t="n">
-        <v>214.27</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-135.87</v>
+        <v>-141.26</v>
       </c>
       <c r="K71" t="n">
-        <v>215.68</v>
+        <v>224.23</v>
       </c>
       <c r="L71" t="n">
-        <v>254.9</v>
+        <v>265.01</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-299.53</v>
+        <v>-319.17</v>
       </c>
       <c r="K72" t="n">
-        <v>121.72</v>
+        <v>129.7</v>
       </c>
       <c r="L72" t="n">
-        <v>323.32</v>
+        <v>344.52</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-152.59</v>
+        <v>-178.74</v>
       </c>
       <c r="K73" t="n">
-        <v>-145.83</v>
+        <v>-170.82</v>
       </c>
       <c r="L73" t="n">
-        <v>211.06</v>
+        <v>247.24</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>84.43000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="K74" t="n">
-        <v>-75.81</v>
+        <v>-61.55</v>
       </c>
       <c r="L74" t="n">
-        <v>113.47</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-52.46</v>
+        <v>-49.41</v>
       </c>
       <c r="K75" t="n">
-        <v>79.63</v>
+        <v>75</v>
       </c>
       <c r="L75" t="n">
-        <v>95.36</v>
+        <v>89.81</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>76.03</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-39.17</v>
+        <v>-36.62</v>
       </c>
       <c r="L76" t="n">
-        <v>85.53</v>
+        <v>79.95</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>111.29</v>
+        <v>104.12</v>
       </c>
       <c r="K77" t="n">
-        <v>27.04</v>
+        <v>25.3</v>
       </c>
       <c r="L77" t="n">
-        <v>114.53</v>
+        <v>107.15</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>31.44</v>
+        <v>29.56</v>
       </c>
       <c r="K78" t="n">
-        <v>-75.44</v>
+        <v>-70.93000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>81.73</v>
+        <v>76.84999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>22.75</v>
+        <v>20.67</v>
       </c>
       <c r="K79" t="n">
-        <v>-121.72</v>
+        <v>-110.56</v>
       </c>
       <c r="L79" t="n">
-        <v>123.83</v>
+        <v>112.48</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>22.81</v>
+        <v>22.71</v>
       </c>
       <c r="K80" t="n">
-        <v>129.73</v>
+        <v>129.14</v>
       </c>
       <c r="L80" t="n">
-        <v>131.72</v>
+        <v>131.12</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-32.39</v>
+        <v>-32.67</v>
       </c>
       <c r="K81" t="n">
-        <v>-102.1</v>
+        <v>-102.99</v>
       </c>
       <c r="L81" t="n">
-        <v>107.11</v>
+        <v>108.04</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>19.55</v>
+        <v>20.3</v>
       </c>
       <c r="K82" t="n">
-        <v>90.2</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>92.29000000000001</v>
+        <v>95.86</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>204.2</v>
+        <v>221.47</v>
       </c>
       <c r="K83" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="L83" t="n">
-        <v>204.21</v>
+        <v>221.48</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-86.65000000000001</v>
+        <v>-89.70999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>231.11</v>
+        <v>239.27</v>
       </c>
       <c r="L84" t="n">
-        <v>246.82</v>
+        <v>255.53</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-133.38</v>
+        <v>-140.72</v>
       </c>
       <c r="K85" t="n">
-        <v>-138.84</v>
+        <v>-146.49</v>
       </c>
       <c r="L85" t="n">
-        <v>192.53</v>
+        <v>203.13</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>3.9</v>
+        <v>4.58</v>
       </c>
       <c r="K86" t="n">
-        <v>146.32</v>
+        <v>171.8</v>
       </c>
       <c r="L86" t="n">
-        <v>146.38</v>
+        <v>171.86</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-31.8</v>
+        <v>-36.12</v>
       </c>
       <c r="K87" t="n">
-        <v>-269.92</v>
+        <v>-306.57</v>
       </c>
       <c r="L87" t="n">
-        <v>271.78</v>
+        <v>308.69</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>92.83</v>
+        <v>103.33</v>
       </c>
       <c r="K88" t="n">
-        <v>226.84</v>
+        <v>252.5</v>
       </c>
       <c r="L88" t="n">
-        <v>245.1</v>
+        <v>272.83</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-49.8</v>
+        <v>-48.75</v>
       </c>
       <c r="K14" t="n">
-        <v>61.03</v>
+        <v>59.73</v>
       </c>
       <c r="L14" t="n">
-        <v>78.77</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>62.54</v>
+        <v>63.71</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.04</v>
+        <v>-2.07</v>
       </c>
       <c r="L15" t="n">
-        <v>62.57</v>
+        <v>63.74</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-33.47</v>
+        <v>-34.25</v>
       </c>
       <c r="K16" t="n">
-        <v>53.84</v>
+        <v>55.1</v>
       </c>
       <c r="L16" t="n">
-        <v>63.4</v>
+        <v>64.88</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>17.87</v>
+        <v>19.32</v>
       </c>
       <c r="K17" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="L17" t="n">
-        <v>18.03</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>60.45</v>
+        <v>62.23</v>
       </c>
       <c r="K18" t="n">
-        <v>16.15</v>
+        <v>16.63</v>
       </c>
       <c r="L18" t="n">
-        <v>62.57</v>
+        <v>64.41</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-29.85</v>
+        <v>-32.38</v>
       </c>
       <c r="K19" t="n">
-        <v>46.3</v>
+        <v>50.22</v>
       </c>
       <c r="L19" t="n">
-        <v>55.09</v>
+        <v>59.76</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>172.4</v>
+        <v>164.01</v>
       </c>
       <c r="K20" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="L20" t="n">
-        <v>172.42</v>
+        <v>164.02</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>80.95999999999999</v>
+        <v>81.58</v>
       </c>
       <c r="K21" t="n">
-        <v>90.27</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>121.26</v>
+        <v>122.19</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>130.78</v>
+        <v>127.87</v>
       </c>
       <c r="K22" t="n">
-        <v>113.23</v>
+        <v>110.71</v>
       </c>
       <c r="L22" t="n">
-        <v>172.98</v>
+        <v>169.14</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>129.08</v>
+        <v>130.35</v>
       </c>
       <c r="K23" t="n">
-        <v>90.65000000000001</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>157.73</v>
+        <v>159.28</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>91.34</v>
+        <v>91</v>
       </c>
       <c r="K24" t="n">
-        <v>137.28</v>
+        <v>136.77</v>
       </c>
       <c r="L24" t="n">
-        <v>164.9</v>
+        <v>164.28</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-63.39</v>
+        <v>-66.75</v>
       </c>
       <c r="K25" t="n">
-        <v>91.40000000000001</v>
+        <v>96.25</v>
       </c>
       <c r="L25" t="n">
-        <v>111.23</v>
+        <v>117.13</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="K26" t="n">
-        <v>255.44</v>
+        <v>248.91</v>
       </c>
       <c r="L26" t="n">
-        <v>255.44</v>
+        <v>248.92</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-167.18</v>
+        <v>-175.11</v>
       </c>
       <c r="K27" t="n">
-        <v>4.53</v>
+        <v>4.75</v>
       </c>
       <c r="L27" t="n">
-        <v>167.24</v>
+        <v>175.17</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-181.87</v>
+        <v>-179.45</v>
       </c>
       <c r="K28" t="n">
-        <v>-145.56</v>
+        <v>-143.63</v>
       </c>
       <c r="L28" t="n">
-        <v>232.95</v>
+        <v>229.85</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>8.08</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>-64.25</v>
+        <v>-64.55</v>
       </c>
       <c r="L29" t="n">
-        <v>64.76000000000001</v>
+        <v>65.06</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-49.91</v>
+        <v>-51.16</v>
       </c>
       <c r="K30" t="n">
-        <v>23.83</v>
+        <v>24.42</v>
       </c>
       <c r="L30" t="n">
-        <v>55.31</v>
+        <v>56.69</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-70.54000000000001</v>
+        <v>-70.36</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>5.99</v>
       </c>
       <c r="L31" t="n">
-        <v>70.8</v>
+        <v>70.62</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>34.41</v>
+        <v>33.65</v>
       </c>
       <c r="K32" t="n">
-        <v>92.29000000000001</v>
+        <v>90.25</v>
       </c>
       <c r="L32" t="n">
-        <v>98.5</v>
+        <v>96.31999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>18.87</v>
+        <v>17.7</v>
       </c>
       <c r="K33" t="n">
-        <v>-124.09</v>
+        <v>-116.43</v>
       </c>
       <c r="L33" t="n">
-        <v>125.52</v>
+        <v>117.76</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>25.21</v>
+        <v>24.2</v>
       </c>
       <c r="K34" t="n">
-        <v>98.28</v>
+        <v>94.36</v>
       </c>
       <c r="L34" t="n">
-        <v>101.46</v>
+        <v>97.42</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>100.36</v>
+        <v>100.14</v>
       </c>
       <c r="K35" t="n">
-        <v>69.45999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>122.05</v>
+        <v>121.79</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>138.87</v>
+        <v>136.49</v>
       </c>
       <c r="K36" t="n">
-        <v>-23.87</v>
+        <v>-23.46</v>
       </c>
       <c r="L36" t="n">
-        <v>140.91</v>
+        <v>138.5</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-44.08</v>
+        <v>-45.85</v>
       </c>
       <c r="K37" t="n">
-        <v>85.95999999999999</v>
+        <v>89.41</v>
       </c>
       <c r="L37" t="n">
-        <v>96.61</v>
+        <v>100.48</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-128.18</v>
+        <v>-131.82</v>
       </c>
       <c r="K38" t="n">
-        <v>18.75</v>
+        <v>19.28</v>
       </c>
       <c r="L38" t="n">
-        <v>129.55</v>
+        <v>133.22</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>60.95</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>20.87</v>
+        <v>22.9</v>
       </c>
       <c r="L39" t="n">
-        <v>64.42</v>
+        <v>70.70999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-115.23</v>
+        <v>-112.88</v>
       </c>
       <c r="K40" t="n">
-        <v>136.15</v>
+        <v>133.37</v>
       </c>
       <c r="L40" t="n">
-        <v>178.36</v>
+        <v>174.73</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-236.28</v>
+        <v>-236.96</v>
       </c>
       <c r="K41" t="n">
-        <v>-92.28</v>
+        <v>-92.54000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>253.66</v>
+        <v>254.39</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>150.86</v>
+        <v>165.24</v>
       </c>
       <c r="K42" t="n">
-        <v>-46.55</v>
+        <v>-50.99</v>
       </c>
       <c r="L42" t="n">
-        <v>157.87</v>
+        <v>172.93</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="K43" t="n">
-        <v>-214.05</v>
+        <v>-223.34</v>
       </c>
       <c r="L43" t="n">
-        <v>214.05</v>
+        <v>223.34</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-29.73</v>
+        <v>-30.25</v>
       </c>
       <c r="K44" t="n">
-        <v>-49.55</v>
+        <v>-50.41</v>
       </c>
       <c r="L44" t="n">
-        <v>57.79</v>
+        <v>58.79</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-70.45</v>
+        <v>-69.5</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.37</v>
+        <v>-7.27</v>
       </c>
       <c r="L45" t="n">
-        <v>70.83</v>
+        <v>69.88</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-43.26</v>
+        <v>-44.19</v>
       </c>
       <c r="K46" t="n">
-        <v>37.35</v>
+        <v>38.15</v>
       </c>
       <c r="L46" t="n">
-        <v>57.15</v>
+        <v>58.38</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-79.84</v>
+        <v>-78.09999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-39.06</v>
+        <v>-38.21</v>
       </c>
       <c r="L47" t="n">
-        <v>88.88</v>
+        <v>86.94</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-110.04</v>
+        <v>-104.08</v>
       </c>
       <c r="K48" t="n">
-        <v>-35.59</v>
+        <v>-33.66</v>
       </c>
       <c r="L48" t="n">
-        <v>115.65</v>
+        <v>109.38</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-23.65</v>
+        <v>-25.88</v>
       </c>
       <c r="K49" t="n">
-        <v>-29.02</v>
+        <v>-31.76</v>
       </c>
       <c r="L49" t="n">
-        <v>37.44</v>
+        <v>40.97</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>62.3</v>
+        <v>66.75</v>
       </c>
       <c r="K50" t="n">
-        <v>61.05</v>
+        <v>65.41</v>
       </c>
       <c r="L50" t="n">
-        <v>87.23</v>
+        <v>93.45999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-100.08</v>
+        <v>-98.89</v>
       </c>
       <c r="K51" t="n">
-        <v>59.91</v>
+        <v>59.2</v>
       </c>
       <c r="L51" t="n">
-        <v>116.64</v>
+        <v>115.26</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>118.92</v>
+        <v>118.27</v>
       </c>
       <c r="K52" t="n">
-        <v>-54.04</v>
+        <v>-53.75</v>
       </c>
       <c r="L52" t="n">
-        <v>130.63</v>
+        <v>129.91</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-99.15000000000001</v>
+        <v>-101.2</v>
       </c>
       <c r="K53" t="n">
-        <v>116.9</v>
+        <v>119.32</v>
       </c>
       <c r="L53" t="n">
-        <v>153.28</v>
+        <v>156.46</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-27.39</v>
+        <v>-28.17</v>
       </c>
       <c r="K54" t="n">
-        <v>-129.45</v>
+        <v>-133.1</v>
       </c>
       <c r="L54" t="n">
-        <v>132.31</v>
+        <v>136.05</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-155.58</v>
+        <v>-153.89</v>
       </c>
       <c r="K55" t="n">
-        <v>46.77</v>
+        <v>46.26</v>
       </c>
       <c r="L55" t="n">
-        <v>162.46</v>
+        <v>160.7</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-170.91</v>
+        <v>-181.19</v>
       </c>
       <c r="K56" t="n">
-        <v>22.36</v>
+        <v>23.71</v>
       </c>
       <c r="L56" t="n">
-        <v>172.36</v>
+        <v>182.73</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-60.93</v>
+        <v>-61.35</v>
       </c>
       <c r="K57" t="n">
-        <v>265.29</v>
+        <v>267.15</v>
       </c>
       <c r="L57" t="n">
-        <v>272.2</v>
+        <v>274.1</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-206.18</v>
+        <v>-206.8</v>
       </c>
       <c r="K58" t="n">
-        <v>-105.12</v>
+        <v>-105.43</v>
       </c>
       <c r="L58" t="n">
-        <v>231.43</v>
+        <v>232.13</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>46.38</v>
+        <v>50.28</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.37</v>
+        <v>-6.9</v>
       </c>
       <c r="L59" t="n">
-        <v>46.81</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-64.66</v>
+        <v>-62.35</v>
       </c>
       <c r="K60" t="n">
-        <v>62.44</v>
+        <v>60.21</v>
       </c>
       <c r="L60" t="n">
-        <v>89.88</v>
+        <v>86.68000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-50.23</v>
+        <v>-52.62</v>
       </c>
       <c r="K61" t="n">
-        <v>-27.11</v>
+        <v>-28.4</v>
       </c>
       <c r="L61" t="n">
-        <v>57.08</v>
+        <v>59.79</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-3.99</v>
+        <v>-4.23</v>
       </c>
       <c r="K62" t="n">
-        <v>-57.69</v>
+        <v>-61.05</v>
       </c>
       <c r="L62" t="n">
-        <v>57.83</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-22.65</v>
+        <v>-22.46</v>
       </c>
       <c r="K63" t="n">
-        <v>-86.56</v>
+        <v>-85.81999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>89.47</v>
+        <v>88.70999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-24.6</v>
+        <v>-26.51</v>
       </c>
       <c r="K64" t="n">
-        <v>-49.32</v>
+        <v>-53.15</v>
       </c>
       <c r="L64" t="n">
-        <v>55.12</v>
+        <v>59.39</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-85.84</v>
+        <v>-92.27</v>
       </c>
       <c r="K65" t="n">
-        <v>11.12</v>
+        <v>11.95</v>
       </c>
       <c r="L65" t="n">
-        <v>86.56</v>
+        <v>93.04000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-138.68</v>
+        <v>-137.96</v>
       </c>
       <c r="K66" t="n">
-        <v>-18.62</v>
+        <v>-18.52</v>
       </c>
       <c r="L66" t="n">
-        <v>139.92</v>
+        <v>139.2</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="K67" t="n">
-        <v>105.36</v>
+        <v>108.98</v>
       </c>
       <c r="L67" t="n">
-        <v>105.41</v>
+        <v>109.04</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-69.52</v>
+        <v>-75.98999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>76.52</v>
+        <v>83.64</v>
       </c>
       <c r="L68" t="n">
-        <v>103.38</v>
+        <v>113.01</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-65.03</v>
+        <v>-65.08</v>
       </c>
       <c r="K69" t="n">
-        <v>144.55</v>
+        <v>144.67</v>
       </c>
       <c r="L69" t="n">
-        <v>158.51</v>
+        <v>158.63</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-169.84</v>
+        <v>-165.63</v>
       </c>
       <c r="K70" t="n">
-        <v>126.04</v>
+        <v>122.91</v>
       </c>
       <c r="L70" t="n">
-        <v>211.5</v>
+        <v>206.25</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-141.26</v>
+        <v>-140.38</v>
       </c>
       <c r="K71" t="n">
-        <v>224.23</v>
+        <v>222.83</v>
       </c>
       <c r="L71" t="n">
-        <v>265.01</v>
+        <v>263.36</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-319.17</v>
+        <v>-311.71</v>
       </c>
       <c r="K72" t="n">
-        <v>129.7</v>
+        <v>126.67</v>
       </c>
       <c r="L72" t="n">
-        <v>344.52</v>
+        <v>336.47</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-178.74</v>
+        <v>-186.3</v>
       </c>
       <c r="K73" t="n">
-        <v>-170.82</v>
+        <v>-178.05</v>
       </c>
       <c r="L73" t="n">
-        <v>247.24</v>
+        <v>257.71</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>68.55</v>
+        <v>65.69</v>
       </c>
       <c r="K74" t="n">
-        <v>-61.55</v>
+        <v>-58.99</v>
       </c>
       <c r="L74" t="n">
-        <v>92.13</v>
+        <v>88.29000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-49.41</v>
+        <v>-47.86</v>
       </c>
       <c r="K75" t="n">
-        <v>75</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>89.81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>71.06999999999999</v>
+        <v>69.66</v>
       </c>
       <c r="K76" t="n">
-        <v>-36.62</v>
+        <v>-35.89</v>
       </c>
       <c r="L76" t="n">
-        <v>79.95</v>
+        <v>78.36</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>104.12</v>
+        <v>100.49</v>
       </c>
       <c r="K77" t="n">
-        <v>25.3</v>
+        <v>24.41</v>
       </c>
       <c r="L77" t="n">
-        <v>107.15</v>
+        <v>103.41</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>29.56</v>
+        <v>30.03</v>
       </c>
       <c r="K78" t="n">
-        <v>-70.93000000000001</v>
+        <v>-72.05</v>
       </c>
       <c r="L78" t="n">
-        <v>76.84999999999999</v>
+        <v>78.05</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>20.67</v>
+        <v>19.7</v>
       </c>
       <c r="K79" t="n">
-        <v>-110.56</v>
+        <v>-105.38</v>
       </c>
       <c r="L79" t="n">
-        <v>112.48</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>22.71</v>
+        <v>22.91</v>
       </c>
       <c r="K80" t="n">
-        <v>129.14</v>
+        <v>130.29</v>
       </c>
       <c r="L80" t="n">
-        <v>131.12</v>
+        <v>132.28</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-32.67</v>
+        <v>-33.47</v>
       </c>
       <c r="K81" t="n">
-        <v>-102.99</v>
+        <v>-105.52</v>
       </c>
       <c r="L81" t="n">
-        <v>108.04</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>20.3</v>
+        <v>21.4</v>
       </c>
       <c r="K82" t="n">
-        <v>93.68000000000001</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>95.86</v>
+        <v>101.05</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>221.47</v>
+        <v>224.28</v>
       </c>
       <c r="K83" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="L83" t="n">
-        <v>221.48</v>
+        <v>224.29</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-89.70999999999999</v>
+        <v>-87.16</v>
       </c>
       <c r="K84" t="n">
-        <v>239.27</v>
+        <v>232.46</v>
       </c>
       <c r="L84" t="n">
-        <v>255.53</v>
+        <v>248.26</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-140.72</v>
+        <v>-140.29</v>
       </c>
       <c r="K85" t="n">
-        <v>-146.49</v>
+        <v>-146.03</v>
       </c>
       <c r="L85" t="n">
-        <v>203.13</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>4.58</v>
+        <v>5</v>
       </c>
       <c r="K86" t="n">
-        <v>171.8</v>
+        <v>187.49</v>
       </c>
       <c r="L86" t="n">
-        <v>171.86</v>
+        <v>187.56</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-36.12</v>
+        <v>-36.59</v>
       </c>
       <c r="K87" t="n">
-        <v>-306.57</v>
+        <v>-310.58</v>
       </c>
       <c r="L87" t="n">
-        <v>308.69</v>
+        <v>312.73</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>103.33</v>
+        <v>105.3</v>
       </c>
       <c r="K88" t="n">
-        <v>252.5</v>
+        <v>257.3</v>
       </c>
       <c r="L88" t="n">
-        <v>272.83</v>
+        <v>278.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -628,25 +628,25 @@
         <v>3.95</v>
       </c>
       <c r="F14" t="n">
-        <v>11.78</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>231.1</v>
+        <v>233.3</v>
       </c>
       <c r="H14" t="n">
-        <v>96</v>
+        <v>97.2</v>
       </c>
       <c r="I14" t="n">
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-48.75</v>
+        <v>-53.22</v>
       </c>
       <c r="K14" t="n">
-        <v>59.73</v>
+        <v>63.44</v>
       </c>
       <c r="L14" t="n">
-        <v>77.09999999999999</v>
+        <v>82.81</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>3.88</v>
       </c>
       <c r="F15" t="n">
-        <v>12.19</v>
+        <v>11.87</v>
       </c>
       <c r="G15" t="n">
-        <v>231.4</v>
+        <v>241.5</v>
       </c>
       <c r="H15" t="n">
         <v>97.3</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>63.71</v>
+        <v>75.5</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.07</v>
+        <v>-2.99</v>
       </c>
       <c r="L15" t="n">
-        <v>63.74</v>
+        <v>75.56</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>3.86</v>
       </c>
       <c r="F16" t="n">
-        <v>11.77</v>
+        <v>10.03</v>
       </c>
       <c r="G16" t="n">
-        <v>228.3</v>
+        <v>233.2</v>
       </c>
       <c r="H16" t="n">
-        <v>98.3</v>
+        <v>95.8</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-34.25</v>
+        <v>-36.92</v>
       </c>
       <c r="K16" t="n">
-        <v>55.1</v>
+        <v>56.39</v>
       </c>
       <c r="L16" t="n">
-        <v>64.88</v>
+        <v>67.41</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>3.29</v>
       </c>
       <c r="F17" t="n">
-        <v>11.99</v>
+        <v>7.11</v>
       </c>
       <c r="G17" t="n">
-        <v>227.7</v>
+        <v>237.6</v>
       </c>
       <c r="H17" t="n">
-        <v>95.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>19.32</v>
+        <v>13.39</v>
       </c>
       <c r="K17" t="n">
-        <v>2.53</v>
+        <v>0.19</v>
       </c>
       <c r="L17" t="n">
-        <v>19.48</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>3.47</v>
       </c>
       <c r="F18" t="n">
-        <v>11.3</v>
+        <v>7.11</v>
       </c>
       <c r="G18" t="n">
-        <v>233.4</v>
+        <v>223.8</v>
       </c>
       <c r="H18" t="n">
-        <v>93.59999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>62.23</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>16.63</v>
+        <v>16.7</v>
       </c>
       <c r="L18" t="n">
-        <v>64.41</v>
+        <v>74.68000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>3.48</v>
       </c>
       <c r="F19" t="n">
-        <v>11.89</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>237</v>
+        <v>235.6</v>
       </c>
       <c r="H19" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-32.38</v>
+        <v>-43.17</v>
       </c>
       <c r="K19" t="n">
-        <v>50.22</v>
+        <v>52.41</v>
       </c>
       <c r="L19" t="n">
-        <v>59.76</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>3.63</v>
       </c>
       <c r="F20" t="n">
-        <v>12.52</v>
+        <v>12.74</v>
       </c>
       <c r="G20" t="n">
-        <v>237.1</v>
+        <v>248.2</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>164.01</v>
+        <v>188.64</v>
       </c>
       <c r="K20" t="n">
-        <v>2.18</v>
+        <v>-0.29</v>
       </c>
       <c r="L20" t="n">
-        <v>164.02</v>
+        <v>188.64</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>4.31</v>
       </c>
       <c r="F21" t="n">
-        <v>12.19</v>
+        <v>11.73</v>
       </c>
       <c r="G21" t="n">
-        <v>229.9</v>
+        <v>241.6</v>
       </c>
       <c r="H21" t="n">
-        <v>98</v>
+        <v>96.5</v>
       </c>
       <c r="I21" t="n">
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>81.58</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>90.95999999999999</v>
+        <v>104.38</v>
       </c>
       <c r="L21" t="n">
-        <v>122.19</v>
+        <v>131.6</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>4.42</v>
       </c>
       <c r="F22" t="n">
-        <v>11.79</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>231.2</v>
+        <v>233.6</v>
       </c>
       <c r="H22" t="n">
-        <v>92.5</v>
+        <v>97.2</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>127.87</v>
+        <v>129.71</v>
       </c>
       <c r="K22" t="n">
-        <v>110.71</v>
+        <v>115.01</v>
       </c>
       <c r="L22" t="n">
-        <v>169.14</v>
+        <v>173.35</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>3.86</v>
       </c>
       <c r="F23" t="n">
-        <v>11.18</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>225.1</v>
+        <v>221.3</v>
       </c>
       <c r="H23" t="n">
-        <v>97.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>130.35</v>
+        <v>126.57</v>
       </c>
       <c r="K23" t="n">
-        <v>91.54000000000001</v>
+        <v>74.47</v>
       </c>
       <c r="L23" t="n">
-        <v>159.28</v>
+        <v>146.85</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>3.58</v>
       </c>
       <c r="F24" t="n">
-        <v>12.51</v>
+        <v>10.92</v>
       </c>
       <c r="G24" t="n">
-        <v>217.5</v>
+        <v>248</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>91</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>136.77</v>
+        <v>160.17</v>
       </c>
       <c r="L24" t="n">
-        <v>164.28</v>
+        <v>174.82</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>3.16</v>
       </c>
       <c r="F25" t="n">
-        <v>12.38</v>
+        <v>10.58</v>
       </c>
       <c r="G25" t="n">
-        <v>239.7</v>
+        <v>245.4</v>
       </c>
       <c r="H25" t="n">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-66.75</v>
+        <v>-111.24</v>
       </c>
       <c r="K25" t="n">
-        <v>96.25</v>
+        <v>87.55</v>
       </c>
       <c r="L25" t="n">
-        <v>117.13</v>
+        <v>141.57</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>3.32</v>
       </c>
       <c r="F26" t="n">
-        <v>12.26</v>
+        <v>10.19</v>
       </c>
       <c r="G26" t="n">
-        <v>235</v>
+        <v>243.1</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>1.87</v>
+        <v>-35.63</v>
       </c>
       <c r="K26" t="n">
-        <v>248.91</v>
+        <v>280.53</v>
       </c>
       <c r="L26" t="n">
-        <v>248.92</v>
+        <v>282.78</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>3.6</v>
       </c>
       <c r="F27" t="n">
-        <v>11.94</v>
+        <v>11.91</v>
       </c>
       <c r="G27" t="n">
-        <v>230.6</v>
+        <v>236.5</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-175.11</v>
+        <v>-230.08</v>
       </c>
       <c r="K27" t="n">
-        <v>4.75</v>
+        <v>-22.95</v>
       </c>
       <c r="L27" t="n">
-        <v>175.17</v>
+        <v>231.23</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>3.64</v>
       </c>
       <c r="F28" t="n">
-        <v>12.45</v>
+        <v>7.97</v>
       </c>
       <c r="G28" t="n">
-        <v>239</v>
+        <v>246.9</v>
       </c>
       <c r="H28" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-179.45</v>
+        <v>-231.86</v>
       </c>
       <c r="K28" t="n">
-        <v>-143.63</v>
+        <v>-167.89</v>
       </c>
       <c r="L28" t="n">
-        <v>229.85</v>
+        <v>286.26</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>4.01</v>
       </c>
       <c r="F29" t="n">
-        <v>12.06</v>
+        <v>10.76</v>
       </c>
       <c r="G29" t="n">
-        <v>242.4</v>
+        <v>220.6</v>
       </c>
       <c r="H29" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>8.119999999999999</v>
+        <v>-73.98</v>
       </c>
       <c r="K29" t="n">
-        <v>-64.55</v>
+        <v>-31.32</v>
       </c>
       <c r="L29" t="n">
-        <v>65.06</v>
+        <v>80.33</v>
       </c>
     </row>
     <row r="30">
@@ -1297,28 +1297,28 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="F30" t="n">
-        <v>11.66</v>
+        <v>10.82</v>
       </c>
       <c r="G30" t="n">
-        <v>234.5</v>
+        <v>251.5</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-51.16</v>
+        <v>27.28</v>
       </c>
       <c r="K30" t="n">
-        <v>24.42</v>
+        <v>59.08</v>
       </c>
       <c r="L30" t="n">
-        <v>56.69</v>
+        <v>65.06999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1339,28 +1339,28 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.34</v>
+        <v>4.15</v>
       </c>
       <c r="F31" t="n">
-        <v>12.26</v>
+        <v>9.91</v>
       </c>
       <c r="G31" t="n">
-        <v>239.7</v>
+        <v>234.3</v>
       </c>
       <c r="H31" t="n">
-        <v>95.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>-70.36</v>
+        <v>3.98</v>
       </c>
       <c r="K31" t="n">
-        <v>5.99</v>
+        <v>81.56</v>
       </c>
       <c r="L31" t="n">
-        <v>70.62</v>
+        <v>81.66</v>
       </c>
     </row>
     <row r="32">
@@ -1381,28 +1381,28 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.68</v>
+        <v>3.73</v>
       </c>
       <c r="F32" t="n">
-        <v>12.28</v>
+        <v>10.5</v>
       </c>
       <c r="G32" t="n">
-        <v>235.2</v>
+        <v>230.4</v>
       </c>
       <c r="H32" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>33.65</v>
+        <v>75.72</v>
       </c>
       <c r="K32" t="n">
-        <v>90.25</v>
+        <v>-75.75</v>
       </c>
       <c r="L32" t="n">
-        <v>96.31999999999999</v>
+        <v>107.11</v>
       </c>
     </row>
     <row r="33">
@@ -1423,28 +1423,28 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="F33" t="n">
-        <v>12.27</v>
+        <v>11.72</v>
       </c>
       <c r="G33" t="n">
-        <v>237.3</v>
+        <v>221.1</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>17.7</v>
+        <v>-119.87</v>
       </c>
       <c r="K33" t="n">
-        <v>-116.43</v>
+        <v>58.73</v>
       </c>
       <c r="L33" t="n">
-        <v>117.76</v>
+        <v>133.48</v>
       </c>
     </row>
     <row r="34">
@@ -1465,28 +1465,28 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="F34" t="n">
-        <v>11.76</v>
+        <v>8.84</v>
       </c>
       <c r="G34" t="n">
-        <v>216.2</v>
+        <v>243.6</v>
       </c>
       <c r="H34" t="n">
-        <v>97.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>24.2</v>
+        <v>99.83</v>
       </c>
       <c r="K34" t="n">
-        <v>94.36</v>
+        <v>-12.73</v>
       </c>
       <c r="L34" t="n">
-        <v>97.42</v>
+        <v>100.64</v>
       </c>
     </row>
     <row r="35">
@@ -1507,28 +1507,28 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.03</v>
+        <v>4.91</v>
       </c>
       <c r="F35" t="n">
-        <v>12.14</v>
+        <v>12.43</v>
       </c>
       <c r="G35" t="n">
-        <v>224.3</v>
+        <v>225</v>
       </c>
       <c r="H35" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>100.14</v>
+        <v>123.36</v>
       </c>
       <c r="K35" t="n">
-        <v>69.31999999999999</v>
+        <v>16.09</v>
       </c>
       <c r="L35" t="n">
-        <v>121.79</v>
+        <v>124.41</v>
       </c>
     </row>
     <row r="36">
@@ -1549,28 +1549,28 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.22</v>
+        <v>4.11</v>
       </c>
       <c r="F36" t="n">
-        <v>11.64</v>
+        <v>12.53</v>
       </c>
       <c r="G36" t="n">
-        <v>239.5</v>
+        <v>240.8</v>
       </c>
       <c r="H36" t="n">
-        <v>94.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>136.49</v>
+        <v>-44.87</v>
       </c>
       <c r="K36" t="n">
-        <v>-23.46</v>
+        <v>136.28</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5</v>
+        <v>143.47</v>
       </c>
     </row>
     <row r="37">
@@ -1591,28 +1591,28 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.66</v>
+        <v>4.23</v>
       </c>
       <c r="F37" t="n">
-        <v>11.56</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>229.1</v>
+        <v>245.4</v>
       </c>
       <c r="H37" t="n">
-        <v>93.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-45.85</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>89.41</v>
+        <v>-16.24</v>
       </c>
       <c r="L37" t="n">
-        <v>100.48</v>
+        <v>98.31</v>
       </c>
     </row>
     <row r="38">
@@ -1633,28 +1633,28 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="F38" t="n">
-        <v>11.71</v>
+        <v>9.31</v>
       </c>
       <c r="G38" t="n">
-        <v>219.3</v>
+        <v>231.9</v>
       </c>
       <c r="H38" t="n">
-        <v>93</v>
+        <v>91.3</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-131.82</v>
+        <v>-151.49</v>
       </c>
       <c r="K38" t="n">
-        <v>19.28</v>
+        <v>-0.01</v>
       </c>
       <c r="L38" t="n">
-        <v>133.22</v>
+        <v>151.49</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>4.94</v>
       </c>
       <c r="F39" t="n">
-        <v>11.92</v>
+        <v>13.57</v>
       </c>
       <c r="G39" t="n">
-        <v>239.4</v>
+        <v>236.3</v>
       </c>
       <c r="H39" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>66.90000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="K39" t="n">
-        <v>22.9</v>
+        <v>-19.58</v>
       </c>
       <c r="L39" t="n">
-        <v>70.70999999999999</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>3.95</v>
       </c>
       <c r="F40" t="n">
-        <v>10.99</v>
+        <v>7.28</v>
       </c>
       <c r="G40" t="n">
-        <v>236.3</v>
+        <v>217.6</v>
       </c>
       <c r="H40" t="n">
-        <v>89.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-112.88</v>
+        <v>-139.58</v>
       </c>
       <c r="K40" t="n">
-        <v>133.37</v>
+        <v>119.69</v>
       </c>
       <c r="L40" t="n">
-        <v>174.73</v>
+        <v>183.87</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>4.24</v>
       </c>
       <c r="F41" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="G41" t="n">
-        <v>243.2</v>
+        <v>239.7</v>
       </c>
       <c r="H41" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-236.96</v>
+        <v>-290.33</v>
       </c>
       <c r="K41" t="n">
-        <v>-92.54000000000001</v>
+        <v>-123.14</v>
       </c>
       <c r="L41" t="n">
-        <v>254.39</v>
+        <v>315.36</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>4.16</v>
       </c>
       <c r="F42" t="n">
-        <v>11.72</v>
+        <v>10.87</v>
       </c>
       <c r="G42" t="n">
-        <v>229.1</v>
+        <v>232.2</v>
       </c>
       <c r="H42" t="n">
-        <v>96.7</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>165.24</v>
+        <v>124.38</v>
       </c>
       <c r="K42" t="n">
-        <v>-50.99</v>
+        <v>-154.66</v>
       </c>
       <c r="L42" t="n">
-        <v>172.93</v>
+        <v>198.47</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>4.36</v>
       </c>
       <c r="F43" t="n">
-        <v>11.66</v>
+        <v>11.89</v>
       </c>
       <c r="G43" t="n">
-        <v>211.8</v>
+        <v>230.9</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>1.71</v>
+        <v>-55.69</v>
       </c>
       <c r="K43" t="n">
-        <v>-223.34</v>
+        <v>-258.44</v>
       </c>
       <c r="L43" t="n">
-        <v>223.34</v>
+        <v>264.37</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>4.46</v>
       </c>
       <c r="F44" t="n">
-        <v>11.29</v>
+        <v>10.26</v>
       </c>
       <c r="G44" t="n">
-        <v>235.6</v>
+        <v>223.6</v>
       </c>
       <c r="H44" t="n">
-        <v>93</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-30.25</v>
+        <v>-37.08</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.41</v>
+        <v>-61.97</v>
       </c>
       <c r="L44" t="n">
-        <v>58.79</v>
+        <v>72.22</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>3.61</v>
       </c>
       <c r="F45" t="n">
-        <v>12.19</v>
+        <v>8.25</v>
       </c>
       <c r="G45" t="n">
-        <v>235.3</v>
+        <v>241.6</v>
       </c>
       <c r="H45" t="n">
-        <v>92.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-69.5</v>
+        <v>-78.43000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.27</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>69.88</v>
+        <v>78.88</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>4.53</v>
       </c>
       <c r="F46" t="n">
-        <v>11.63</v>
+        <v>13.5</v>
       </c>
       <c r="G46" t="n">
-        <v>236.4</v>
+        <v>230.3</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-44.19</v>
+        <v>-56.03</v>
       </c>
       <c r="K46" t="n">
-        <v>38.15</v>
+        <v>45.72</v>
       </c>
       <c r="L46" t="n">
-        <v>58.38</v>
+        <v>72.31999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>4.54</v>
       </c>
       <c r="F47" t="n">
-        <v>11.26</v>
+        <v>13.57</v>
       </c>
       <c r="G47" t="n">
-        <v>232.4</v>
+        <v>223</v>
       </c>
       <c r="H47" t="n">
-        <v>92.8</v>
+        <v>97.8</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-78.09999999999999</v>
+        <v>-91.58</v>
       </c>
       <c r="K47" t="n">
-        <v>-38.21</v>
+        <v>-46.88</v>
       </c>
       <c r="L47" t="n">
-        <v>86.94</v>
+        <v>102.88</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>4.52</v>
       </c>
       <c r="F48" t="n">
-        <v>10.98</v>
+        <v>11.85</v>
       </c>
       <c r="G48" t="n">
-        <v>232.4</v>
+        <v>217.3</v>
       </c>
       <c r="H48" t="n">
-        <v>96.2</v>
+        <v>97.8</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-104.08</v>
+        <v>-110.1</v>
       </c>
       <c r="K48" t="n">
-        <v>-33.66</v>
+        <v>-37.89</v>
       </c>
       <c r="L48" t="n">
-        <v>109.38</v>
+        <v>116.44</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>4.27</v>
       </c>
       <c r="F49" t="n">
-        <v>12.61</v>
+        <v>12.54</v>
       </c>
       <c r="G49" t="n">
-        <v>245.5</v>
+        <v>249.9</v>
       </c>
       <c r="H49" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-25.88</v>
+        <v>-44.41</v>
       </c>
       <c r="K49" t="n">
-        <v>-31.76</v>
+        <v>-43.54</v>
       </c>
       <c r="L49" t="n">
-        <v>40.97</v>
+        <v>62.19</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>4.09</v>
       </c>
       <c r="F50" t="n">
-        <v>11.73</v>
+        <v>13.57</v>
       </c>
       <c r="G50" t="n">
-        <v>213.9</v>
+        <v>232.4</v>
       </c>
       <c r="H50" t="n">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>66.75</v>
+        <v>62.68</v>
       </c>
       <c r="K50" t="n">
-        <v>65.41</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>93.45999999999999</v>
+        <v>104.95</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>3.72</v>
       </c>
       <c r="F51" t="n">
-        <v>11.98</v>
+        <v>12.31</v>
       </c>
       <c r="G51" t="n">
-        <v>228.6</v>
+        <v>237.3</v>
       </c>
       <c r="H51" t="n">
-        <v>99.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-98.89</v>
+        <v>-125.64</v>
       </c>
       <c r="K51" t="n">
-        <v>59.2</v>
+        <v>62.55</v>
       </c>
       <c r="L51" t="n">
-        <v>115.26</v>
+        <v>140.35</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>4.74</v>
       </c>
       <c r="F52" t="n">
-        <v>11.88</v>
+        <v>11.57</v>
       </c>
       <c r="G52" t="n">
-        <v>226.8</v>
+        <v>235.4</v>
       </c>
       <c r="H52" t="n">
-        <v>93.8</v>
+        <v>95</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>118.27</v>
+        <v>127.76</v>
       </c>
       <c r="K52" t="n">
-        <v>-53.75</v>
+        <v>-77.18000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>129.91</v>
+        <v>149.27</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>4.48</v>
       </c>
       <c r="F53" t="n">
-        <v>11.53</v>
+        <v>13.57</v>
       </c>
       <c r="G53" t="n">
-        <v>220.4</v>
+        <v>228.4</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>91.8</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-101.2</v>
+        <v>-142.07</v>
       </c>
       <c r="K53" t="n">
-        <v>119.32</v>
+        <v>104.45</v>
       </c>
       <c r="L53" t="n">
-        <v>156.46</v>
+        <v>176.34</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>4.13</v>
       </c>
       <c r="F54" t="n">
-        <v>12.1</v>
+        <v>12.65</v>
       </c>
       <c r="G54" t="n">
-        <v>232.9</v>
+        <v>239.9</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-28.17</v>
+        <v>-67.70999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-133.1</v>
+        <v>-161.89</v>
       </c>
       <c r="L54" t="n">
-        <v>136.05</v>
+        <v>175.48</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>4.32</v>
       </c>
       <c r="F55" t="n">
-        <v>11.87</v>
+        <v>12.5</v>
       </c>
       <c r="G55" t="n">
-        <v>234.9</v>
+        <v>235.2</v>
       </c>
       <c r="H55" t="n">
-        <v>98.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>-153.89</v>
+        <v>-199.09</v>
       </c>
       <c r="K55" t="n">
-        <v>46.26</v>
+        <v>35.26</v>
       </c>
       <c r="L55" t="n">
-        <v>160.7</v>
+        <v>202.19</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>3.81</v>
       </c>
       <c r="F56" t="n">
-        <v>11.62</v>
+        <v>13.57</v>
       </c>
       <c r="G56" t="n">
-        <v>226.3</v>
+        <v>230.2</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>94.7</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-181.19</v>
+        <v>-221.62</v>
       </c>
       <c r="K56" t="n">
-        <v>23.71</v>
+        <v>-14.33</v>
       </c>
       <c r="L56" t="n">
-        <v>182.73</v>
+        <v>222.08</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>4.48</v>
       </c>
       <c r="F57" t="n">
-        <v>11.85</v>
+        <v>12.16</v>
       </c>
       <c r="G57" t="n">
-        <v>235.7</v>
+        <v>234.8</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-61.35</v>
+        <v>-97.68000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>267.15</v>
+        <v>260.34</v>
       </c>
       <c r="L57" t="n">
-        <v>274.1</v>
+        <v>278.06</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>4.29</v>
       </c>
       <c r="F58" t="n">
-        <v>11.98</v>
+        <v>13.57</v>
       </c>
       <c r="G58" t="n">
-        <v>220.7</v>
+        <v>237.3</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-206.8</v>
+        <v>-283.11</v>
       </c>
       <c r="K58" t="n">
-        <v>-105.43</v>
+        <v>-134.78</v>
       </c>
       <c r="L58" t="n">
-        <v>232.13</v>
+        <v>313.56</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>4.51</v>
       </c>
       <c r="F59" t="n">
-        <v>11.55</v>
+        <v>13.16</v>
       </c>
       <c r="G59" t="n">
-        <v>242.1</v>
+        <v>228.7</v>
       </c>
       <c r="H59" t="n">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>50.28</v>
+        <v>59.55</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.9</v>
+        <v>-12.45</v>
       </c>
       <c r="L59" t="n">
-        <v>50.75</v>
+        <v>60.84</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>4.93</v>
       </c>
       <c r="F60" t="n">
-        <v>11.97</v>
+        <v>13.57</v>
       </c>
       <c r="G60" t="n">
-        <v>227.9</v>
+        <v>237.2</v>
       </c>
       <c r="H60" t="n">
-        <v>97.7</v>
+        <v>95.5</v>
       </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-62.35</v>
+        <v>-66.91</v>
       </c>
       <c r="K60" t="n">
-        <v>60.21</v>
+        <v>62.86</v>
       </c>
       <c r="L60" t="n">
-        <v>86.68000000000001</v>
+        <v>91.81</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>4.68</v>
       </c>
       <c r="F61" t="n">
-        <v>11.48</v>
+        <v>13.57</v>
       </c>
       <c r="G61" t="n">
-        <v>238.8</v>
+        <v>227.4</v>
       </c>
       <c r="H61" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-52.62</v>
+        <v>-57.56</v>
       </c>
       <c r="K61" t="n">
-        <v>-28.4</v>
+        <v>-32.56</v>
       </c>
       <c r="L61" t="n">
-        <v>59.79</v>
+        <v>66.13</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>3.79</v>
       </c>
       <c r="F62" t="n">
-        <v>11.55</v>
+        <v>10.49</v>
       </c>
       <c r="G62" t="n">
-        <v>250.5</v>
+        <v>228.9</v>
       </c>
       <c r="H62" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.23</v>
+        <v>-7.72</v>
       </c>
       <c r="K62" t="n">
-        <v>-61.05</v>
+        <v>-71.06</v>
       </c>
       <c r="L62" t="n">
-        <v>61.2</v>
+        <v>71.48</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>3.64</v>
       </c>
       <c r="F63" t="n">
-        <v>12.06</v>
+        <v>10.18</v>
       </c>
       <c r="G63" t="n">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="H63" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-22.46</v>
+        <v>-24.27</v>
       </c>
       <c r="K63" t="n">
-        <v>-85.81999999999999</v>
+        <v>-86.15000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>88.70999999999999</v>
+        <v>89.51000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>4.38</v>
       </c>
       <c r="F64" t="n">
-        <v>11.13</v>
+        <v>12.73</v>
       </c>
       <c r="G64" t="n">
-        <v>229.8</v>
+        <v>220.4</v>
       </c>
       <c r="H64" t="n">
-        <v>98.3</v>
+        <v>96.5</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-26.51</v>
+        <v>-33.66</v>
       </c>
       <c r="K64" t="n">
-        <v>-53.15</v>
+        <v>-65.70999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>59.39</v>
+        <v>73.83</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>4.08</v>
       </c>
       <c r="F65" t="n">
-        <v>11.61</v>
+        <v>10.51</v>
       </c>
       <c r="G65" t="n">
-        <v>235.1</v>
+        <v>230</v>
       </c>
       <c r="H65" t="n">
-        <v>93.7</v>
+        <v>99.2</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-92.27</v>
+        <v>-108.2</v>
       </c>
       <c r="K65" t="n">
-        <v>11.95</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>93.04000000000001</v>
+        <v>108.58</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>4.54</v>
       </c>
       <c r="F66" t="n">
-        <v>11.33</v>
+        <v>11.91</v>
       </c>
       <c r="G66" t="n">
-        <v>241</v>
+        <v>224.4</v>
       </c>
       <c r="H66" t="n">
-        <v>95.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-137.96</v>
+        <v>-159.94</v>
       </c>
       <c r="K66" t="n">
-        <v>-18.52</v>
+        <v>-36.59</v>
       </c>
       <c r="L66" t="n">
-        <v>139.2</v>
+        <v>164.07</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>4.85</v>
       </c>
       <c r="F67" t="n">
-        <v>11.52</v>
+        <v>13.57</v>
       </c>
       <c r="G67" t="n">
-        <v>241.1</v>
+        <v>228.3</v>
       </c>
       <c r="H67" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>3.51</v>
+        <v>-18.8</v>
       </c>
       <c r="K67" t="n">
-        <v>108.98</v>
+        <v>131.98</v>
       </c>
       <c r="L67" t="n">
-        <v>109.04</v>
+        <v>133.32</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>4.32</v>
       </c>
       <c r="F68" t="n">
-        <v>11.46</v>
+        <v>13.1</v>
       </c>
       <c r="G68" t="n">
-        <v>236.5</v>
+        <v>227</v>
       </c>
       <c r="H68" t="n">
-        <v>99.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="I68" t="n">
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-75.98999999999999</v>
+        <v>-138.37</v>
       </c>
       <c r="K68" t="n">
-        <v>83.64</v>
+        <v>23.18</v>
       </c>
       <c r="L68" t="n">
-        <v>113.01</v>
+        <v>140.3</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>4.22</v>
       </c>
       <c r="F69" t="n">
-        <v>11</v>
+        <v>8.84</v>
       </c>
       <c r="G69" t="n">
-        <v>241.4</v>
+        <v>217.7</v>
       </c>
       <c r="H69" t="n">
         <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-65.08</v>
+        <v>-94.81999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>144.67</v>
+        <v>137.33</v>
       </c>
       <c r="L69" t="n">
-        <v>158.63</v>
+        <v>166.88</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>4.46</v>
       </c>
       <c r="F70" t="n">
-        <v>12.11</v>
+        <v>12.43</v>
       </c>
       <c r="G70" t="n">
-        <v>228.3</v>
+        <v>239.9</v>
       </c>
       <c r="H70" t="n">
-        <v>96.8</v>
+        <v>95.8</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-165.63</v>
+        <v>-200.62</v>
       </c>
       <c r="K70" t="n">
-        <v>122.91</v>
+        <v>117</v>
       </c>
       <c r="L70" t="n">
-        <v>206.25</v>
+        <v>232.25</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>4.19</v>
       </c>
       <c r="F71" t="n">
-        <v>11.01</v>
+        <v>12.41</v>
       </c>
       <c r="G71" t="n">
-        <v>221.7</v>
+        <v>217.9</v>
       </c>
       <c r="H71" t="n">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-140.38</v>
+        <v>-174.77</v>
       </c>
       <c r="K71" t="n">
-        <v>222.83</v>
+        <v>210.69</v>
       </c>
       <c r="L71" t="n">
-        <v>263.36</v>
+        <v>273.74</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>4.56</v>
       </c>
       <c r="F72" t="n">
-        <v>11.44</v>
+        <v>13.57</v>
       </c>
       <c r="G72" t="n">
-        <v>246.3</v>
+        <v>226.7</v>
       </c>
       <c r="H72" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-311.71</v>
+        <v>-343.22</v>
       </c>
       <c r="K72" t="n">
-        <v>126.67</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>336.47</v>
+        <v>357.24</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>4.99</v>
       </c>
       <c r="F73" t="n">
-        <v>11.53</v>
+        <v>13.57</v>
       </c>
       <c r="G73" t="n">
-        <v>233.1</v>
+        <v>228.4</v>
       </c>
       <c r="H73" t="n">
-        <v>92.5</v>
+        <v>98.2</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-186.3</v>
+        <v>-245.63</v>
       </c>
       <c r="K73" t="n">
-        <v>-178.05</v>
+        <v>-241.5</v>
       </c>
       <c r="L73" t="n">
-        <v>257.71</v>
+        <v>344.46</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>5.42</v>
       </c>
       <c r="F74" t="n">
-        <v>11.36</v>
+        <v>13.57</v>
       </c>
       <c r="G74" t="n">
-        <v>229.7</v>
+        <v>225</v>
       </c>
       <c r="H74" t="n">
-        <v>100</v>
+        <v>96.5</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>65.69</v>
+        <v>73.7</v>
       </c>
       <c r="K74" t="n">
-        <v>-58.99</v>
+        <v>-68.23999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>88.29000000000001</v>
+        <v>100.44</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>4.41</v>
       </c>
       <c r="F75" t="n">
-        <v>11.65</v>
+        <v>13.57</v>
       </c>
       <c r="G75" t="n">
-        <v>230.9</v>
+        <v>230.8</v>
       </c>
       <c r="H75" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-47.86</v>
+        <v>-54.22</v>
       </c>
       <c r="K75" t="n">
-        <v>72.65000000000001</v>
+        <v>79.92</v>
       </c>
       <c r="L75" t="n">
-        <v>87</v>
+        <v>96.58</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>4.79</v>
       </c>
       <c r="F76" t="n">
-        <v>11.81</v>
+        <v>13.57</v>
       </c>
       <c r="G76" t="n">
-        <v>231.6</v>
+        <v>233.9</v>
       </c>
       <c r="H76" t="n">
-        <v>97</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>69.66</v>
+        <v>75.78</v>
       </c>
       <c r="K76" t="n">
-        <v>-35.89</v>
+        <v>-40.52</v>
       </c>
       <c r="L76" t="n">
-        <v>78.36</v>
+        <v>85.93000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>4.57</v>
       </c>
       <c r="F77" t="n">
-        <v>12.11</v>
+        <v>10.34</v>
       </c>
       <c r="G77" t="n">
-        <v>247.8</v>
+        <v>239.9</v>
       </c>
       <c r="H77" t="n">
         <v>100</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>100.49</v>
+        <v>102.8</v>
       </c>
       <c r="K77" t="n">
-        <v>24.41</v>
+        <v>23.53</v>
       </c>
       <c r="L77" t="n">
-        <v>103.41</v>
+        <v>105.46</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>4.94</v>
       </c>
       <c r="F78" t="n">
-        <v>12.13</v>
+        <v>13.57</v>
       </c>
       <c r="G78" t="n">
-        <v>232.7</v>
+        <v>240.5</v>
       </c>
       <c r="H78" t="n">
-        <v>99.7</v>
+        <v>98</v>
       </c>
       <c r="I78" t="n">
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>30.03</v>
+        <v>28.66</v>
       </c>
       <c r="K78" t="n">
-        <v>-72.05</v>
+        <v>-84</v>
       </c>
       <c r="L78" t="n">
-        <v>78.05</v>
+        <v>88.75</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>4.83</v>
       </c>
       <c r="F79" t="n">
-        <v>10.87</v>
+        <v>13.57</v>
       </c>
       <c r="G79" t="n">
-        <v>241</v>
+        <v>215.2</v>
       </c>
       <c r="H79" t="n">
         <v>100</v>
       </c>
       <c r="I79" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>19.7</v>
+        <v>23</v>
       </c>
       <c r="K79" t="n">
-        <v>-105.38</v>
+        <v>-133</v>
       </c>
       <c r="L79" t="n">
-        <v>107.2</v>
+        <v>134.98</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>4.55</v>
       </c>
       <c r="F80" t="n">
-        <v>12.33</v>
+        <v>11.58</v>
       </c>
       <c r="G80" t="n">
-        <v>226</v>
+        <v>244.5</v>
       </c>
       <c r="H80" t="n">
-        <v>93.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>22.91</v>
+        <v>2.45</v>
       </c>
       <c r="K80" t="n">
-        <v>130.29</v>
+        <v>136.33</v>
       </c>
       <c r="L80" t="n">
-        <v>132.28</v>
+        <v>136.35</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>4.65</v>
       </c>
       <c r="F81" t="n">
-        <v>11.65</v>
+        <v>13.25</v>
       </c>
       <c r="G81" t="n">
-        <v>233.7</v>
+        <v>230.7</v>
       </c>
       <c r="H81" t="n">
-        <v>94.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-33.47</v>
+        <v>-52.47</v>
       </c>
       <c r="K81" t="n">
-        <v>-105.52</v>
+        <v>-127.07</v>
       </c>
       <c r="L81" t="n">
-        <v>110.7</v>
+        <v>137.48</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>4.35</v>
       </c>
       <c r="F82" t="n">
-        <v>11.3</v>
+        <v>13.57</v>
       </c>
       <c r="G82" t="n">
-        <v>225.8</v>
+        <v>223.9</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>21.4</v>
+        <v>4.62</v>
       </c>
       <c r="K82" t="n">
-        <v>98.76000000000001</v>
+        <v>109.94</v>
       </c>
       <c r="L82" t="n">
-        <v>101.05</v>
+        <v>110.03</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>5.77</v>
       </c>
       <c r="F83" t="n">
-        <v>11.51</v>
+        <v>13.57</v>
       </c>
       <c r="G83" t="n">
-        <v>237.3</v>
+        <v>228</v>
       </c>
       <c r="H83" t="n">
         <v>100</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>224.28</v>
+        <v>224.51</v>
       </c>
       <c r="K83" t="n">
-        <v>1.96</v>
+        <v>-30.29</v>
       </c>
       <c r="L83" t="n">
-        <v>224.29</v>
+        <v>226.55</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>5.08</v>
       </c>
       <c r="F84" t="n">
-        <v>12.06</v>
+        <v>13.57</v>
       </c>
       <c r="G84" t="n">
-        <v>222.8</v>
+        <v>239</v>
       </c>
       <c r="H84" t="n">
-        <v>96.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="I84" t="n">
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-87.16</v>
+        <v>-123.82</v>
       </c>
       <c r="K84" t="n">
-        <v>232.46</v>
+        <v>241.5</v>
       </c>
       <c r="L84" t="n">
-        <v>248.26</v>
+        <v>271.39</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>4.94</v>
       </c>
       <c r="F85" t="n">
-        <v>10.9</v>
+        <v>12.87</v>
       </c>
       <c r="G85" t="n">
-        <v>241.6</v>
+        <v>215.9</v>
       </c>
       <c r="H85" t="n">
-        <v>91.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-140.29</v>
+        <v>-160.6</v>
       </c>
       <c r="K85" t="n">
-        <v>-146.03</v>
+        <v>-191.76</v>
       </c>
       <c r="L85" t="n">
-        <v>202.5</v>
+        <v>250.13</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>4.53</v>
       </c>
       <c r="F86" t="n">
-        <v>12.23</v>
+        <v>11.64</v>
       </c>
       <c r="G86" t="n">
-        <v>235.8</v>
+        <v>242.3</v>
       </c>
       <c r="H86" t="n">
-        <v>93.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>5</v>
+        <v>-91.94</v>
       </c>
       <c r="K86" t="n">
-        <v>187.49</v>
+        <v>206.07</v>
       </c>
       <c r="L86" t="n">
-        <v>187.56</v>
+        <v>225.65</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>4.87</v>
       </c>
       <c r="F87" t="n">
-        <v>11.04</v>
+        <v>13.57</v>
       </c>
       <c r="G87" t="n">
-        <v>236.5</v>
+        <v>218.6</v>
       </c>
       <c r="H87" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I87" t="n">
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-36.59</v>
+        <v>-50.93</v>
       </c>
       <c r="K87" t="n">
-        <v>-310.58</v>
+        <v>-369.05</v>
       </c>
       <c r="L87" t="n">
-        <v>312.73</v>
+        <v>372.55</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>4.61</v>
       </c>
       <c r="F88" t="n">
-        <v>11.4</v>
+        <v>12.55</v>
       </c>
       <c r="G88" t="n">
-        <v>235.7</v>
+        <v>225.9</v>
       </c>
       <c r="H88" t="n">
-        <v>95.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I88" t="n">
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>105.3</v>
+        <v>102.67</v>
       </c>
       <c r="K88" t="n">
-        <v>257.3</v>
+        <v>280.06</v>
       </c>
       <c r="L88" t="n">
-        <v>278.01</v>
+        <v>298.28</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-53.22</v>
+        <v>-53.04</v>
       </c>
       <c r="K14" t="n">
-        <v>63.44</v>
+        <v>63.23</v>
       </c>
       <c r="L14" t="n">
-        <v>82.81</v>
+        <v>82.53</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>75.5</v>
+        <v>78.16</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.99</v>
+        <v>-3.09</v>
       </c>
       <c r="L15" t="n">
-        <v>75.56</v>
+        <v>78.22</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-36.92</v>
+        <v>-36.06</v>
       </c>
       <c r="K16" t="n">
-        <v>56.39</v>
+        <v>55.08</v>
       </c>
       <c r="L16" t="n">
-        <v>67.41</v>
+        <v>65.83</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>13.39</v>
+        <v>13.9</v>
       </c>
       <c r="K17" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="L17" t="n">
-        <v>13.39</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>72.79000000000001</v>
+        <v>74.14</v>
       </c>
       <c r="K18" t="n">
-        <v>16.7</v>
+        <v>17.01</v>
       </c>
       <c r="L18" t="n">
-        <v>74.68000000000001</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-43.17</v>
+        <v>-44.78</v>
       </c>
       <c r="K19" t="n">
-        <v>52.41</v>
+        <v>54.36</v>
       </c>
       <c r="L19" t="n">
-        <v>67.90000000000001</v>
+        <v>70.43000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>188.64</v>
+        <v>199.18</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="L20" t="n">
-        <v>188.64</v>
+        <v>199.18</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>80.15000000000001</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>104.38</v>
+        <v>104.2</v>
       </c>
       <c r="L21" t="n">
-        <v>131.6</v>
+        <v>131.37</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>129.71</v>
+        <v>136.8</v>
       </c>
       <c r="K22" t="n">
-        <v>115.01</v>
+        <v>121.29</v>
       </c>
       <c r="L22" t="n">
-        <v>173.35</v>
+        <v>182.82</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>126.57</v>
+        <v>118.57</v>
       </c>
       <c r="K23" t="n">
-        <v>74.47</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>146.85</v>
+        <v>137.57</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>70.04000000000001</v>
+        <v>70.06</v>
       </c>
       <c r="K24" t="n">
-        <v>160.17</v>
+        <v>160.24</v>
       </c>
       <c r="L24" t="n">
-        <v>174.82</v>
+        <v>174.89</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-111.24</v>
+        <v>-104.14</v>
       </c>
       <c r="K25" t="n">
-        <v>87.55</v>
+        <v>81.97</v>
       </c>
       <c r="L25" t="n">
-        <v>141.57</v>
+        <v>132.53</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-35.63</v>
+        <v>-37.67</v>
       </c>
       <c r="K26" t="n">
-        <v>280.53</v>
+        <v>296.59</v>
       </c>
       <c r="L26" t="n">
-        <v>282.78</v>
+        <v>298.97</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-230.08</v>
+        <v>-230.76</v>
       </c>
       <c r="K27" t="n">
-        <v>-22.95</v>
+        <v>-23.02</v>
       </c>
       <c r="L27" t="n">
-        <v>231.23</v>
+        <v>231.9</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-231.86</v>
+        <v>-245.78</v>
       </c>
       <c r="K28" t="n">
-        <v>-167.89</v>
+        <v>-177.97</v>
       </c>
       <c r="L28" t="n">
-        <v>286.26</v>
+        <v>303.45</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-73.98</v>
+        <v>-77.88</v>
       </c>
       <c r="K29" t="n">
-        <v>-31.32</v>
+        <v>-32.97</v>
       </c>
       <c r="L29" t="n">
-        <v>80.33</v>
+        <v>84.56999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>27.28</v>
+        <v>26.64</v>
       </c>
       <c r="K30" t="n">
-        <v>59.08</v>
+        <v>57.69</v>
       </c>
       <c r="L30" t="n">
-        <v>65.06999999999999</v>
+        <v>63.54</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="K31" t="n">
-        <v>81.56</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>81.66</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>75.72</v>
+        <v>74</v>
       </c>
       <c r="K32" t="n">
-        <v>-75.75</v>
+        <v>-74.03</v>
       </c>
       <c r="L32" t="n">
-        <v>107.11</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-119.87</v>
+        <v>-112.02</v>
       </c>
       <c r="K33" t="n">
-        <v>58.73</v>
+        <v>54.88</v>
       </c>
       <c r="L33" t="n">
-        <v>133.48</v>
+        <v>124.74</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>99.83</v>
+        <v>97.2</v>
       </c>
       <c r="K34" t="n">
-        <v>-12.73</v>
+        <v>-12.39</v>
       </c>
       <c r="L34" t="n">
-        <v>100.64</v>
+        <v>97.98</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>123.36</v>
+        <v>127.69</v>
       </c>
       <c r="K35" t="n">
-        <v>16.09</v>
+        <v>16.65</v>
       </c>
       <c r="L35" t="n">
-        <v>124.41</v>
+        <v>128.77</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-44.87</v>
+        <v>-44.8</v>
       </c>
       <c r="K36" t="n">
-        <v>136.28</v>
+        <v>136.08</v>
       </c>
       <c r="L36" t="n">
-        <v>143.47</v>
+        <v>143.26</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>96.95999999999999</v>
+        <v>92.77</v>
       </c>
       <c r="K37" t="n">
-        <v>-16.24</v>
+        <v>-15.53</v>
       </c>
       <c r="L37" t="n">
-        <v>98.31</v>
+        <v>94.06</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-151.49</v>
+        <v>-141.95</v>
       </c>
       <c r="K38" t="n">
         <v>-0.01</v>
       </c>
       <c r="L38" t="n">
-        <v>151.49</v>
+        <v>141.95</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="K39" t="n">
-        <v>-19.58</v>
+        <v>-20.52</v>
       </c>
       <c r="L39" t="n">
-        <v>19.6</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-139.58</v>
+        <v>-145.07</v>
       </c>
       <c r="K40" t="n">
-        <v>119.69</v>
+        <v>124.39</v>
       </c>
       <c r="L40" t="n">
-        <v>183.87</v>
+        <v>191.1</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-290.33</v>
+        <v>-309.02</v>
       </c>
       <c r="K41" t="n">
-        <v>-123.14</v>
+        <v>-131.07</v>
       </c>
       <c r="L41" t="n">
-        <v>315.36</v>
+        <v>335.66</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>124.38</v>
+        <v>132.33</v>
       </c>
       <c r="K42" t="n">
-        <v>-154.66</v>
+        <v>-164.54</v>
       </c>
       <c r="L42" t="n">
-        <v>198.47</v>
+        <v>211.15</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-55.69</v>
+        <v>-59.66</v>
       </c>
       <c r="K43" t="n">
-        <v>-258.44</v>
+        <v>-276.86</v>
       </c>
       <c r="L43" t="n">
-        <v>264.37</v>
+        <v>283.22</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-37.08</v>
+        <v>-38.96</v>
       </c>
       <c r="K44" t="n">
-        <v>-61.97</v>
+        <v>-65.11</v>
       </c>
       <c r="L44" t="n">
-        <v>72.22</v>
+        <v>75.87</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-78.43000000000001</v>
+        <v>-81.3</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>78.88</v>
+        <v>81.77</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-56.03</v>
+        <v>-56.79</v>
       </c>
       <c r="K46" t="n">
-        <v>45.72</v>
+        <v>46.34</v>
       </c>
       <c r="L46" t="n">
-        <v>72.31999999999999</v>
+        <v>73.29000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-91.58</v>
+        <v>-89.17</v>
       </c>
       <c r="K47" t="n">
-        <v>-46.88</v>
+        <v>-45.65</v>
       </c>
       <c r="L47" t="n">
-        <v>102.88</v>
+        <v>100.18</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-110.1</v>
+        <v>-102.46</v>
       </c>
       <c r="K48" t="n">
-        <v>-37.89</v>
+        <v>-35.26</v>
       </c>
       <c r="L48" t="n">
-        <v>116.44</v>
+        <v>108.36</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-44.41</v>
+        <v>-41.37</v>
       </c>
       <c r="K49" t="n">
-        <v>-43.54</v>
+        <v>-40.57</v>
       </c>
       <c r="L49" t="n">
-        <v>62.19</v>
+        <v>57.94</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>62.68</v>
+        <v>65</v>
       </c>
       <c r="K50" t="n">
-        <v>84.18000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="L50" t="n">
-        <v>104.95</v>
+        <v>108.84</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-125.64</v>
+        <v>-122.97</v>
       </c>
       <c r="K51" t="n">
-        <v>62.55</v>
+        <v>61.22</v>
       </c>
       <c r="L51" t="n">
-        <v>140.35</v>
+        <v>137.37</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>127.76</v>
+        <v>134.69</v>
       </c>
       <c r="K52" t="n">
-        <v>-77.18000000000001</v>
+        <v>-81.37</v>
       </c>
       <c r="L52" t="n">
-        <v>149.27</v>
+        <v>157.36</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-142.07</v>
+        <v>-145.06</v>
       </c>
       <c r="K53" t="n">
-        <v>104.45</v>
+        <v>106.65</v>
       </c>
       <c r="L53" t="n">
-        <v>176.34</v>
+        <v>180.05</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-67.70999999999999</v>
+        <v>-69.11</v>
       </c>
       <c r="K54" t="n">
-        <v>-161.89</v>
+        <v>-165.23</v>
       </c>
       <c r="L54" t="n">
-        <v>175.48</v>
+        <v>179.1</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>-199.09</v>
+        <v>-199.34</v>
       </c>
       <c r="K55" t="n">
-        <v>35.26</v>
+        <v>35.3</v>
       </c>
       <c r="L55" t="n">
-        <v>202.19</v>
+        <v>202.44</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-221.62</v>
+        <v>-218.07</v>
       </c>
       <c r="K56" t="n">
-        <v>-14.33</v>
+        <v>-14.1</v>
       </c>
       <c r="L56" t="n">
-        <v>222.08</v>
+        <v>218.53</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-97.68000000000001</v>
+        <v>-95</v>
       </c>
       <c r="K57" t="n">
-        <v>260.34</v>
+        <v>253.2</v>
       </c>
       <c r="L57" t="n">
-        <v>278.06</v>
+        <v>270.44</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-283.11</v>
+        <v>-297.85</v>
       </c>
       <c r="K58" t="n">
-        <v>-134.78</v>
+        <v>-141.79</v>
       </c>
       <c r="L58" t="n">
-        <v>313.56</v>
+        <v>329.88</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>59.55</v>
+        <v>60.35</v>
       </c>
       <c r="K59" t="n">
-        <v>-12.45</v>
+        <v>-12.62</v>
       </c>
       <c r="L59" t="n">
-        <v>60.84</v>
+        <v>61.66</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-66.91</v>
+        <v>-63.62</v>
       </c>
       <c r="K60" t="n">
-        <v>62.86</v>
+        <v>59.78</v>
       </c>
       <c r="L60" t="n">
-        <v>91.81</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-57.56</v>
+        <v>-56.01</v>
       </c>
       <c r="K61" t="n">
-        <v>-32.56</v>
+        <v>-31.68</v>
       </c>
       <c r="L61" t="n">
-        <v>66.13</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-7.72</v>
+        <v>-7.38</v>
       </c>
       <c r="K62" t="n">
-        <v>-71.06</v>
+        <v>-67.92</v>
       </c>
       <c r="L62" t="n">
-        <v>71.48</v>
+        <v>68.31999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-24.27</v>
+        <v>-22.68</v>
       </c>
       <c r="K63" t="n">
-        <v>-86.15000000000001</v>
+        <v>-80.5</v>
       </c>
       <c r="L63" t="n">
-        <v>89.51000000000001</v>
+        <v>83.63</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-33.66</v>
+        <v>-33.48</v>
       </c>
       <c r="K64" t="n">
-        <v>-65.70999999999999</v>
+        <v>-65.36</v>
       </c>
       <c r="L64" t="n">
-        <v>73.83</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-108.2</v>
+        <v>-108.05</v>
       </c>
       <c r="K65" t="n">
-        <v>-9.119999999999999</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>108.58</v>
+        <v>108.43</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-159.94</v>
+        <v>-168.65</v>
       </c>
       <c r="K66" t="n">
-        <v>-36.59</v>
+        <v>-38.58</v>
       </c>
       <c r="L66" t="n">
-        <v>164.07</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-18.8</v>
+        <v>-19.48</v>
       </c>
       <c r="K67" t="n">
-        <v>131.98</v>
+        <v>136.73</v>
       </c>
       <c r="L67" t="n">
-        <v>133.32</v>
+        <v>138.11</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-138.37</v>
+        <v>-135.71</v>
       </c>
       <c r="K68" t="n">
-        <v>23.18</v>
+        <v>22.74</v>
       </c>
       <c r="L68" t="n">
-        <v>140.3</v>
+        <v>137.6</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-94.81999999999999</v>
+        <v>-94.92</v>
       </c>
       <c r="K69" t="n">
-        <v>137.33</v>
+        <v>137.49</v>
       </c>
       <c r="L69" t="n">
-        <v>166.88</v>
+        <v>167.07</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-200.62</v>
+        <v>-208.62</v>
       </c>
       <c r="K70" t="n">
-        <v>117</v>
+        <v>121.67</v>
       </c>
       <c r="L70" t="n">
-        <v>232.25</v>
+        <v>241.51</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-174.77</v>
+        <v>-164.77</v>
       </c>
       <c r="K71" t="n">
-        <v>210.69</v>
+        <v>198.63</v>
       </c>
       <c r="L71" t="n">
-        <v>273.74</v>
+        <v>258.08</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-343.22</v>
+        <v>-326.29</v>
       </c>
       <c r="K72" t="n">
-        <v>99.09999999999999</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>357.24</v>
+        <v>339.61</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-245.63</v>
+        <v>-264.29</v>
       </c>
       <c r="K73" t="n">
-        <v>-241.5</v>
+        <v>-259.84</v>
       </c>
       <c r="L73" t="n">
-        <v>344.46</v>
+        <v>370.63</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>73.7</v>
+        <v>74.41</v>
       </c>
       <c r="K74" t="n">
-        <v>-68.23999999999999</v>
+        <v>-68.89</v>
       </c>
       <c r="L74" t="n">
-        <v>100.44</v>
+        <v>101.4</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-54.22</v>
+        <v>-54.98</v>
       </c>
       <c r="K75" t="n">
-        <v>79.92</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>96.58</v>
+        <v>97.93000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>75.78</v>
+        <v>73.7</v>
       </c>
       <c r="K76" t="n">
-        <v>-40.52</v>
+        <v>-39.4</v>
       </c>
       <c r="L76" t="n">
-        <v>85.93000000000001</v>
+        <v>83.56999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>102.8</v>
+        <v>100.08</v>
       </c>
       <c r="K77" t="n">
-        <v>23.53</v>
+        <v>22.91</v>
       </c>
       <c r="L77" t="n">
-        <v>105.46</v>
+        <v>102.67</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>28.66</v>
+        <v>27.86</v>
       </c>
       <c r="K78" t="n">
-        <v>-84</v>
+        <v>-81.65000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>88.75</v>
+        <v>86.28</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>23</v>
+        <v>24.13</v>
       </c>
       <c r="K79" t="n">
-        <v>-133</v>
+        <v>-139.52</v>
       </c>
       <c r="L79" t="n">
-        <v>134.98</v>
+        <v>141.59</v>
       </c>
     </row>
     <row r="80">
@@ -3415,10 +3415,10 @@
         <v>2.45</v>
       </c>
       <c r="K80" t="n">
-        <v>136.33</v>
+        <v>136.05</v>
       </c>
       <c r="L80" t="n">
-        <v>136.35</v>
+        <v>136.07</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-52.47</v>
+        <v>-50.18</v>
       </c>
       <c r="K81" t="n">
-        <v>-127.07</v>
+        <v>-121.51</v>
       </c>
       <c r="L81" t="n">
-        <v>137.48</v>
+        <v>131.46</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>4.62</v>
+        <v>4.42</v>
       </c>
       <c r="K82" t="n">
-        <v>109.94</v>
+        <v>105.17</v>
       </c>
       <c r="L82" t="n">
-        <v>110.03</v>
+        <v>105.26</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>224.51</v>
+        <v>212.49</v>
       </c>
       <c r="K83" t="n">
-        <v>-30.29</v>
+        <v>-28.66</v>
       </c>
       <c r="L83" t="n">
-        <v>226.55</v>
+        <v>214.41</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-123.82</v>
+        <v>-127.42</v>
       </c>
       <c r="K84" t="n">
-        <v>241.5</v>
+        <v>248.53</v>
       </c>
       <c r="L84" t="n">
-        <v>271.39</v>
+        <v>279.29</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-160.6</v>
+        <v>-171.2</v>
       </c>
       <c r="K85" t="n">
-        <v>-191.76</v>
+        <v>-204.42</v>
       </c>
       <c r="L85" t="n">
-        <v>250.13</v>
+        <v>266.64</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-91.94</v>
+        <v>-93.34</v>
       </c>
       <c r="K86" t="n">
-        <v>206.07</v>
+        <v>209.21</v>
       </c>
       <c r="L86" t="n">
-        <v>225.65</v>
+        <v>229.09</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-50.93</v>
+        <v>-53.81</v>
       </c>
       <c r="K87" t="n">
-        <v>-369.05</v>
+        <v>-389.98</v>
       </c>
       <c r="L87" t="n">
-        <v>372.55</v>
+        <v>393.68</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>102.67</v>
+        <v>108.31</v>
       </c>
       <c r="K88" t="n">
-        <v>280.06</v>
+        <v>295.43</v>
       </c>
       <c r="L88" t="n">
-        <v>298.28</v>
+        <v>314.66</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="F14" t="n">
-        <v>9.279999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="G14" t="n">
-        <v>233.3</v>
+        <v>229.7</v>
       </c>
       <c r="H14" t="n">
-        <v>97.2</v>
+        <v>79.2</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-53.04</v>
+        <v>-79.38</v>
       </c>
       <c r="K14" t="n">
-        <v>63.23</v>
+        <v>14.47</v>
       </c>
       <c r="L14" t="n">
-        <v>82.53</v>
+        <v>80.69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:58:51</t>
+          <t>06:59:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.88</v>
+        <v>3.99</v>
       </c>
       <c r="F15" t="n">
-        <v>11.87</v>
+        <v>10.5</v>
       </c>
       <c r="G15" t="n">
-        <v>241.5</v>
+        <v>226</v>
       </c>
       <c r="H15" t="n">
-        <v>97.3</v>
+        <v>61.3</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>78.16</v>
+        <v>-53.12</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.09</v>
+        <v>-32.74</v>
       </c>
       <c r="L15" t="n">
-        <v>78.22</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:59:56</t>
+          <t>07:01:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="F16" t="n">
-        <v>10.03</v>
+        <v>8.68</v>
       </c>
       <c r="G16" t="n">
-        <v>233.2</v>
+        <v>228</v>
       </c>
       <c r="H16" t="n">
-        <v>95.8</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-36.06</v>
+        <v>-85.73</v>
       </c>
       <c r="K16" t="n">
-        <v>55.08</v>
+        <v>20.87</v>
       </c>
       <c r="L16" t="n">
-        <v>65.83</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:04:27</t>
+          <t>07:07:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.29</v>
+        <v>4.37</v>
       </c>
       <c r="F17" t="n">
-        <v>7.11</v>
+        <v>12.92</v>
       </c>
       <c r="G17" t="n">
-        <v>237.6</v>
+        <v>225.1</v>
       </c>
       <c r="H17" t="n">
-        <v>95.5</v>
+        <v>59.4</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>13.9</v>
+        <v>98.64</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2</v>
+        <v>-114.24</v>
       </c>
       <c r="L17" t="n">
-        <v>13.9</v>
+        <v>150.93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:05:51</t>
+          <t>07:09:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.47</v>
+        <v>3.9</v>
       </c>
       <c r="F18" t="n">
-        <v>7.11</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>223.8</v>
+        <v>242.5</v>
       </c>
       <c r="H18" t="n">
-        <v>98.3</v>
+        <v>61</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J18" t="n">
-        <v>74.14</v>
+        <v>-87.95999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>17.01</v>
+        <v>-70.06</v>
       </c>
       <c r="L18" t="n">
-        <v>76.06</v>
+        <v>112.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:08:02</t>
+          <t>07:11:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.48</v>
+        <v>4.18</v>
       </c>
       <c r="F19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>235.6</v>
+        <v>230.2</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-44.78</v>
+        <v>-113.84</v>
       </c>
       <c r="K19" t="n">
-        <v>54.36</v>
+        <v>-76.81</v>
       </c>
       <c r="L19" t="n">
-        <v>70.43000000000001</v>
+        <v>137.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:12:54</t>
+          <t>07:17:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.63</v>
+        <v>3.06</v>
       </c>
       <c r="F20" t="n">
-        <v>12.74</v>
+        <v>6.75</v>
       </c>
       <c r="G20" t="n">
-        <v>248.2</v>
+        <v>227.6</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>59.2</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>199.18</v>
+        <v>83.02</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>199.18</v>
+        <v>105.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:14:38</t>
+          <t>07:18:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.31</v>
+        <v>3.19</v>
       </c>
       <c r="F21" t="n">
-        <v>11.73</v>
+        <v>9.24</v>
       </c>
       <c r="G21" t="n">
-        <v>241.6</v>
+        <v>249.6</v>
       </c>
       <c r="H21" t="n">
-        <v>96.5</v>
+        <v>58.6</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>80.01000000000001</v>
+        <v>-7.09</v>
       </c>
       <c r="K21" t="n">
-        <v>104.2</v>
+        <v>-113.8</v>
       </c>
       <c r="L21" t="n">
-        <v>131.37</v>
+        <v>114.02</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:16:18</t>
+          <t>07:20:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.42</v>
+        <v>4.54</v>
       </c>
       <c r="F22" t="n">
-        <v>9.220000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="G22" t="n">
-        <v>233.6</v>
+        <v>241.5</v>
       </c>
       <c r="H22" t="n">
-        <v>97.2</v>
+        <v>60.6</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J22" t="n">
-        <v>136.8</v>
+        <v>-181</v>
       </c>
       <c r="K22" t="n">
-        <v>121.29</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>182.82</v>
+        <v>206.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:20:48</t>
+          <t>07:24:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.86</v>
+        <v>3.1</v>
       </c>
       <c r="F23" t="n">
-        <v>9.720000000000001</v>
+        <v>7.12</v>
       </c>
       <c r="G23" t="n">
-        <v>221.3</v>
+        <v>229.8</v>
       </c>
       <c r="H23" t="n">
-        <v>94.09999999999999</v>
+        <v>42.2</v>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>118.57</v>
+        <v>146.89</v>
       </c>
       <c r="K23" t="n">
-        <v>69.76000000000001</v>
+        <v>-69.31</v>
       </c>
       <c r="L23" t="n">
-        <v>137.57</v>
+        <v>162.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:21:44</t>
+          <t>07:26:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="F24" t="n">
-        <v>10.92</v>
+        <v>9.07</v>
       </c>
       <c r="G24" t="n">
-        <v>248</v>
+        <v>250.1</v>
       </c>
       <c r="H24" t="n">
-        <v>90.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>70.06</v>
+        <v>31.78</v>
       </c>
       <c r="K24" t="n">
-        <v>160.24</v>
+        <v>-218.96</v>
       </c>
       <c r="L24" t="n">
-        <v>174.89</v>
+        <v>221.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:23:47</t>
+          <t>07:28:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.16</v>
+        <v>3.43</v>
       </c>
       <c r="F25" t="n">
-        <v>10.58</v>
+        <v>7.84</v>
       </c>
       <c r="G25" t="n">
-        <v>245.4</v>
+        <v>237.1</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>85.2</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J25" t="n">
-        <v>-104.14</v>
+        <v>-195.52</v>
       </c>
       <c r="K25" t="n">
-        <v>81.97</v>
+        <v>67.63</v>
       </c>
       <c r="L25" t="n">
-        <v>132.53</v>
+        <v>206.88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:28:46</t>
+          <t>07:32:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.32</v>
+        <v>4.22</v>
       </c>
       <c r="F26" t="n">
-        <v>10.19</v>
+        <v>13.16</v>
       </c>
       <c r="G26" t="n">
-        <v>243.1</v>
+        <v>250.4</v>
       </c>
       <c r="H26" t="n">
-        <v>99.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>-37.67</v>
+        <v>-15.49</v>
       </c>
       <c r="K26" t="n">
-        <v>296.59</v>
+        <v>347.97</v>
       </c>
       <c r="L26" t="n">
-        <v>298.97</v>
+        <v>348.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:30:52</t>
+          <t>07:33:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.6</v>
+        <v>4.82</v>
       </c>
       <c r="F27" t="n">
-        <v>11.91</v>
+        <v>12.94</v>
       </c>
       <c r="G27" t="n">
-        <v>236.5</v>
+        <v>229.6</v>
       </c>
       <c r="H27" t="n">
-        <v>96.90000000000001</v>
+        <v>47.8</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J27" t="n">
-        <v>-230.76</v>
+        <v>-127.19</v>
       </c>
       <c r="K27" t="n">
-        <v>-23.02</v>
+        <v>346.76</v>
       </c>
       <c r="L27" t="n">
-        <v>231.9</v>
+        <v>369.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:33:20</t>
+          <t>07:35:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.64</v>
+        <v>4.66</v>
       </c>
       <c r="F28" t="n">
-        <v>7.97</v>
+        <v>12.09</v>
       </c>
       <c r="G28" t="n">
-        <v>246.9</v>
+        <v>231.1</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-245.78</v>
+        <v>-251.49</v>
       </c>
       <c r="K28" t="n">
-        <v>-177.97</v>
+        <v>-190.09</v>
       </c>
       <c r="L28" t="n">
-        <v>303.45</v>
+        <v>315.24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:43:28</t>
+          <t>07:44:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.01</v>
+        <v>3.57</v>
       </c>
       <c r="F29" t="n">
-        <v>10.76</v>
+        <v>8.91</v>
       </c>
       <c r="G29" t="n">
-        <v>220.6</v>
+        <v>244.5</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J29" t="n">
-        <v>-77.88</v>
+        <v>-2.93</v>
       </c>
       <c r="K29" t="n">
-        <v>-32.97</v>
+        <v>-86.19</v>
       </c>
       <c r="L29" t="n">
-        <v>84.56999999999999</v>
+        <v>86.23999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:44:45</t>
+          <t>07:45:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.92</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>10.82</v>
+        <v>13.57</v>
       </c>
       <c r="G30" t="n">
-        <v>251.5</v>
+        <v>226.4</v>
       </c>
       <c r="H30" t="n">
-        <v>97.09999999999999</v>
+        <v>58.9</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>26.64</v>
+        <v>-52.33</v>
       </c>
       <c r="K30" t="n">
-        <v>57.69</v>
+        <v>-116.69</v>
       </c>
       <c r="L30" t="n">
-        <v>63.54</v>
+        <v>127.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:46:15</t>
+          <t>07:48:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.15</v>
+        <v>4.38</v>
       </c>
       <c r="F31" t="n">
-        <v>9.91</v>
+        <v>12.85</v>
       </c>
       <c r="G31" t="n">
-        <v>234.3</v>
+        <v>220.6</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>74.7</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J31" t="n">
-        <v>3.96</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>81.20999999999999</v>
+        <v>-68.34</v>
       </c>
       <c r="L31" t="n">
-        <v>81.3</v>
+        <v>98.01000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:50:33</t>
+          <t>07:53:41</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="F32" t="n">
-        <v>10.5</v>
+        <v>12.05</v>
       </c>
       <c r="G32" t="n">
-        <v>230.4</v>
+        <v>236.6</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I32" t="n">
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>74</v>
+        <v>-94.05</v>
       </c>
       <c r="K32" t="n">
-        <v>-74.03</v>
+        <v>-61.54</v>
       </c>
       <c r="L32" t="n">
-        <v>104.68</v>
+        <v>112.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:51:07</t>
+          <t>07:55:42</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.61</v>
+        <v>3.77</v>
       </c>
       <c r="F33" t="n">
-        <v>11.72</v>
+        <v>10.51</v>
       </c>
       <c r="G33" t="n">
-        <v>221.1</v>
+        <v>237</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>63.3</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-112.02</v>
+        <v>-49.62</v>
       </c>
       <c r="K33" t="n">
-        <v>54.88</v>
+        <v>63.51</v>
       </c>
       <c r="L33" t="n">
-        <v>124.74</v>
+        <v>80.59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:53:28</t>
+          <t>07:56:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.57</v>
+        <v>3.79</v>
       </c>
       <c r="F34" t="n">
-        <v>8.84</v>
+        <v>10.57</v>
       </c>
       <c r="G34" t="n">
-        <v>243.6</v>
+        <v>228</v>
       </c>
       <c r="H34" t="n">
-        <v>98.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>97.2</v>
+        <v>94.77</v>
       </c>
       <c r="K34" t="n">
-        <v>-12.39</v>
+        <v>49.81</v>
       </c>
       <c r="L34" t="n">
-        <v>97.98</v>
+        <v>107.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:57:44</t>
+          <t>08:01:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.91</v>
+        <v>4.86</v>
       </c>
       <c r="F35" t="n">
-        <v>12.43</v>
+        <v>13.57</v>
       </c>
       <c r="G35" t="n">
-        <v>225</v>
+        <v>217.3</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>127.69</v>
+        <v>198.47</v>
       </c>
       <c r="K35" t="n">
-        <v>16.65</v>
+        <v>37.54</v>
       </c>
       <c r="L35" t="n">
-        <v>128.77</v>
+        <v>201.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:00:29</t>
+          <t>08:03:03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.11</v>
+        <v>4.19</v>
       </c>
       <c r="F36" t="n">
-        <v>12.53</v>
+        <v>11.36</v>
       </c>
       <c r="G36" t="n">
-        <v>240.8</v>
+        <v>241</v>
       </c>
       <c r="H36" t="n">
-        <v>96.90000000000001</v>
+        <v>57.7</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J36" t="n">
-        <v>-44.8</v>
+        <v>-149.72</v>
       </c>
       <c r="K36" t="n">
-        <v>136.08</v>
+        <v>24.26</v>
       </c>
       <c r="L36" t="n">
-        <v>143.26</v>
+        <v>151.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:02:49</t>
+          <t>08:05:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.23</v>
+        <v>3.72</v>
       </c>
       <c r="F37" t="n">
-        <v>9.640000000000001</v>
+        <v>12.29</v>
       </c>
       <c r="G37" t="n">
-        <v>245.4</v>
+        <v>241.4</v>
       </c>
       <c r="H37" t="n">
-        <v>96.09999999999999</v>
+        <v>42.3</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J37" t="n">
-        <v>92.77</v>
+        <v>112.1</v>
       </c>
       <c r="K37" t="n">
-        <v>-15.53</v>
+        <v>-51.72</v>
       </c>
       <c r="L37" t="n">
-        <v>94.06</v>
+        <v>123.46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:07:43</t>
+          <t>08:10:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.05</v>
+        <v>3.78</v>
       </c>
       <c r="F38" t="n">
-        <v>9.31</v>
+        <v>12.78</v>
       </c>
       <c r="G38" t="n">
-        <v>231.9</v>
+        <v>231.4</v>
       </c>
       <c r="H38" t="n">
-        <v>91.3</v>
+        <v>41</v>
       </c>
       <c r="I38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-141.95</v>
+        <v>-182.76</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.01</v>
+        <v>-74.52</v>
       </c>
       <c r="L38" t="n">
-        <v>141.95</v>
+        <v>197.36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:10:04</t>
+          <t>08:11:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.94</v>
+        <v>4.06</v>
       </c>
       <c r="F39" t="n">
-        <v>13.57</v>
+        <v>11.51</v>
       </c>
       <c r="G39" t="n">
-        <v>236.3</v>
+        <v>231.9</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>28.2</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9</v>
+        <v>-75.55</v>
       </c>
       <c r="K39" t="n">
-        <v>-20.52</v>
+        <v>-293.7</v>
       </c>
       <c r="L39" t="n">
-        <v>20.54</v>
+        <v>303.27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:12:39</t>
+          <t>08:13:29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="F40" t="n">
-        <v>7.28</v>
+        <v>12.63</v>
       </c>
       <c r="G40" t="n">
-        <v>217.6</v>
+        <v>234.7</v>
       </c>
       <c r="H40" t="n">
-        <v>99.7</v>
+        <v>69.7</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-145.07</v>
+        <v>269.33</v>
       </c>
       <c r="K40" t="n">
-        <v>124.39</v>
+        <v>-77.06</v>
       </c>
       <c r="L40" t="n">
-        <v>191.1</v>
+        <v>280.14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:16:19</t>
+          <t>08:19:13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.24</v>
+        <v>4.57</v>
       </c>
       <c r="F41" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="G41" t="n">
-        <v>239.7</v>
+        <v>233</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>87.8</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-309.02</v>
+        <v>38.6</v>
       </c>
       <c r="K41" t="n">
-        <v>-131.07</v>
+        <v>-286.58</v>
       </c>
       <c r="L41" t="n">
-        <v>335.66</v>
+        <v>289.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:18:56</t>
+          <t>08:21:03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.16</v>
+        <v>3.91</v>
       </c>
       <c r="F42" t="n">
-        <v>10.87</v>
+        <v>11</v>
       </c>
       <c r="G42" t="n">
-        <v>232.2</v>
+        <v>221.6</v>
       </c>
       <c r="H42" t="n">
-        <v>96.09999999999999</v>
+        <v>62</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>132.33</v>
+        <v>-245.16</v>
       </c>
       <c r="K42" t="n">
-        <v>-164.54</v>
+        <v>-250.71</v>
       </c>
       <c r="L42" t="n">
-        <v>211.15</v>
+        <v>350.65</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:20:16</t>
+          <t>08:22:09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.36</v>
+        <v>4.05</v>
       </c>
       <c r="F43" t="n">
-        <v>11.89</v>
+        <v>10.33</v>
       </c>
       <c r="G43" t="n">
-        <v>230.9</v>
+        <v>228.5</v>
       </c>
       <c r="H43" t="n">
-        <v>87.5</v>
+        <v>39.1</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J43" t="n">
-        <v>-59.66</v>
+        <v>-170.01</v>
       </c>
       <c r="K43" t="n">
-        <v>-276.86</v>
+        <v>-162.05</v>
       </c>
       <c r="L43" t="n">
-        <v>283.22</v>
+        <v>234.87</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:30:20</t>
+          <t>08:36:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.46</v>
+        <v>3.64</v>
       </c>
       <c r="F44" t="n">
-        <v>10.26</v>
+        <v>9.9</v>
       </c>
       <c r="G44" t="n">
-        <v>223.6</v>
+        <v>242.2</v>
       </c>
       <c r="H44" t="n">
-        <v>99.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>-38.96</v>
+        <v>-87.84999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>-65.11</v>
+        <v>23.85</v>
       </c>
       <c r="L44" t="n">
-        <v>75.87</v>
+        <v>91.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:31:36</t>
+          <t>08:37:48</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.61</v>
+        <v>4.2</v>
       </c>
       <c r="F45" t="n">
-        <v>8.25</v>
+        <v>10.47</v>
       </c>
       <c r="G45" t="n">
-        <v>241.6</v>
+        <v>229.6</v>
       </c>
       <c r="H45" t="n">
-        <v>99.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J45" t="n">
-        <v>-81.3</v>
+        <v>-94.20999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.779999999999999</v>
+        <v>51.88</v>
       </c>
       <c r="L45" t="n">
-        <v>81.77</v>
+        <v>107.55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:33:52</t>
+          <t>08:39:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.53</v>
+        <v>4.87</v>
       </c>
       <c r="F46" t="n">
-        <v>13.5</v>
+        <v>12.06</v>
       </c>
       <c r="G46" t="n">
-        <v>230.3</v>
+        <v>223.5</v>
       </c>
       <c r="H46" t="n">
-        <v>99.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>-56.79</v>
+        <v>-94.18000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>46.34</v>
+        <v>-75.94</v>
       </c>
       <c r="L46" t="n">
-        <v>73.29000000000001</v>
+        <v>120.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:37:08</t>
+          <t>08:44:36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
       <c r="F47" t="n">
-        <v>13.57</v>
+        <v>12.41</v>
       </c>
       <c r="G47" t="n">
-        <v>223</v>
+        <v>227.5</v>
       </c>
       <c r="H47" t="n">
-        <v>97.8</v>
+        <v>78</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>-89.17</v>
+        <v>139.12</v>
       </c>
       <c r="K47" t="n">
-        <v>-45.65</v>
+        <v>-57.58</v>
       </c>
       <c r="L47" t="n">
-        <v>100.18</v>
+        <v>150.56</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:38:22</t>
+          <t>08:45:40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.52</v>
+        <v>4.35</v>
       </c>
       <c r="F48" t="n">
-        <v>11.85</v>
+        <v>7.63</v>
       </c>
       <c r="G48" t="n">
-        <v>217.3</v>
+        <v>233.3</v>
       </c>
       <c r="H48" t="n">
-        <v>97.8</v>
+        <v>72.8</v>
       </c>
       <c r="I48" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>-102.46</v>
+        <v>-84.59</v>
       </c>
       <c r="K48" t="n">
-        <v>-35.26</v>
+        <v>100.32</v>
       </c>
       <c r="L48" t="n">
-        <v>108.36</v>
+        <v>131.23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:40:27</t>
+          <t>08:47:55</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.27</v>
+        <v>3.9</v>
       </c>
       <c r="F49" t="n">
-        <v>12.54</v>
+        <v>12.29</v>
       </c>
       <c r="G49" t="n">
-        <v>249.9</v>
+        <v>236</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>96.5</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>-41.37</v>
+        <v>-36.42</v>
       </c>
       <c r="K49" t="n">
-        <v>-40.57</v>
+        <v>-113.56</v>
       </c>
       <c r="L49" t="n">
-        <v>57.94</v>
+        <v>119.26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:44:54</t>
+          <t>08:51:51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.09</v>
+        <v>4.44</v>
       </c>
       <c r="F50" t="n">
-        <v>13.57</v>
+        <v>13.15</v>
       </c>
       <c r="G50" t="n">
-        <v>232.4</v>
+        <v>234</v>
       </c>
       <c r="H50" t="n">
-        <v>88.5</v>
+        <v>76.7</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>65</v>
+        <v>-133.48</v>
       </c>
       <c r="K50" t="n">
-        <v>87.3</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>108.84</v>
+        <v>161.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:45:45</t>
+          <t>08:52:56</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="F51" t="n">
-        <v>12.31</v>
+        <v>10.27</v>
       </c>
       <c r="G51" t="n">
-        <v>237.3</v>
+        <v>233.7</v>
       </c>
       <c r="H51" t="n">
-        <v>95.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="I51" t="n">
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-122.97</v>
+        <v>-16.68</v>
       </c>
       <c r="K51" t="n">
-        <v>61.22</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>137.37</v>
+        <v>92.56</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:47:06</t>
+          <t>08:54:55</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.74</v>
+        <v>4.07</v>
       </c>
       <c r="F52" t="n">
-        <v>11.57</v>
+        <v>11.45</v>
       </c>
       <c r="G52" t="n">
-        <v>235.4</v>
+        <v>235.8</v>
       </c>
       <c r="H52" t="n">
-        <v>95</v>
+        <v>27.4</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>134.69</v>
+        <v>-136.2</v>
       </c>
       <c r="K52" t="n">
-        <v>-81.37</v>
+        <v>165.06</v>
       </c>
       <c r="L52" t="n">
-        <v>157.36</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:51:24</t>
+          <t>08:58:54</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.48</v>
+        <v>5.07</v>
       </c>
       <c r="F53" t="n">
-        <v>13.57</v>
+        <v>12.05</v>
       </c>
       <c r="G53" t="n">
-        <v>228.4</v>
+        <v>227.7</v>
       </c>
       <c r="H53" t="n">
-        <v>91.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>-145.06</v>
+        <v>-251.67</v>
       </c>
       <c r="K53" t="n">
-        <v>106.65</v>
+        <v>12.97</v>
       </c>
       <c r="L53" t="n">
-        <v>180.05</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:52:39</t>
+          <t>09:00:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2308,31 +2308,31 @@
         <v>4.13</v>
       </c>
       <c r="F54" t="n">
-        <v>12.65</v>
+        <v>13.57</v>
       </c>
       <c r="G54" t="n">
-        <v>239.9</v>
+        <v>227.1</v>
       </c>
       <c r="H54" t="n">
-        <v>98.09999999999999</v>
+        <v>45.5</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-69.11</v>
+        <v>-39</v>
       </c>
       <c r="K54" t="n">
-        <v>-165.23</v>
+        <v>-287.79</v>
       </c>
       <c r="L54" t="n">
-        <v>179.1</v>
+        <v>290.42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:55:03</t>
+          <t>09:01:10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.32</v>
+        <v>4.11</v>
       </c>
       <c r="F55" t="n">
-        <v>12.5</v>
+        <v>12.46</v>
       </c>
       <c r="G55" t="n">
-        <v>235.2</v>
+        <v>232.1</v>
       </c>
       <c r="H55" t="n">
-        <v>99.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-199.34</v>
+        <v>-278.82</v>
       </c>
       <c r="K55" t="n">
-        <v>35.3</v>
+        <v>-60.91</v>
       </c>
       <c r="L55" t="n">
-        <v>202.44</v>
+        <v>285.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:00:02</t>
+          <t>09:05:08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.81</v>
+        <v>5.2</v>
       </c>
       <c r="F56" t="n">
-        <v>13.57</v>
+        <v>11.57</v>
       </c>
       <c r="G56" t="n">
-        <v>230.2</v>
+        <v>235.4</v>
       </c>
       <c r="H56" t="n">
-        <v>94.7</v>
+        <v>61.4</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J56" t="n">
-        <v>-218.07</v>
+        <v>12.5</v>
       </c>
       <c r="K56" t="n">
-        <v>-14.1</v>
+        <v>411.13</v>
       </c>
       <c r="L56" t="n">
-        <v>218.53</v>
+        <v>411.32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:01:13</t>
+          <t>09:07:02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="F57" t="n">
-        <v>12.16</v>
+        <v>10.58</v>
       </c>
       <c r="G57" t="n">
-        <v>234.8</v>
+        <v>226.6</v>
       </c>
       <c r="H57" t="n">
-        <v>99.5</v>
+        <v>28.2</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>-95</v>
+        <v>-281.66</v>
       </c>
       <c r="K57" t="n">
-        <v>253.2</v>
+        <v>-136.84</v>
       </c>
       <c r="L57" t="n">
-        <v>270.44</v>
+        <v>313.14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:03:23</t>
+          <t>09:08:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.29</v>
+        <v>5.22</v>
       </c>
       <c r="F58" t="n">
         <v>13.57</v>
       </c>
       <c r="G58" t="n">
-        <v>237.3</v>
+        <v>229.7</v>
       </c>
       <c r="H58" t="n">
-        <v>91.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J58" t="n">
-        <v>-297.85</v>
+        <v>-126.26</v>
       </c>
       <c r="K58" t="n">
-        <v>-141.79</v>
+        <v>-390.52</v>
       </c>
       <c r="L58" t="n">
-        <v>329.88</v>
+        <v>410.42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:15:54</t>
+          <t>09:22:02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.51</v>
+        <v>4.52</v>
       </c>
       <c r="F59" t="n">
-        <v>13.16</v>
+        <v>13.57</v>
       </c>
       <c r="G59" t="n">
-        <v>228.7</v>
+        <v>235.8</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>60.35</v>
+        <v>-43.7</v>
       </c>
       <c r="K59" t="n">
-        <v>-12.62</v>
+        <v>-49.99</v>
       </c>
       <c r="L59" t="n">
-        <v>61.66</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:17:56</t>
+          <t>09:24:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.93</v>
+        <v>4.11</v>
       </c>
       <c r="F60" t="n">
-        <v>13.57</v>
+        <v>11.93</v>
       </c>
       <c r="G60" t="n">
-        <v>237.2</v>
+        <v>237.9</v>
       </c>
       <c r="H60" t="n">
-        <v>95.5</v>
+        <v>77.8</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J60" t="n">
-        <v>-63.62</v>
+        <v>-70.58</v>
       </c>
       <c r="K60" t="n">
-        <v>59.78</v>
+        <v>-53.57</v>
       </c>
       <c r="L60" t="n">
-        <v>87.3</v>
+        <v>88.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:19:17</t>
+          <t>09:25:03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.68</v>
+        <v>4.15</v>
       </c>
       <c r="F61" t="n">
-        <v>13.57</v>
+        <v>11.27</v>
       </c>
       <c r="G61" t="n">
-        <v>227.4</v>
+        <v>235.8</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>90.7</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-56.01</v>
+        <v>21.48</v>
       </c>
       <c r="K61" t="n">
-        <v>-31.68</v>
+        <v>-114.07</v>
       </c>
       <c r="L61" t="n">
-        <v>64.34999999999999</v>
+        <v>116.08</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:23:33</t>
+          <t>09:30:26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.79</v>
+        <v>4.5</v>
       </c>
       <c r="F62" t="n">
-        <v>10.49</v>
+        <v>13.57</v>
       </c>
       <c r="G62" t="n">
-        <v>228.9</v>
+        <v>238.6</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-7.38</v>
+        <v>-104.17</v>
       </c>
       <c r="K62" t="n">
-        <v>-67.92</v>
+        <v>17.74</v>
       </c>
       <c r="L62" t="n">
-        <v>68.31999999999999</v>
+        <v>105.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:25:10</t>
+          <t>09:31:44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.64</v>
+        <v>4.11</v>
       </c>
       <c r="F63" t="n">
-        <v>10.18</v>
+        <v>13.43</v>
       </c>
       <c r="G63" t="n">
-        <v>239</v>
+        <v>248.2</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="I63" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-22.68</v>
+        <v>-51.38</v>
       </c>
       <c r="K63" t="n">
-        <v>-80.5</v>
+        <v>-49.7</v>
       </c>
       <c r="L63" t="n">
-        <v>83.63</v>
+        <v>71.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:26:03</t>
+          <t>09:33:35</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.38</v>
+        <v>3.92</v>
       </c>
       <c r="F64" t="n">
-        <v>12.73</v>
+        <v>13.57</v>
       </c>
       <c r="G64" t="n">
-        <v>220.4</v>
+        <v>219.4</v>
       </c>
       <c r="H64" t="n">
-        <v>96.5</v>
+        <v>68.3</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J64" t="n">
-        <v>-33.48</v>
+        <v>-14.12</v>
       </c>
       <c r="K64" t="n">
-        <v>-65.36</v>
+        <v>-100.06</v>
       </c>
       <c r="L64" t="n">
-        <v>73.44</v>
+        <v>101.06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:30:21</t>
+          <t>09:37:50</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="F65" t="n">
-        <v>10.51</v>
+        <v>11.05</v>
       </c>
       <c r="G65" t="n">
-        <v>230</v>
+        <v>234.3</v>
       </c>
       <c r="H65" t="n">
-        <v>99.2</v>
+        <v>57.4</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J65" t="n">
-        <v>-108.05</v>
+        <v>-124.07</v>
       </c>
       <c r="K65" t="n">
-        <v>-9.109999999999999</v>
+        <v>137.98</v>
       </c>
       <c r="L65" t="n">
-        <v>108.43</v>
+        <v>185.56</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:32:26</t>
+          <t>09:39:14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.54</v>
+        <v>4.24</v>
       </c>
       <c r="F66" t="n">
-        <v>11.91</v>
+        <v>11.55</v>
       </c>
       <c r="G66" t="n">
-        <v>224.4</v>
+        <v>235.2</v>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>58.9</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-168.65</v>
+        <v>-51</v>
       </c>
       <c r="K66" t="n">
-        <v>-38.58</v>
+        <v>164.11</v>
       </c>
       <c r="L66" t="n">
-        <v>173</v>
+        <v>171.85</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:33:10</t>
+          <t>09:40:36</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.85</v>
+        <v>5.22</v>
       </c>
       <c r="F67" t="n">
         <v>13.57</v>
       </c>
       <c r="G67" t="n">
-        <v>228.3</v>
+        <v>220.4</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>54.1</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>-19.48</v>
+        <v>-220.03</v>
       </c>
       <c r="K67" t="n">
-        <v>136.73</v>
+        <v>106.66</v>
       </c>
       <c r="L67" t="n">
-        <v>138.11</v>
+        <v>244.52</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:36:56</t>
+          <t>09:45:24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.32</v>
+        <v>4.53</v>
       </c>
       <c r="F68" t="n">
-        <v>13.1</v>
+        <v>13.57</v>
       </c>
       <c r="G68" t="n">
-        <v>227</v>
+        <v>236.1</v>
       </c>
       <c r="H68" t="n">
-        <v>99.8</v>
+        <v>52.5</v>
       </c>
       <c r="I68" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-135.71</v>
+        <v>-338.29</v>
       </c>
       <c r="K68" t="n">
-        <v>22.74</v>
+        <v>74.88</v>
       </c>
       <c r="L68" t="n">
-        <v>137.6</v>
+        <v>346.47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:38:09</t>
+          <t>09:46:53</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.22</v>
+        <v>4.9</v>
       </c>
       <c r="F69" t="n">
-        <v>8.84</v>
+        <v>13.11</v>
       </c>
       <c r="G69" t="n">
-        <v>217.7</v>
+        <v>258.1</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>55.7</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-94.92</v>
+        <v>-178.6</v>
       </c>
       <c r="K69" t="n">
-        <v>137.49</v>
+        <v>208.27</v>
       </c>
       <c r="L69" t="n">
-        <v>167.07</v>
+        <v>274.36</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:40:31</t>
+          <t>09:47:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.46</v>
+        <v>4.8</v>
       </c>
       <c r="F70" t="n">
-        <v>12.43</v>
+        <v>13.57</v>
       </c>
       <c r="G70" t="n">
-        <v>239.9</v>
+        <v>232.7</v>
       </c>
       <c r="H70" t="n">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-208.62</v>
+        <v>264.97</v>
       </c>
       <c r="K70" t="n">
-        <v>121.67</v>
+        <v>-134.3</v>
       </c>
       <c r="L70" t="n">
-        <v>241.51</v>
+        <v>297.06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:46:12</t>
+          <t>09:51:45</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.19</v>
+        <v>4.31</v>
       </c>
       <c r="F71" t="n">
-        <v>12.41</v>
+        <v>11.37</v>
       </c>
       <c r="G71" t="n">
-        <v>217.9</v>
+        <v>232.7</v>
       </c>
       <c r="H71" t="n">
-        <v>92.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I71" t="n">
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-164.77</v>
+        <v>-127.15</v>
       </c>
       <c r="K71" t="n">
-        <v>198.63</v>
+        <v>-300.85</v>
       </c>
       <c r="L71" t="n">
-        <v>258.08</v>
+        <v>326.61</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:47:08</t>
+          <t>09:53:45</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.56</v>
+        <v>4.87</v>
       </c>
       <c r="F72" t="n">
-        <v>13.57</v>
+        <v>12.81</v>
       </c>
       <c r="G72" t="n">
-        <v>226.7</v>
+        <v>222.5</v>
       </c>
       <c r="H72" t="n">
         <v>100</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J72" t="n">
-        <v>-326.29</v>
+        <v>47.11</v>
       </c>
       <c r="K72" t="n">
-        <v>94.20999999999999</v>
+        <v>-397.43</v>
       </c>
       <c r="L72" t="n">
-        <v>339.61</v>
+        <v>400.22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:49:50</t>
+          <t>09:55:13</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.99</v>
+        <v>4.36</v>
       </c>
       <c r="F73" t="n">
         <v>13.57</v>
       </c>
       <c r="G73" t="n">
-        <v>228.4</v>
+        <v>247.5</v>
       </c>
       <c r="H73" t="n">
-        <v>98.2</v>
+        <v>69.5</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-264.29</v>
+        <v>-60.63</v>
       </c>
       <c r="K73" t="n">
-        <v>-259.84</v>
+        <v>338.45</v>
       </c>
       <c r="L73" t="n">
-        <v>370.63</v>
+        <v>343.84</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:58:07</t>
+          <t>10:04:57</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.42</v>
+        <v>4.79</v>
       </c>
       <c r="F74" t="n">
         <v>13.57</v>
       </c>
       <c r="G74" t="n">
-        <v>225</v>
+        <v>243.7</v>
       </c>
       <c r="H74" t="n">
-        <v>96.5</v>
+        <v>67.5</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>74.41</v>
+        <v>-74.84</v>
       </c>
       <c r="K74" t="n">
-        <v>-68.89</v>
+        <v>-89.45</v>
       </c>
       <c r="L74" t="n">
-        <v>101.4</v>
+        <v>116.63</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:00:34</t>
+          <t>10:06:24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.41</v>
+        <v>5.01</v>
       </c>
       <c r="F75" t="n">
         <v>13.57</v>
       </c>
       <c r="G75" t="n">
-        <v>230.8</v>
+        <v>233.9</v>
       </c>
       <c r="H75" t="n">
-        <v>97</v>
+        <v>55.6</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>-54.98</v>
+        <v>-119.43</v>
       </c>
       <c r="K75" t="n">
-        <v>81.04000000000001</v>
+        <v>72.25</v>
       </c>
       <c r="L75" t="n">
-        <v>97.93000000000001</v>
+        <v>139.58</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:01:49</t>
+          <t>10:07:24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.79</v>
+        <v>4.67</v>
       </c>
       <c r="F76" t="n">
         <v>13.57</v>
       </c>
       <c r="G76" t="n">
-        <v>233.9</v>
+        <v>244.2</v>
       </c>
       <c r="H76" t="n">
-        <v>97.40000000000001</v>
+        <v>58</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J76" t="n">
-        <v>73.7</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-39.4</v>
+        <v>-48.22</v>
       </c>
       <c r="L76" t="n">
-        <v>83.56999999999999</v>
+        <v>103.86</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:07:48</t>
+          <t>10:11:11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.57</v>
+        <v>4.75</v>
       </c>
       <c r="F77" t="n">
-        <v>10.34</v>
+        <v>13.07</v>
       </c>
       <c r="G77" t="n">
-        <v>239.9</v>
+        <v>239.4</v>
       </c>
       <c r="H77" t="n">
-        <v>100</v>
+        <v>58.4</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>100.08</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>22.91</v>
+        <v>96.52</v>
       </c>
       <c r="L77" t="n">
-        <v>102.67</v>
+        <v>121.68</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:10:03</t>
+          <t>10:12:04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.94</v>
+        <v>4.46</v>
       </c>
       <c r="F78" t="n">
-        <v>13.57</v>
+        <v>13.04</v>
       </c>
       <c r="G78" t="n">
-        <v>240.5</v>
+        <v>243.5</v>
       </c>
       <c r="H78" t="n">
-        <v>98</v>
+        <v>60.7</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>27.86</v>
+        <v>-92.78</v>
       </c>
       <c r="K78" t="n">
-        <v>-81.65000000000001</v>
+        <v>12.57</v>
       </c>
       <c r="L78" t="n">
-        <v>86.28</v>
+        <v>93.63</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:12:26</t>
+          <t>10:14:39</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.83</v>
+        <v>4.94</v>
       </c>
       <c r="F79" t="n">
         <v>13.57</v>
       </c>
       <c r="G79" t="n">
-        <v>215.2</v>
+        <v>218.2</v>
       </c>
       <c r="H79" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>24.13</v>
+        <v>98.58</v>
       </c>
       <c r="K79" t="n">
-        <v>-139.52</v>
+        <v>174.71</v>
       </c>
       <c r="L79" t="n">
-        <v>141.59</v>
+        <v>200.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:17:55</t>
+          <t>10:19:23</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.55</v>
+        <v>4.41</v>
       </c>
       <c r="F80" t="n">
-        <v>11.58</v>
+        <v>13.34</v>
       </c>
       <c r="G80" t="n">
-        <v>244.5</v>
+        <v>245.2</v>
       </c>
       <c r="H80" t="n">
-        <v>94.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J80" t="n">
-        <v>2.45</v>
+        <v>32.34</v>
       </c>
       <c r="K80" t="n">
-        <v>136.05</v>
+        <v>-155.58</v>
       </c>
       <c r="L80" t="n">
-        <v>136.07</v>
+        <v>158.91</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:19:50</t>
+          <t>10:20:33</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.65</v>
+        <v>4.76</v>
       </c>
       <c r="F81" t="n">
-        <v>13.25</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>230.7</v>
+        <v>226.7</v>
       </c>
       <c r="H81" t="n">
-        <v>98.5</v>
+        <v>44.9</v>
       </c>
       <c r="I81" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J81" t="n">
-        <v>-50.18</v>
+        <v>-150.9</v>
       </c>
       <c r="K81" t="n">
-        <v>-121.51</v>
+        <v>-214.54</v>
       </c>
       <c r="L81" t="n">
-        <v>131.46</v>
+        <v>262.29</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:22:04</t>
+          <t>10:22:28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.35</v>
+        <v>4.51</v>
       </c>
       <c r="F82" t="n">
-        <v>13.57</v>
+        <v>10.79</v>
       </c>
       <c r="G82" t="n">
-        <v>223.9</v>
+        <v>233.8</v>
       </c>
       <c r="H82" t="n">
-        <v>94.5</v>
+        <v>73.8</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>4.42</v>
+        <v>-84.34999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>105.17</v>
+        <v>-184.54</v>
       </c>
       <c r="L82" t="n">
-        <v>105.26</v>
+        <v>202.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:27:37</t>
+          <t>10:26:36</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.77</v>
+        <v>4.88</v>
       </c>
       <c r="F83" t="n">
         <v>13.57</v>
       </c>
       <c r="G83" t="n">
-        <v>228</v>
+        <v>244.2</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>55.7</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J83" t="n">
-        <v>212.49</v>
+        <v>-220.28</v>
       </c>
       <c r="K83" t="n">
-        <v>-28.66</v>
+        <v>-187.51</v>
       </c>
       <c r="L83" t="n">
-        <v>214.41</v>
+        <v>289.28</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:28:54</t>
+          <t>10:28:42</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.08</v>
+        <v>4.44</v>
       </c>
       <c r="F84" t="n">
-        <v>13.57</v>
+        <v>11.81</v>
       </c>
       <c r="G84" t="n">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="H84" t="n">
-        <v>93</v>
+        <v>50.1</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J84" t="n">
-        <v>-127.42</v>
+        <v>-181.87</v>
       </c>
       <c r="K84" t="n">
-        <v>248.53</v>
+        <v>56.52</v>
       </c>
       <c r="L84" t="n">
-        <v>279.29</v>
+        <v>190.45</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:30:13</t>
+          <t>10:30:38</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.94</v>
+        <v>4.21</v>
       </c>
       <c r="F85" t="n">
-        <v>12.87</v>
+        <v>10.85</v>
       </c>
       <c r="G85" t="n">
-        <v>215.9</v>
+        <v>238</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>48.8</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-171.2</v>
+        <v>-252.12</v>
       </c>
       <c r="K85" t="n">
-        <v>-204.42</v>
+        <v>-34.5</v>
       </c>
       <c r="L85" t="n">
-        <v>266.64</v>
+        <v>254.47</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:35:11</t>
+          <t>10:34:08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.53</v>
+        <v>4.94</v>
       </c>
       <c r="F86" t="n">
-        <v>11.64</v>
+        <v>13.57</v>
       </c>
       <c r="G86" t="n">
-        <v>242.3</v>
+        <v>242.5</v>
       </c>
       <c r="H86" t="n">
-        <v>99.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-93.34</v>
+        <v>-271.32</v>
       </c>
       <c r="K86" t="n">
-        <v>209.21</v>
+        <v>-113.32</v>
       </c>
       <c r="L86" t="n">
-        <v>229.09</v>
+        <v>294.03</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:36:21</t>
+          <t>10:36:05</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.87</v>
+        <v>4.31</v>
       </c>
       <c r="F87" t="n">
         <v>13.57</v>
       </c>
       <c r="G87" t="n">
-        <v>218.6</v>
+        <v>238.4</v>
       </c>
       <c r="H87" t="n">
-        <v>99.8</v>
+        <v>44.8</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-53.81</v>
+        <v>-42.09</v>
       </c>
       <c r="K87" t="n">
-        <v>-389.98</v>
+        <v>-354.24</v>
       </c>
       <c r="L87" t="n">
-        <v>393.68</v>
+        <v>356.73</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:37:22</t>
+          <t>10:38:16</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.61</v>
+        <v>3.83</v>
       </c>
       <c r="F88" t="n">
-        <v>12.55</v>
+        <v>11.63</v>
       </c>
       <c r="G88" t="n">
-        <v>225.9</v>
+        <v>236.5</v>
       </c>
       <c r="H88" t="n">
-        <v>99.40000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J88" t="n">
-        <v>108.31</v>
+        <v>-232.45</v>
       </c>
       <c r="K88" t="n">
-        <v>295.43</v>
+        <v>-155.61</v>
       </c>
       <c r="L88" t="n">
-        <v>314.66</v>
+        <v>279.73</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="F14" t="n">
-        <v>9.06</v>
+        <v>8.19</v>
       </c>
       <c r="G14" t="n">
-        <v>229.7</v>
+        <v>228.3</v>
       </c>
       <c r="H14" t="n">
-        <v>79.2</v>
+        <v>58.7</v>
       </c>
       <c r="I14" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-79.38</v>
+        <v>-48.02</v>
       </c>
       <c r="K14" t="n">
-        <v>14.47</v>
+        <v>18.23</v>
       </c>
       <c r="L14" t="n">
-        <v>80.69</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:59:21</t>
+          <t>06:59:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="F15" t="n">
-        <v>10.5</v>
+        <v>8.52</v>
       </c>
       <c r="G15" t="n">
-        <v>226</v>
+        <v>244.5</v>
       </c>
       <c r="H15" t="n">
-        <v>61.3</v>
+        <v>39.3</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-53.12</v>
+        <v>11.82</v>
       </c>
       <c r="K15" t="n">
-        <v>-32.74</v>
+        <v>-70.14</v>
       </c>
       <c r="L15" t="n">
-        <v>62.4</v>
+        <v>71.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:01:30</t>
+          <t>07:00:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.95</v>
+        <v>3.49</v>
       </c>
       <c r="F16" t="n">
-        <v>8.68</v>
+        <v>10.48</v>
       </c>
       <c r="G16" t="n">
-        <v>228</v>
+        <v>248.6</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>98.8</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-85.73</v>
+        <v>-45.94</v>
       </c>
       <c r="K16" t="n">
-        <v>20.87</v>
+        <v>11.19</v>
       </c>
       <c r="L16" t="n">
-        <v>88.23</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:07:09</t>
+          <t>07:06:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.37</v>
+        <v>4.14</v>
       </c>
       <c r="F17" t="n">
-        <v>12.92</v>
+        <v>13.57</v>
       </c>
       <c r="G17" t="n">
-        <v>225.1</v>
+        <v>240.2</v>
       </c>
       <c r="H17" t="n">
-        <v>59.4</v>
+        <v>29.9</v>
       </c>
       <c r="I17" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>98.64</v>
+        <v>104.14</v>
       </c>
       <c r="K17" t="n">
-        <v>-114.24</v>
+        <v>-6.26</v>
       </c>
       <c r="L17" t="n">
-        <v>150.93</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:09:41</t>
+          <t>07:07:24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="F18" t="n">
-        <v>8.289999999999999</v>
+        <v>13.55</v>
       </c>
       <c r="G18" t="n">
-        <v>242.5</v>
+        <v>220.2</v>
       </c>
       <c r="H18" t="n">
-        <v>61</v>
+        <v>40.4</v>
       </c>
       <c r="I18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-87.95999999999999</v>
+        <v>105.46</v>
       </c>
       <c r="K18" t="n">
-        <v>-70.06</v>
+        <v>19.13</v>
       </c>
       <c r="L18" t="n">
-        <v>112.45</v>
+        <v>107.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:11:24</t>
+          <t>07:09:09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.18</v>
+        <v>4.03</v>
       </c>
       <c r="F19" t="n">
-        <v>9.470000000000001</v>
+        <v>12.79</v>
       </c>
       <c r="G19" t="n">
-        <v>230.2</v>
+        <v>237</v>
       </c>
       <c r="H19" t="n">
-        <v>95.7</v>
+        <v>48.9</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-113.84</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-76.81</v>
+        <v>-69.54000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>137.33</v>
+        <v>95.29000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:17:04</t>
+          <t>07:13:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.06</v>
+        <v>3.92</v>
       </c>
       <c r="F20" t="n">
-        <v>6.75</v>
+        <v>9.56</v>
       </c>
       <c r="G20" t="n">
-        <v>227.6</v>
+        <v>228.3</v>
       </c>
       <c r="H20" t="n">
-        <v>59.2</v>
+        <v>56</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>83.02</v>
+        <v>-126.9</v>
       </c>
       <c r="K20" t="n">
-        <v>65.43000000000001</v>
+        <v>29.27</v>
       </c>
       <c r="L20" t="n">
-        <v>105.71</v>
+        <v>130.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:18:31</t>
+          <t>07:15:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="F21" t="n">
-        <v>9.24</v>
+        <v>11.09</v>
       </c>
       <c r="G21" t="n">
-        <v>249.6</v>
+        <v>228.1</v>
       </c>
       <c r="H21" t="n">
-        <v>58.6</v>
+        <v>55.9</v>
       </c>
       <c r="I21" t="n">
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.09</v>
+        <v>47.18</v>
       </c>
       <c r="K21" t="n">
-        <v>-113.8</v>
+        <v>-48.72</v>
       </c>
       <c r="L21" t="n">
-        <v>114.02</v>
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:20:47</t>
+          <t>07:18:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.54</v>
+        <v>3.69</v>
       </c>
       <c r="F22" t="n">
-        <v>10.8</v>
+        <v>7.66</v>
       </c>
       <c r="G22" t="n">
-        <v>241.5</v>
+        <v>245.7</v>
       </c>
       <c r="H22" t="n">
-        <v>60.6</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-181</v>
+        <v>19.25</v>
       </c>
       <c r="K22" t="n">
-        <v>99.26000000000001</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>206.43</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:24:18</t>
+          <t>07:21:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="F23" t="n">
-        <v>7.12</v>
+        <v>11.88</v>
       </c>
       <c r="G23" t="n">
-        <v>229.8</v>
+        <v>214.2</v>
       </c>
       <c r="H23" t="n">
-        <v>42.2</v>
+        <v>45.9</v>
       </c>
       <c r="I23" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>146.89</v>
+        <v>-139.29</v>
       </c>
       <c r="K23" t="n">
-        <v>-69.31</v>
+        <v>-196.53</v>
       </c>
       <c r="L23" t="n">
-        <v>162.43</v>
+        <v>240.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:26:32</t>
+          <t>07:23:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="F24" t="n">
-        <v>9.07</v>
+        <v>7.88</v>
       </c>
       <c r="G24" t="n">
-        <v>250.1</v>
+        <v>233.4</v>
       </c>
       <c r="H24" t="n">
-        <v>90.90000000000001</v>
+        <v>40.1</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>31.78</v>
+        <v>-232.65</v>
       </c>
       <c r="K24" t="n">
-        <v>-218.96</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>221.25</v>
+        <v>232.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:28:17</t>
+          <t>07:25:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.43</v>
+        <v>4.01</v>
       </c>
       <c r="F25" t="n">
-        <v>7.84</v>
+        <v>10.47</v>
       </c>
       <c r="G25" t="n">
-        <v>237.1</v>
+        <v>243.2</v>
       </c>
       <c r="H25" t="n">
-        <v>85.2</v>
+        <v>32.3</v>
       </c>
       <c r="I25" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-195.52</v>
+        <v>-154.47</v>
       </c>
       <c r="K25" t="n">
-        <v>67.63</v>
+        <v>-113.93</v>
       </c>
       <c r="L25" t="n">
-        <v>206.88</v>
+        <v>191.94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:32:22</t>
+          <t>07:30:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.22</v>
+        <v>3.11</v>
       </c>
       <c r="F26" t="n">
-        <v>13.16</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>250.4</v>
+        <v>229.3</v>
       </c>
       <c r="H26" t="n">
-        <v>82.09999999999999</v>
+        <v>35.4</v>
       </c>
       <c r="I26" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.49</v>
+        <v>-110.25</v>
       </c>
       <c r="K26" t="n">
-        <v>347.97</v>
+        <v>178.09</v>
       </c>
       <c r="L26" t="n">
-        <v>348.31</v>
+        <v>209.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:33:30</t>
+          <t>07:31:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.82</v>
+        <v>4.21</v>
       </c>
       <c r="F27" t="n">
-        <v>12.94</v>
+        <v>10.95</v>
       </c>
       <c r="G27" t="n">
-        <v>229.6</v>
+        <v>236.2</v>
       </c>
       <c r="H27" t="n">
-        <v>47.8</v>
+        <v>50.6</v>
       </c>
       <c r="I27" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>-127.19</v>
+        <v>-262.35</v>
       </c>
       <c r="K27" t="n">
-        <v>346.76</v>
+        <v>47.15</v>
       </c>
       <c r="L27" t="n">
-        <v>369.35</v>
+        <v>266.56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:35:38</t>
+          <t>07:32:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.66</v>
+        <v>4.01</v>
       </c>
       <c r="F28" t="n">
-        <v>12.09</v>
+        <v>10.95</v>
       </c>
       <c r="G28" t="n">
-        <v>231.1</v>
+        <v>245.2</v>
       </c>
       <c r="H28" t="n">
-        <v>39</v>
+        <v>43.6</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>-251.49</v>
+        <v>145.88</v>
       </c>
       <c r="K28" t="n">
-        <v>-190.09</v>
+        <v>196.61</v>
       </c>
       <c r="L28" t="n">
-        <v>315.24</v>
+        <v>244.81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:44:39</t>
+          <t>07:40:38</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.57</v>
+        <v>4.49</v>
       </c>
       <c r="F29" t="n">
-        <v>8.91</v>
+        <v>12.25</v>
       </c>
       <c r="G29" t="n">
-        <v>244.5</v>
+        <v>230.3</v>
       </c>
       <c r="H29" t="n">
-        <v>82.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="I29" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.93</v>
+        <v>-85.8</v>
       </c>
       <c r="K29" t="n">
-        <v>-86.19</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>86.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:45:51</t>
+          <t>07:42:24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="F30" t="n">
-        <v>13.57</v>
+        <v>10.85</v>
       </c>
       <c r="G30" t="n">
-        <v>226.4</v>
+        <v>232</v>
       </c>
       <c r="H30" t="n">
-        <v>58.9</v>
+        <v>54.3</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-52.33</v>
+        <v>-70.75</v>
       </c>
       <c r="K30" t="n">
-        <v>-116.69</v>
+        <v>-45.51</v>
       </c>
       <c r="L30" t="n">
-        <v>127.89</v>
+        <v>84.12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:48:00</t>
+          <t>07:44:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.38</v>
+        <v>4.07</v>
       </c>
       <c r="F31" t="n">
-        <v>12.85</v>
+        <v>10.02</v>
       </c>
       <c r="G31" t="n">
-        <v>220.6</v>
+        <v>224.2</v>
       </c>
       <c r="H31" t="n">
-        <v>74.7</v>
+        <v>68.2</v>
       </c>
       <c r="I31" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>70.23999999999999</v>
+        <v>15.43</v>
       </c>
       <c r="K31" t="n">
-        <v>-68.34</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>98.01000000000001</v>
+        <v>83.69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:53:41</t>
+          <t>07:49:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="F32" t="n">
-        <v>12.05</v>
+        <v>11.44</v>
       </c>
       <c r="G32" t="n">
-        <v>236.6</v>
+        <v>230.8</v>
       </c>
       <c r="H32" t="n">
-        <v>72.59999999999999</v>
+        <v>42</v>
       </c>
       <c r="I32" t="n">
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-94.05</v>
+        <v>10.52</v>
       </c>
       <c r="K32" t="n">
-        <v>-61.54</v>
+        <v>122.68</v>
       </c>
       <c r="L32" t="n">
-        <v>112.4</v>
+        <v>123.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:55:42</t>
+          <t>07:50:43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.77</v>
+        <v>4.59</v>
       </c>
       <c r="F33" t="n">
-        <v>10.51</v>
+        <v>12.19</v>
       </c>
       <c r="G33" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H33" t="n">
-        <v>63.3</v>
+        <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-49.62</v>
+        <v>112.44</v>
       </c>
       <c r="K33" t="n">
-        <v>63.51</v>
+        <v>-0.89</v>
       </c>
       <c r="L33" t="n">
-        <v>80.59</v>
+        <v>112.45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:56:43</t>
+          <t>07:52:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.79</v>
+        <v>4.05</v>
       </c>
       <c r="F34" t="n">
-        <v>10.57</v>
+        <v>10.69</v>
       </c>
       <c r="G34" t="n">
-        <v>228</v>
+        <v>246.4</v>
       </c>
       <c r="H34" t="n">
-        <v>66</v>
+        <v>29.7</v>
       </c>
       <c r="I34" t="n">
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>94.77</v>
+        <v>47.6</v>
       </c>
       <c r="K34" t="n">
-        <v>49.81</v>
+        <v>77.03</v>
       </c>
       <c r="L34" t="n">
-        <v>107.06</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:01:32</t>
+          <t>07:57:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.86</v>
+        <v>4.31</v>
       </c>
       <c r="F35" t="n">
-        <v>13.57</v>
+        <v>13.55</v>
       </c>
       <c r="G35" t="n">
-        <v>217.3</v>
+        <v>232</v>
       </c>
       <c r="H35" t="n">
-        <v>76.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>198.47</v>
+        <v>23.54</v>
       </c>
       <c r="K35" t="n">
-        <v>37.54</v>
+        <v>-127.08</v>
       </c>
       <c r="L35" t="n">
-        <v>201.99</v>
+        <v>129.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:03:03</t>
+          <t>07:59:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.19</v>
+        <v>4.01</v>
       </c>
       <c r="F36" t="n">
-        <v>11.36</v>
+        <v>7.56</v>
       </c>
       <c r="G36" t="n">
-        <v>241</v>
+        <v>226.8</v>
       </c>
       <c r="H36" t="n">
-        <v>57.7</v>
+        <v>65.2</v>
       </c>
       <c r="I36" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-149.72</v>
+        <v>0.1</v>
       </c>
       <c r="K36" t="n">
-        <v>24.26</v>
+        <v>128.36</v>
       </c>
       <c r="L36" t="n">
-        <v>151.67</v>
+        <v>128.36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:05:36</t>
+          <t>08:00:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.72</v>
+        <v>4.27</v>
       </c>
       <c r="F37" t="n">
-        <v>12.29</v>
+        <v>10.11</v>
       </c>
       <c r="G37" t="n">
-        <v>241.4</v>
+        <v>244</v>
       </c>
       <c r="H37" t="n">
-        <v>42.3</v>
+        <v>48.6</v>
       </c>
       <c r="I37" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>112.1</v>
+        <v>-151.88</v>
       </c>
       <c r="K37" t="n">
-        <v>-51.72</v>
+        <v>28.52</v>
       </c>
       <c r="L37" t="n">
-        <v>123.46</v>
+        <v>154.54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:10:22</t>
+          <t>08:04:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.78</v>
+        <v>4.55</v>
       </c>
       <c r="F38" t="n">
-        <v>12.78</v>
+        <v>11.19</v>
       </c>
       <c r="G38" t="n">
-        <v>231.4</v>
+        <v>231</v>
       </c>
       <c r="H38" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-182.76</v>
+        <v>281.38</v>
       </c>
       <c r="K38" t="n">
-        <v>-74.52</v>
+        <v>17.87</v>
       </c>
       <c r="L38" t="n">
-        <v>197.36</v>
+        <v>281.94</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:11:36</t>
+          <t>08:05:09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.06</v>
+        <v>4.91</v>
       </c>
       <c r="F39" t="n">
-        <v>11.51</v>
+        <v>12.83</v>
       </c>
       <c r="G39" t="n">
-        <v>231.9</v>
+        <v>234.8</v>
       </c>
       <c r="H39" t="n">
-        <v>28.2</v>
+        <v>69.7</v>
       </c>
       <c r="I39" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-75.55</v>
+        <v>-90.93000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>-293.7</v>
+        <v>-270.42</v>
       </c>
       <c r="L39" t="n">
-        <v>303.27</v>
+        <v>285.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:13:29</t>
+          <t>08:07:49</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.91</v>
+        <v>4.23</v>
       </c>
       <c r="F40" t="n">
-        <v>12.63</v>
+        <v>11.36</v>
       </c>
       <c r="G40" t="n">
-        <v>234.7</v>
+        <v>238.7</v>
       </c>
       <c r="H40" t="n">
-        <v>69.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>269.33</v>
+        <v>158.93</v>
       </c>
       <c r="K40" t="n">
-        <v>-77.06</v>
+        <v>-191.47</v>
       </c>
       <c r="L40" t="n">
-        <v>280.14</v>
+        <v>248.84</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:19:13</t>
+          <t>08:12:03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.57</v>
+        <v>4.49</v>
       </c>
       <c r="F41" t="n">
-        <v>12.1</v>
+        <v>10.8</v>
       </c>
       <c r="G41" t="n">
-        <v>233</v>
+        <v>238.5</v>
       </c>
       <c r="H41" t="n">
-        <v>87.8</v>
+        <v>99.2</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>38.6</v>
+        <v>316.25</v>
       </c>
       <c r="K41" t="n">
-        <v>-286.58</v>
+        <v>-92.66</v>
       </c>
       <c r="L41" t="n">
-        <v>289.17</v>
+        <v>329.54</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:21:03</t>
+          <t>08:13:21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.91</v>
+        <v>4.51</v>
       </c>
       <c r="F42" t="n">
-        <v>11</v>
+        <v>12.72</v>
       </c>
       <c r="G42" t="n">
-        <v>221.6</v>
+        <v>230.3</v>
       </c>
       <c r="H42" t="n">
         <v>62</v>
       </c>
       <c r="I42" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-245.16</v>
+        <v>-354.68</v>
       </c>
       <c r="K42" t="n">
-        <v>-250.71</v>
+        <v>172.19</v>
       </c>
       <c r="L42" t="n">
-        <v>350.65</v>
+        <v>394.27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:22:09</t>
+          <t>08:15:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.05</v>
+        <v>3.93</v>
       </c>
       <c r="F43" t="n">
-        <v>10.33</v>
+        <v>10.22</v>
       </c>
       <c r="G43" t="n">
-        <v>228.5</v>
+        <v>228.6</v>
       </c>
       <c r="H43" t="n">
-        <v>39.1</v>
+        <v>51.7</v>
       </c>
       <c r="I43" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-170.01</v>
+        <v>-162.11</v>
       </c>
       <c r="K43" t="n">
-        <v>-162.05</v>
+        <v>-160.11</v>
       </c>
       <c r="L43" t="n">
-        <v>234.87</v>
+        <v>227.85</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:36:00</t>
+          <t>08:26:10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.64</v>
+        <v>4.33</v>
       </c>
       <c r="F44" t="n">
-        <v>9.9</v>
+        <v>11.95</v>
       </c>
       <c r="G44" t="n">
-        <v>242.2</v>
+        <v>230.5</v>
       </c>
       <c r="H44" t="n">
-        <v>68.90000000000001</v>
+        <v>38.2</v>
       </c>
       <c r="I44" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>-87.84999999999999</v>
+        <v>-55.73</v>
       </c>
       <c r="K44" t="n">
-        <v>23.85</v>
+        <v>-54.55</v>
       </c>
       <c r="L44" t="n">
-        <v>91.03</v>
+        <v>77.98</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:37:48</t>
+          <t>08:27:41</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="F45" t="n">
-        <v>10.47</v>
+        <v>10.9</v>
       </c>
       <c r="G45" t="n">
-        <v>229.6</v>
+        <v>232.3</v>
       </c>
       <c r="H45" t="n">
-        <v>83.59999999999999</v>
+        <v>49.5</v>
       </c>
       <c r="I45" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-94.20999999999999</v>
+        <v>-14.02</v>
       </c>
       <c r="K45" t="n">
-        <v>51.88</v>
+        <v>-71.2</v>
       </c>
       <c r="L45" t="n">
-        <v>107.55</v>
+        <v>72.56999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:39:35</t>
+          <t>08:28:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.87</v>
+        <v>4.38</v>
       </c>
       <c r="F46" t="n">
-        <v>12.06</v>
+        <v>11.02</v>
       </c>
       <c r="G46" t="n">
-        <v>223.5</v>
+        <v>233.7</v>
       </c>
       <c r="H46" t="n">
-        <v>69.59999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="I46" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-94.18000000000001</v>
+        <v>22.52</v>
       </c>
       <c r="K46" t="n">
-        <v>-75.94</v>
+        <v>81.41</v>
       </c>
       <c r="L46" t="n">
-        <v>120.98</v>
+        <v>84.45999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:44:36</t>
+          <t>08:33:09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.48</v>
+        <v>4.33</v>
       </c>
       <c r="F47" t="n">
-        <v>12.41</v>
+        <v>12.46</v>
       </c>
       <c r="G47" t="n">
-        <v>227.5</v>
+        <v>240.9</v>
       </c>
       <c r="H47" t="n">
-        <v>78</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>139.12</v>
+        <v>-1.91</v>
       </c>
       <c r="K47" t="n">
-        <v>-57.58</v>
+        <v>103.06</v>
       </c>
       <c r="L47" t="n">
-        <v>150.56</v>
+        <v>103.08</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:45:40</t>
+          <t>08:35:14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.35</v>
+        <v>4.59</v>
       </c>
       <c r="F48" t="n">
-        <v>7.63</v>
+        <v>13.17</v>
       </c>
       <c r="G48" t="n">
         <v>233.3</v>
       </c>
       <c r="H48" t="n">
-        <v>72.8</v>
+        <v>58.1</v>
       </c>
       <c r="I48" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-84.59</v>
+        <v>-129.89</v>
       </c>
       <c r="K48" t="n">
-        <v>100.32</v>
+        <v>57.67</v>
       </c>
       <c r="L48" t="n">
-        <v>131.23</v>
+        <v>142.12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:47:55</t>
+          <t>08:36:51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.9</v>
+        <v>4.93</v>
       </c>
       <c r="F49" t="n">
-        <v>12.29</v>
+        <v>13.57</v>
       </c>
       <c r="G49" t="n">
-        <v>236</v>
+        <v>239.8</v>
       </c>
       <c r="H49" t="n">
-        <v>96.5</v>
+        <v>76</v>
       </c>
       <c r="I49" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-36.42</v>
+        <v>200.36</v>
       </c>
       <c r="K49" t="n">
-        <v>-113.56</v>
+        <v>39.3</v>
       </c>
       <c r="L49" t="n">
-        <v>119.26</v>
+        <v>204.18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:51:51</t>
+          <t>08:42:35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.44</v>
+        <v>4.26</v>
       </c>
       <c r="F50" t="n">
-        <v>13.15</v>
+        <v>10.58</v>
       </c>
       <c r="G50" t="n">
-        <v>234</v>
+        <v>237.8</v>
       </c>
       <c r="H50" t="n">
-        <v>76.7</v>
+        <v>74.5</v>
       </c>
       <c r="I50" t="n">
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-133.48</v>
+        <v>6.76</v>
       </c>
       <c r="K50" t="n">
-        <v>90.84999999999999</v>
+        <v>155.49</v>
       </c>
       <c r="L50" t="n">
-        <v>161.46</v>
+        <v>155.64</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:52:56</t>
+          <t>08:44:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="F51" t="n">
-        <v>10.27</v>
+        <v>13.57</v>
       </c>
       <c r="G51" t="n">
-        <v>233.7</v>
+        <v>236.7</v>
       </c>
       <c r="H51" t="n">
-        <v>70.3</v>
+        <v>68.7</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.68</v>
+        <v>-163.83</v>
       </c>
       <c r="K51" t="n">
-        <v>91.04000000000001</v>
+        <v>-81.90000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>92.56</v>
+        <v>183.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:54:55</t>
+          <t>08:46:13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.07</v>
+        <v>4.63</v>
       </c>
       <c r="F52" t="n">
-        <v>11.45</v>
+        <v>13.2</v>
       </c>
       <c r="G52" t="n">
-        <v>235.8</v>
+        <v>245.1</v>
       </c>
       <c r="H52" t="n">
-        <v>27.4</v>
+        <v>83.7</v>
       </c>
       <c r="I52" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-136.2</v>
+        <v>-118.68</v>
       </c>
       <c r="K52" t="n">
-        <v>165.06</v>
+        <v>148.32</v>
       </c>
       <c r="L52" t="n">
-        <v>214</v>
+        <v>189.96</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:58:54</t>
+          <t>08:51:14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.07</v>
+        <v>4.77</v>
       </c>
       <c r="F53" t="n">
-        <v>12.05</v>
+        <v>13.57</v>
       </c>
       <c r="G53" t="n">
-        <v>227.7</v>
+        <v>234.8</v>
       </c>
       <c r="H53" t="n">
-        <v>85.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="I53" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-251.67</v>
+        <v>-180.22</v>
       </c>
       <c r="K53" t="n">
-        <v>12.97</v>
+        <v>210.3</v>
       </c>
       <c r="L53" t="n">
-        <v>252</v>
+        <v>276.95</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:00:01</t>
+          <t>08:53:40</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.13</v>
+        <v>4.51</v>
       </c>
       <c r="F54" t="n">
         <v>13.57</v>
       </c>
       <c r="G54" t="n">
-        <v>227.1</v>
+        <v>240.5</v>
       </c>
       <c r="H54" t="n">
-        <v>45.5</v>
+        <v>96</v>
       </c>
       <c r="I54" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-39</v>
+        <v>-221.91</v>
       </c>
       <c r="K54" t="n">
-        <v>-287.79</v>
+        <v>-62.49</v>
       </c>
       <c r="L54" t="n">
-        <v>290.42</v>
+        <v>230.54</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:01:10</t>
+          <t>08:54:19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.11</v>
+        <v>3.49</v>
       </c>
       <c r="F55" t="n">
-        <v>12.46</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>232.1</v>
+        <v>216.1</v>
       </c>
       <c r="H55" t="n">
-        <v>93.5</v>
+        <v>84</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>-278.82</v>
+        <v>-194.88</v>
       </c>
       <c r="K55" t="n">
-        <v>-60.91</v>
+        <v>-21.29</v>
       </c>
       <c r="L55" t="n">
-        <v>285.4</v>
+        <v>196.04</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:05:08</t>
+          <t>08:59:07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.2</v>
+        <v>4.07</v>
       </c>
       <c r="F56" t="n">
-        <v>11.57</v>
+        <v>13.57</v>
       </c>
       <c r="G56" t="n">
-        <v>235.4</v>
+        <v>218.7</v>
       </c>
       <c r="H56" t="n">
-        <v>61.4</v>
+        <v>42.7</v>
       </c>
       <c r="I56" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>12.5</v>
+        <v>-194.64</v>
       </c>
       <c r="K56" t="n">
-        <v>411.13</v>
+        <v>102.2</v>
       </c>
       <c r="L56" t="n">
-        <v>411.32</v>
+        <v>219.84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:07:02</t>
+          <t>09:01:25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.45</v>
+        <v>4.51</v>
       </c>
       <c r="F57" t="n">
-        <v>10.58</v>
+        <v>12.97</v>
       </c>
       <c r="G57" t="n">
-        <v>226.6</v>
+        <v>247.1</v>
       </c>
       <c r="H57" t="n">
-        <v>28.2</v>
+        <v>68.3</v>
       </c>
       <c r="I57" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-281.66</v>
+        <v>123.69</v>
       </c>
       <c r="K57" t="n">
-        <v>-136.84</v>
+        <v>303.13</v>
       </c>
       <c r="L57" t="n">
-        <v>313.14</v>
+        <v>327.39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:08:00</t>
+          <t>09:03:48</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.22</v>
+        <v>4.59</v>
       </c>
       <c r="F58" t="n">
         <v>13.57</v>
       </c>
       <c r="G58" t="n">
-        <v>229.7</v>
+        <v>216.3</v>
       </c>
       <c r="H58" t="n">
-        <v>65.2</v>
+        <v>44.7</v>
       </c>
       <c r="I58" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-126.26</v>
+        <v>-174.08</v>
       </c>
       <c r="K58" t="n">
-        <v>-390.52</v>
+        <v>-326.21</v>
       </c>
       <c r="L58" t="n">
-        <v>410.42</v>
+        <v>369.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:22:02</t>
+          <t>09:14:02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.52</v>
+        <v>4.25</v>
       </c>
       <c r="F59" t="n">
-        <v>13.57</v>
+        <v>12.15</v>
       </c>
       <c r="G59" t="n">
-        <v>235.8</v>
+        <v>238</v>
       </c>
       <c r="H59" t="n">
-        <v>42.9</v>
+        <v>47.8</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-43.7</v>
+        <v>-17.24</v>
       </c>
       <c r="K59" t="n">
-        <v>-49.99</v>
+        <v>-65.73</v>
       </c>
       <c r="L59" t="n">
-        <v>66.40000000000001</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:24:00</t>
+          <t>09:15:08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.11</v>
+        <v>4.99</v>
       </c>
       <c r="F60" t="n">
-        <v>11.93</v>
+        <v>13.57</v>
       </c>
       <c r="G60" t="n">
-        <v>237.9</v>
+        <v>228.5</v>
       </c>
       <c r="H60" t="n">
-        <v>77.8</v>
+        <v>26.8</v>
       </c>
       <c r="I60" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-70.58</v>
+        <v>22.41</v>
       </c>
       <c r="K60" t="n">
-        <v>-53.57</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>88.61</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:25:03</t>
+          <t>09:16:32</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="F61" t="n">
-        <v>11.27</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>235.8</v>
+        <v>223.1</v>
       </c>
       <c r="H61" t="n">
-        <v>90.7</v>
+        <v>70.5</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>21.48</v>
+        <v>105.23</v>
       </c>
       <c r="K61" t="n">
-        <v>-114.07</v>
+        <v>-38.1</v>
       </c>
       <c r="L61" t="n">
-        <v>116.08</v>
+        <v>111.92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:30:26</t>
+          <t>09:21:49</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.5</v>
+        <v>4.74</v>
       </c>
       <c r="F62" t="n">
         <v>13.57</v>
       </c>
       <c r="G62" t="n">
-        <v>238.6</v>
+        <v>241.4</v>
       </c>
       <c r="H62" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-104.17</v>
+        <v>-138.83</v>
       </c>
       <c r="K62" t="n">
-        <v>17.74</v>
+        <v>113.79</v>
       </c>
       <c r="L62" t="n">
-        <v>105.67</v>
+        <v>179.51</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:31:44</t>
+          <t>09:23:19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.11</v>
+        <v>4.15</v>
       </c>
       <c r="F63" t="n">
-        <v>13.43</v>
+        <v>11.63</v>
       </c>
       <c r="G63" t="n">
-        <v>248.2</v>
+        <v>228.1</v>
       </c>
       <c r="H63" t="n">
-        <v>88.2</v>
+        <v>52.8</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-51.38</v>
+        <v>102.97</v>
       </c>
       <c r="K63" t="n">
-        <v>-49.7</v>
+        <v>-4.68</v>
       </c>
       <c r="L63" t="n">
-        <v>71.48</v>
+        <v>103.07</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:33:35</t>
+          <t>09:24:49</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.92</v>
+        <v>4.48</v>
       </c>
       <c r="F64" t="n">
-        <v>13.57</v>
+        <v>12.13</v>
       </c>
       <c r="G64" t="n">
-        <v>219.4</v>
+        <v>224.6</v>
       </c>
       <c r="H64" t="n">
-        <v>68.3</v>
+        <v>56.1</v>
       </c>
       <c r="I64" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-14.12</v>
+        <v>2.03</v>
       </c>
       <c r="K64" t="n">
-        <v>-100.06</v>
+        <v>-109.92</v>
       </c>
       <c r="L64" t="n">
-        <v>101.06</v>
+        <v>109.94</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:37:50</t>
+          <t>09:29:56</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.06</v>
+        <v>4.73</v>
       </c>
       <c r="F65" t="n">
-        <v>11.05</v>
+        <v>13.57</v>
       </c>
       <c r="G65" t="n">
-        <v>234.3</v>
+        <v>242</v>
       </c>
       <c r="H65" t="n">
-        <v>57.4</v>
+        <v>42</v>
       </c>
       <c r="I65" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-124.07</v>
+        <v>-157.51</v>
       </c>
       <c r="K65" t="n">
-        <v>137.98</v>
+        <v>44.18</v>
       </c>
       <c r="L65" t="n">
-        <v>185.56</v>
+        <v>163.59</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:39:14</t>
+          <t>09:31:33</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.24</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>11.55</v>
+        <v>10</v>
       </c>
       <c r="G66" t="n">
-        <v>235.2</v>
+        <v>232.5</v>
       </c>
       <c r="H66" t="n">
-        <v>58.9</v>
+        <v>69.2</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-51</v>
+        <v>-150.47</v>
       </c>
       <c r="K66" t="n">
-        <v>164.11</v>
+        <v>66.64</v>
       </c>
       <c r="L66" t="n">
-        <v>171.85</v>
+        <v>164.57</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:40:36</t>
+          <t>09:32:31</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.22</v>
+        <v>4.2</v>
       </c>
       <c r="F67" t="n">
         <v>13.57</v>
       </c>
       <c r="G67" t="n">
-        <v>220.4</v>
+        <v>238.8</v>
       </c>
       <c r="H67" t="n">
-        <v>54.1</v>
+        <v>67.2</v>
       </c>
       <c r="I67" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-220.03</v>
+        <v>-59.6</v>
       </c>
       <c r="K67" t="n">
-        <v>106.66</v>
+        <v>168.41</v>
       </c>
       <c r="L67" t="n">
-        <v>244.52</v>
+        <v>178.64</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:45:24</t>
+          <t>09:35:55</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.53</v>
+        <v>4.31</v>
       </c>
       <c r="F68" t="n">
-        <v>13.57</v>
+        <v>13.05</v>
       </c>
       <c r="G68" t="n">
-        <v>236.1</v>
+        <v>219.2</v>
       </c>
       <c r="H68" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-338.29</v>
+        <v>-269.61</v>
       </c>
       <c r="K68" t="n">
-        <v>74.88</v>
+        <v>-23.91</v>
       </c>
       <c r="L68" t="n">
-        <v>346.47</v>
+        <v>270.67</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:46:53</t>
+          <t>09:37:37</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.9</v>
+        <v>4.54</v>
       </c>
       <c r="F69" t="n">
-        <v>13.11</v>
+        <v>13.57</v>
       </c>
       <c r="G69" t="n">
-        <v>258.1</v>
+        <v>234.5</v>
       </c>
       <c r="H69" t="n">
-        <v>55.7</v>
+        <v>2.4</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-178.6</v>
+        <v>-282.39</v>
       </c>
       <c r="K69" t="n">
-        <v>208.27</v>
+        <v>-43.35</v>
       </c>
       <c r="L69" t="n">
-        <v>274.36</v>
+        <v>285.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:47:51</t>
+          <t>09:39:23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.8</v>
+        <v>4.53</v>
       </c>
       <c r="F70" t="n">
         <v>13.57</v>
       </c>
       <c r="G70" t="n">
-        <v>232.7</v>
+        <v>234.4</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>46.2</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>264.97</v>
+        <v>155.29</v>
       </c>
       <c r="K70" t="n">
-        <v>-134.3</v>
+        <v>182.51</v>
       </c>
       <c r="L70" t="n">
-        <v>297.06</v>
+        <v>239.63</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:51:45</t>
+          <t>09:44:41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.31</v>
+        <v>5.15</v>
       </c>
       <c r="F71" t="n">
-        <v>11.37</v>
+        <v>13.54</v>
       </c>
       <c r="G71" t="n">
-        <v>232.7</v>
+        <v>239</v>
       </c>
       <c r="H71" t="n">
-        <v>100</v>
+        <v>81.7</v>
       </c>
       <c r="I71" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-127.15</v>
+        <v>-706.83</v>
       </c>
       <c r="K71" t="n">
-        <v>-300.85</v>
+        <v>419.72</v>
       </c>
       <c r="L71" t="n">
-        <v>326.61</v>
+        <v>822.0599999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:53:45</t>
+          <t>09:46:31</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.87</v>
+        <v>4.9</v>
       </c>
       <c r="F72" t="n">
-        <v>12.81</v>
+        <v>13.57</v>
       </c>
       <c r="G72" t="n">
-        <v>222.5</v>
+        <v>225.7</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>74.5</v>
       </c>
       <c r="I72" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>47.11</v>
+        <v>353.95</v>
       </c>
       <c r="K72" t="n">
-        <v>-397.43</v>
+        <v>-52.26</v>
       </c>
       <c r="L72" t="n">
-        <v>400.22</v>
+        <v>357.79</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:55:13</t>
+          <t>09:47:27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.36</v>
+        <v>5.27</v>
       </c>
       <c r="F73" t="n">
         <v>13.57</v>
       </c>
       <c r="G73" t="n">
-        <v>247.5</v>
+        <v>224.9</v>
       </c>
       <c r="H73" t="n">
-        <v>69.5</v>
+        <v>75.7</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-60.63</v>
+        <v>-3.82</v>
       </c>
       <c r="K73" t="n">
-        <v>338.45</v>
+        <v>-392.24</v>
       </c>
       <c r="L73" t="n">
-        <v>343.84</v>
+        <v>392.26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:04:57</t>
+          <t>09:59:39</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.79</v>
+        <v>4.57</v>
       </c>
       <c r="F74" t="n">
-        <v>13.57</v>
+        <v>10.89</v>
       </c>
       <c r="G74" t="n">
-        <v>243.7</v>
+        <v>229.2</v>
       </c>
       <c r="H74" t="n">
-        <v>67.5</v>
+        <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-74.84</v>
+        <v>40.37</v>
       </c>
       <c r="K74" t="n">
-        <v>-89.45</v>
+        <v>-64.92</v>
       </c>
       <c r="L74" t="n">
-        <v>116.63</v>
+        <v>76.45</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:06:24</t>
+          <t>10:00:56</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.01</v>
+        <v>4.49</v>
       </c>
       <c r="F75" t="n">
-        <v>13.57</v>
+        <v>11.32</v>
       </c>
       <c r="G75" t="n">
-        <v>233.9</v>
+        <v>249.5</v>
       </c>
       <c r="H75" t="n">
-        <v>55.6</v>
+        <v>59.8</v>
       </c>
       <c r="I75" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>-119.43</v>
+        <v>-5.57</v>
       </c>
       <c r="K75" t="n">
-        <v>72.25</v>
+        <v>-116.73</v>
       </c>
       <c r="L75" t="n">
-        <v>139.58</v>
+        <v>116.86</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:07:24</t>
+          <t>10:02:55</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.67</v>
+        <v>4.83</v>
       </c>
       <c r="F76" t="n">
         <v>13.57</v>
       </c>
       <c r="G76" t="n">
-        <v>244.2</v>
+        <v>239.5</v>
       </c>
       <c r="H76" t="n">
-        <v>58</v>
+        <v>73.3</v>
       </c>
       <c r="I76" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>91.98999999999999</v>
+        <v>79.27</v>
       </c>
       <c r="K76" t="n">
-        <v>-48.22</v>
+        <v>-5.95</v>
       </c>
       <c r="L76" t="n">
-        <v>103.86</v>
+        <v>79.48999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:11:11</t>
+          <t>10:07:26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.75</v>
+        <v>5.21</v>
       </c>
       <c r="F77" t="n">
-        <v>13.07</v>
+        <v>13.57</v>
       </c>
       <c r="G77" t="n">
-        <v>239.4</v>
+        <v>225.5</v>
       </c>
       <c r="H77" t="n">
-        <v>58.4</v>
+        <v>79.2</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>74.09999999999999</v>
+        <v>-70.94</v>
       </c>
       <c r="K77" t="n">
-        <v>96.52</v>
+        <v>121.91</v>
       </c>
       <c r="L77" t="n">
-        <v>121.68</v>
+        <v>141.05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:12:04</t>
+          <t>10:09:45</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.46</v>
+        <v>4.35</v>
       </c>
       <c r="F78" t="n">
-        <v>13.04</v>
+        <v>10.66</v>
       </c>
       <c r="G78" t="n">
-        <v>243.5</v>
+        <v>238.5</v>
       </c>
       <c r="H78" t="n">
-        <v>60.7</v>
+        <v>58.8</v>
       </c>
       <c r="I78" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>-92.78</v>
+        <v>-44.38</v>
       </c>
       <c r="K78" t="n">
-        <v>12.57</v>
+        <v>104.88</v>
       </c>
       <c r="L78" t="n">
-        <v>93.63</v>
+        <v>113.88</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:14:39</t>
+          <t>10:10:49</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.94</v>
+        <v>4.25</v>
       </c>
       <c r="F79" t="n">
         <v>13.57</v>
       </c>
       <c r="G79" t="n">
-        <v>218.2</v>
+        <v>239.7</v>
       </c>
       <c r="H79" t="n">
-        <v>77</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>98.58</v>
+        <v>64.92</v>
       </c>
       <c r="K79" t="n">
-        <v>174.71</v>
+        <v>-67.83</v>
       </c>
       <c r="L79" t="n">
-        <v>200.6</v>
+        <v>93.89</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:19:23</t>
+          <t>10:16:50</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.41</v>
+        <v>4.84</v>
       </c>
       <c r="F80" t="n">
-        <v>13.34</v>
+        <v>11.57</v>
       </c>
       <c r="G80" t="n">
-        <v>245.2</v>
+        <v>238.2</v>
       </c>
       <c r="H80" t="n">
-        <v>71.7</v>
+        <v>54.5</v>
       </c>
       <c r="I80" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>32.34</v>
+        <v>-170.8</v>
       </c>
       <c r="K80" t="n">
-        <v>-155.58</v>
+        <v>-119.16</v>
       </c>
       <c r="L80" t="n">
-        <v>158.91</v>
+        <v>208.26</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:20:33</t>
+          <t>10:17:51</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.76</v>
+        <v>4.61</v>
       </c>
       <c r="F81" t="n">
-        <v>9.960000000000001</v>
+        <v>13.57</v>
       </c>
       <c r="G81" t="n">
-        <v>226.7</v>
+        <v>244.2</v>
       </c>
       <c r="H81" t="n">
-        <v>44.9</v>
+        <v>55.5</v>
       </c>
       <c r="I81" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-150.9</v>
+        <v>-93.08</v>
       </c>
       <c r="K81" t="n">
-        <v>-214.54</v>
+        <v>133.89</v>
       </c>
       <c r="L81" t="n">
-        <v>262.29</v>
+        <v>163.07</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:22:28</t>
+          <t>10:18:37</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.51</v>
+        <v>5.06</v>
       </c>
       <c r="F82" t="n">
-        <v>10.79</v>
+        <v>13.57</v>
       </c>
       <c r="G82" t="n">
-        <v>233.8</v>
+        <v>244.9</v>
       </c>
       <c r="H82" t="n">
-        <v>73.8</v>
+        <v>43.9</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-84.34999999999999</v>
+        <v>-4.31</v>
       </c>
       <c r="K82" t="n">
-        <v>-184.54</v>
+        <v>-205.37</v>
       </c>
       <c r="L82" t="n">
-        <v>202.9</v>
+        <v>205.42</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:26:36</t>
+          <t>10:22:08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.88</v>
+        <v>4.81</v>
       </c>
       <c r="F83" t="n">
-        <v>13.57</v>
+        <v>11.85</v>
       </c>
       <c r="G83" t="n">
-        <v>244.2</v>
+        <v>217.5</v>
       </c>
       <c r="H83" t="n">
-        <v>55.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>-220.28</v>
+        <v>114.78</v>
       </c>
       <c r="K83" t="n">
-        <v>-187.51</v>
+        <v>265.63</v>
       </c>
       <c r="L83" t="n">
-        <v>289.28</v>
+        <v>289.37</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:28:42</t>
+          <t>10:24:05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.44</v>
+        <v>4.97</v>
       </c>
       <c r="F84" t="n">
-        <v>11.81</v>
+        <v>13.47</v>
       </c>
       <c r="G84" t="n">
-        <v>221</v>
+        <v>239.3</v>
       </c>
       <c r="H84" t="n">
-        <v>50.1</v>
+        <v>79.8</v>
       </c>
       <c r="I84" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-181.87</v>
+        <v>-27.87</v>
       </c>
       <c r="K84" t="n">
-        <v>56.52</v>
+        <v>-318.04</v>
       </c>
       <c r="L84" t="n">
-        <v>190.45</v>
+        <v>319.26</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:30:38</t>
+          <t>10:25:50</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.21</v>
+        <v>4.88</v>
       </c>
       <c r="F85" t="n">
-        <v>10.85</v>
+        <v>13.57</v>
       </c>
       <c r="G85" t="n">
-        <v>238</v>
+        <v>237.5</v>
       </c>
       <c r="H85" t="n">
-        <v>48.8</v>
+        <v>64.3</v>
       </c>
       <c r="I85" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-252.12</v>
+        <v>-52.15</v>
       </c>
       <c r="K85" t="n">
-        <v>-34.5</v>
+        <v>226.34</v>
       </c>
       <c r="L85" t="n">
-        <v>254.47</v>
+        <v>232.27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:34:08</t>
+          <t>10:30:34</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.94</v>
+        <v>5.34</v>
       </c>
       <c r="F86" t="n">
         <v>13.57</v>
       </c>
       <c r="G86" t="n">
-        <v>242.5</v>
+        <v>240.1</v>
       </c>
       <c r="H86" t="n">
-        <v>67.90000000000001</v>
+        <v>30.7</v>
       </c>
       <c r="I86" t="n">
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-271.32</v>
+        <v>-308.19</v>
       </c>
       <c r="K86" t="n">
-        <v>-113.32</v>
+        <v>154.27</v>
       </c>
       <c r="L86" t="n">
-        <v>294.03</v>
+        <v>344.65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:36:05</t>
+          <t>10:32:59</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.31</v>
+        <v>4.97</v>
       </c>
       <c r="F87" t="n">
         <v>13.57</v>
       </c>
       <c r="G87" t="n">
-        <v>238.4</v>
+        <v>237.1</v>
       </c>
       <c r="H87" t="n">
-        <v>44.8</v>
+        <v>43.9</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-42.09</v>
+        <v>224.86</v>
       </c>
       <c r="K87" t="n">
-        <v>-354.24</v>
+        <v>-19.27</v>
       </c>
       <c r="L87" t="n">
-        <v>356.73</v>
+        <v>225.69</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:38:16</t>
+          <t>10:35:42</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.83</v>
+        <v>4.86</v>
       </c>
       <c r="F88" t="n">
-        <v>11.63</v>
+        <v>12.67</v>
       </c>
       <c r="G88" t="n">
-        <v>236.5</v>
+        <v>216.9</v>
       </c>
       <c r="H88" t="n">
-        <v>13.5</v>
+        <v>41.6</v>
       </c>
       <c r="I88" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-232.45</v>
+        <v>325.04</v>
       </c>
       <c r="K88" t="n">
-        <v>-155.61</v>
+        <v>-84.81</v>
       </c>
       <c r="L88" t="n">
-        <v>279.73</v>
+        <v>335.92</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-48.75</v>
+        <v>-53.86</v>
       </c>
       <c r="K14" t="n">
-        <v>59.73</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>77.09999999999999</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>63.71</v>
+        <v>74.17</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.07</v>
+        <v>-2.41</v>
       </c>
       <c r="L15" t="n">
-        <v>63.74</v>
+        <v>74.20999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-34.25</v>
+        <v>-40.28</v>
       </c>
       <c r="K16" t="n">
-        <v>55.1</v>
+        <v>64.8</v>
       </c>
       <c r="L16" t="n">
-        <v>64.88</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>19.32</v>
+        <v>24.11</v>
       </c>
       <c r="K17" t="n">
-        <v>2.53</v>
+        <v>3.16</v>
       </c>
       <c r="L17" t="n">
-        <v>19.48</v>
+        <v>24.31</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>62.23</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>16.63</v>
+        <v>19.52</v>
       </c>
       <c r="L18" t="n">
-        <v>64.41</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-32.38</v>
+        <v>-41.02</v>
       </c>
       <c r="K19" t="n">
-        <v>50.22</v>
+        <v>63.62</v>
       </c>
       <c r="L19" t="n">
-        <v>59.76</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>164.01</v>
+        <v>185.47</v>
       </c>
       <c r="K20" t="n">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="L20" t="n">
-        <v>164.02</v>
+        <v>185.49</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>81.58</v>
+        <v>100.44</v>
       </c>
       <c r="K21" t="n">
-        <v>90.95999999999999</v>
+        <v>111.99</v>
       </c>
       <c r="L21" t="n">
-        <v>122.19</v>
+        <v>150.44</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>127.87</v>
+        <v>151.61</v>
       </c>
       <c r="K22" t="n">
-        <v>110.71</v>
+        <v>131.26</v>
       </c>
       <c r="L22" t="n">
-        <v>169.14</v>
+        <v>200.53</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>130.35</v>
+        <v>165.03</v>
       </c>
       <c r="K23" t="n">
-        <v>91.54000000000001</v>
+        <v>115.9</v>
       </c>
       <c r="L23" t="n">
-        <v>159.28</v>
+        <v>201.67</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>91</v>
+        <v>112.87</v>
       </c>
       <c r="K24" t="n">
-        <v>136.77</v>
+        <v>169.63</v>
       </c>
       <c r="L24" t="n">
-        <v>164.28</v>
+        <v>203.75</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-66.75</v>
+        <v>-87.22</v>
       </c>
       <c r="K25" t="n">
-        <v>96.25</v>
+        <v>125.76</v>
       </c>
       <c r="L25" t="n">
-        <v>117.13</v>
+        <v>153.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="K26" t="n">
-        <v>248.91</v>
+        <v>309.18</v>
       </c>
       <c r="L26" t="n">
-        <v>248.92</v>
+        <v>309.18</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-175.11</v>
+        <v>-238.39</v>
       </c>
       <c r="K27" t="n">
-        <v>4.75</v>
+        <v>6.46</v>
       </c>
       <c r="L27" t="n">
-        <v>175.17</v>
+        <v>238.48</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-179.45</v>
+        <v>-225.69</v>
       </c>
       <c r="K28" t="n">
-        <v>-143.63</v>
+        <v>-180.63</v>
       </c>
       <c r="L28" t="n">
-        <v>229.85</v>
+        <v>289.07</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>8.119999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>-64.55</v>
+        <v>-73.86</v>
       </c>
       <c r="L29" t="n">
-        <v>65.06</v>
+        <v>74.44</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-51.16</v>
+        <v>-59.78</v>
       </c>
       <c r="K30" t="n">
-        <v>24.42</v>
+        <v>28.54</v>
       </c>
       <c r="L30" t="n">
-        <v>56.69</v>
+        <v>66.23999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-70.36</v>
+        <v>-80.23</v>
       </c>
       <c r="K31" t="n">
-        <v>5.99</v>
+        <v>6.83</v>
       </c>
       <c r="L31" t="n">
-        <v>70.62</v>
+        <v>80.52</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>33.65</v>
+        <v>38.29</v>
       </c>
       <c r="K32" t="n">
-        <v>90.25</v>
+        <v>102.71</v>
       </c>
       <c r="L32" t="n">
-        <v>96.31999999999999</v>
+        <v>109.62</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>17.7</v>
+        <v>18.68</v>
       </c>
       <c r="K33" t="n">
-        <v>-116.43</v>
+        <v>-122.86</v>
       </c>
       <c r="L33" t="n">
-        <v>117.76</v>
+        <v>124.27</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>24.2</v>
+        <v>26.58</v>
       </c>
       <c r="K34" t="n">
-        <v>94.36</v>
+        <v>103.65</v>
       </c>
       <c r="L34" t="n">
-        <v>97.42</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>100.14</v>
+        <v>121.07</v>
       </c>
       <c r="K35" t="n">
-        <v>69.31999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="L35" t="n">
-        <v>121.79</v>
+        <v>147.24</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>136.49</v>
+        <v>162.64</v>
       </c>
       <c r="K36" t="n">
-        <v>-23.46</v>
+        <v>-27.95</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5</v>
+        <v>165.02</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-45.85</v>
+        <v>-58.39</v>
       </c>
       <c r="K37" t="n">
-        <v>89.41</v>
+        <v>113.87</v>
       </c>
       <c r="L37" t="n">
-        <v>100.48</v>
+        <v>127.96</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-131.82</v>
+        <v>-169.27</v>
       </c>
       <c r="K38" t="n">
-        <v>19.28</v>
+        <v>24.76</v>
       </c>
       <c r="L38" t="n">
-        <v>133.22</v>
+        <v>171.07</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>66.90000000000001</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>22.9</v>
+        <v>33.8</v>
       </c>
       <c r="L39" t="n">
-        <v>70.70999999999999</v>
+        <v>104.37</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-112.88</v>
+        <v>-136.1</v>
       </c>
       <c r="K40" t="n">
-        <v>133.37</v>
+        <v>160.81</v>
       </c>
       <c r="L40" t="n">
-        <v>174.73</v>
+        <v>210.67</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-236.96</v>
+        <v>-316.06</v>
       </c>
       <c r="K41" t="n">
-        <v>-92.54000000000001</v>
+        <v>-123.44</v>
       </c>
       <c r="L41" t="n">
-        <v>254.39</v>
+        <v>339.31</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>165.24</v>
+        <v>240.79</v>
       </c>
       <c r="K42" t="n">
-        <v>-50.99</v>
+        <v>-74.3</v>
       </c>
       <c r="L42" t="n">
-        <v>172.93</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>1.71</v>
+        <v>2.42</v>
       </c>
       <c r="K43" t="n">
-        <v>-223.34</v>
+        <v>-315.94</v>
       </c>
       <c r="L43" t="n">
-        <v>223.34</v>
+        <v>315.95</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-30.25</v>
+        <v>-35.02</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.41</v>
+        <v>-58.36</v>
       </c>
       <c r="L44" t="n">
-        <v>58.79</v>
+        <v>68.06</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-69.5</v>
+        <v>-77</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.27</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>69.88</v>
+        <v>77.42</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-44.19</v>
+        <v>-51.81</v>
       </c>
       <c r="K46" t="n">
-        <v>38.15</v>
+        <v>44.73</v>
       </c>
       <c r="L46" t="n">
-        <v>58.38</v>
+        <v>68.45</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-78.09999999999999</v>
+        <v>-87.59</v>
       </c>
       <c r="K47" t="n">
-        <v>-38.21</v>
+        <v>-42.86</v>
       </c>
       <c r="L47" t="n">
-        <v>86.94</v>
+        <v>97.51000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-104.08</v>
+        <v>-111.88</v>
       </c>
       <c r="K48" t="n">
-        <v>-33.66</v>
+        <v>-36.19</v>
       </c>
       <c r="L48" t="n">
-        <v>109.38</v>
+        <v>117.59</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-25.88</v>
+        <v>-33.1</v>
       </c>
       <c r="K49" t="n">
-        <v>-31.76</v>
+        <v>-40.62</v>
       </c>
       <c r="L49" t="n">
-        <v>40.97</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>66.75</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>65.41</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>93.45999999999999</v>
+        <v>123.85</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-98.89</v>
+        <v>-116.92</v>
       </c>
       <c r="K51" t="n">
-        <v>59.2</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>115.26</v>
+        <v>136.27</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>118.27</v>
+        <v>144.14</v>
       </c>
       <c r="K52" t="n">
-        <v>-53.75</v>
+        <v>-65.5</v>
       </c>
       <c r="L52" t="n">
-        <v>129.91</v>
+        <v>158.32</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-101.2</v>
+        <v>-136.16</v>
       </c>
       <c r="K53" t="n">
-        <v>119.32</v>
+        <v>160.54</v>
       </c>
       <c r="L53" t="n">
-        <v>156.46</v>
+        <v>210.51</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-28.17</v>
+        <v>-36.48</v>
       </c>
       <c r="K54" t="n">
-        <v>-133.1</v>
+        <v>-172.38</v>
       </c>
       <c r="L54" t="n">
-        <v>136.05</v>
+        <v>176.2</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-153.89</v>
+        <v>-189.48</v>
       </c>
       <c r="K55" t="n">
-        <v>46.26</v>
+        <v>56.96</v>
       </c>
       <c r="L55" t="n">
-        <v>160.7</v>
+        <v>197.86</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-181.19</v>
+        <v>-253.55</v>
       </c>
       <c r="K56" t="n">
-        <v>23.71</v>
+        <v>33.18</v>
       </c>
       <c r="L56" t="n">
-        <v>182.73</v>
+        <v>255.71</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-61.35</v>
+        <v>-83.44</v>
       </c>
       <c r="K57" t="n">
-        <v>267.15</v>
+        <v>363.32</v>
       </c>
       <c r="L57" t="n">
-        <v>274.1</v>
+        <v>372.78</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-206.8</v>
+        <v>-276.68</v>
       </c>
       <c r="K58" t="n">
-        <v>-105.43</v>
+        <v>-141.06</v>
       </c>
       <c r="L58" t="n">
-        <v>232.13</v>
+        <v>310.57</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>50.28</v>
+        <v>63.21</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.9</v>
+        <v>-8.68</v>
       </c>
       <c r="L59" t="n">
-        <v>50.75</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-62.35</v>
+        <v>-68.43000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>60.21</v>
+        <v>66.08</v>
       </c>
       <c r="L60" t="n">
-        <v>86.68000000000001</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-52.62</v>
+        <v>-63.78</v>
       </c>
       <c r="K61" t="n">
-        <v>-28.4</v>
+        <v>-34.42</v>
       </c>
       <c r="L61" t="n">
-        <v>59.79</v>
+        <v>72.48</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.23</v>
+        <v>-5.19</v>
       </c>
       <c r="K62" t="n">
-        <v>-61.05</v>
+        <v>-74.91</v>
       </c>
       <c r="L62" t="n">
-        <v>61.2</v>
+        <v>75.09</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-22.46</v>
+        <v>-25.72</v>
       </c>
       <c r="K63" t="n">
-        <v>-85.81999999999999</v>
+        <v>-98.28</v>
       </c>
       <c r="L63" t="n">
-        <v>88.70999999999999</v>
+        <v>101.59</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-26.51</v>
+        <v>-33.49</v>
       </c>
       <c r="K64" t="n">
-        <v>-53.15</v>
+        <v>-67.16</v>
       </c>
       <c r="L64" t="n">
-        <v>59.39</v>
+        <v>75.04000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-92.27</v>
+        <v>-121.67</v>
       </c>
       <c r="K65" t="n">
-        <v>11.95</v>
+        <v>15.76</v>
       </c>
       <c r="L65" t="n">
-        <v>93.04000000000001</v>
+        <v>122.69</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-137.96</v>
+        <v>-168.09</v>
       </c>
       <c r="K66" t="n">
-        <v>-18.52</v>
+        <v>-22.57</v>
       </c>
       <c r="L66" t="n">
-        <v>139.2</v>
+        <v>169.59</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>3.51</v>
+        <v>4.51</v>
       </c>
       <c r="K67" t="n">
-        <v>108.98</v>
+        <v>140.11</v>
       </c>
       <c r="L67" t="n">
-        <v>109.04</v>
+        <v>140.18</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-75.98999999999999</v>
+        <v>-105.54</v>
       </c>
       <c r="K68" t="n">
-        <v>83.64</v>
+        <v>116.17</v>
       </c>
       <c r="L68" t="n">
-        <v>113.01</v>
+        <v>156.95</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-65.08</v>
+        <v>-81.51000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>144.67</v>
+        <v>181.18</v>
       </c>
       <c r="L69" t="n">
-        <v>158.63</v>
+        <v>198.67</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-165.63</v>
+        <v>-208.6</v>
       </c>
       <c r="K70" t="n">
-        <v>122.91</v>
+        <v>154.8</v>
       </c>
       <c r="L70" t="n">
-        <v>206.25</v>
+        <v>259.76</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-140.38</v>
+        <v>-183.7</v>
       </c>
       <c r="K71" t="n">
-        <v>222.83</v>
+        <v>291.61</v>
       </c>
       <c r="L71" t="n">
-        <v>263.36</v>
+        <v>344.65</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-311.71</v>
+        <v>-406.4</v>
       </c>
       <c r="K72" t="n">
-        <v>126.67</v>
+        <v>165.15</v>
       </c>
       <c r="L72" t="n">
-        <v>336.47</v>
+        <v>438.67</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-186.3</v>
+        <v>-263.57</v>
       </c>
       <c r="K73" t="n">
-        <v>-178.05</v>
+        <v>-251.9</v>
       </c>
       <c r="L73" t="n">
-        <v>257.71</v>
+        <v>364.58</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>65.69</v>
+        <v>71.72</v>
       </c>
       <c r="K74" t="n">
-        <v>-58.99</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>88.29000000000001</v>
+        <v>96.39</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-47.86</v>
+        <v>-52.85</v>
       </c>
       <c r="K75" t="n">
-        <v>72.65000000000001</v>
+        <v>80.22</v>
       </c>
       <c r="L75" t="n">
-        <v>87</v>
+        <v>96.06999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>69.66</v>
+        <v>77.91</v>
       </c>
       <c r="K76" t="n">
-        <v>-35.89</v>
+        <v>-40.14</v>
       </c>
       <c r="L76" t="n">
-        <v>78.36</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>100.49</v>
+        <v>112.06</v>
       </c>
       <c r="K77" t="n">
-        <v>24.41</v>
+        <v>27.22</v>
       </c>
       <c r="L77" t="n">
-        <v>103.41</v>
+        <v>115.32</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>30.03</v>
+        <v>35.82</v>
       </c>
       <c r="K78" t="n">
-        <v>-72.05</v>
+        <v>-85.93000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>78.05</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>19.7</v>
+        <v>21.53</v>
       </c>
       <c r="K79" t="n">
-        <v>-105.38</v>
+        <v>-115.19</v>
       </c>
       <c r="L79" t="n">
-        <v>107.2</v>
+        <v>117.19</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>22.91</v>
+        <v>28.41</v>
       </c>
       <c r="K80" t="n">
-        <v>130.29</v>
+        <v>161.59</v>
       </c>
       <c r="L80" t="n">
-        <v>132.28</v>
+        <v>164.07</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-33.47</v>
+        <v>-41.92</v>
       </c>
       <c r="K81" t="n">
-        <v>-105.52</v>
+        <v>-132.15</v>
       </c>
       <c r="L81" t="n">
-        <v>110.7</v>
+        <v>138.64</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>21.4</v>
+        <v>27.85</v>
       </c>
       <c r="K82" t="n">
-        <v>98.76000000000001</v>
+        <v>128.52</v>
       </c>
       <c r="L82" t="n">
-        <v>101.05</v>
+        <v>131.51</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>224.28</v>
+        <v>307.8</v>
       </c>
       <c r="K83" t="n">
-        <v>1.96</v>
+        <v>2.69</v>
       </c>
       <c r="L83" t="n">
-        <v>224.29</v>
+        <v>307.81</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-87.16</v>
+        <v>-111.72</v>
       </c>
       <c r="K84" t="n">
-        <v>232.46</v>
+        <v>297.95</v>
       </c>
       <c r="L84" t="n">
-        <v>248.26</v>
+        <v>318.21</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-140.29</v>
+        <v>-184.23</v>
       </c>
       <c r="K85" t="n">
-        <v>-146.03</v>
+        <v>-191.78</v>
       </c>
       <c r="L85" t="n">
-        <v>202.5</v>
+        <v>265.93</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>5</v>
+        <v>7.37</v>
       </c>
       <c r="K86" t="n">
-        <v>187.49</v>
+        <v>276.15</v>
       </c>
       <c r="L86" t="n">
-        <v>187.56</v>
+        <v>276.25</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-36.59</v>
+        <v>-50.66</v>
       </c>
       <c r="K87" t="n">
-        <v>-310.58</v>
+        <v>-429.99</v>
       </c>
       <c r="L87" t="n">
-        <v>312.73</v>
+        <v>432.97</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>105.3</v>
+        <v>145.15</v>
       </c>
       <c r="K88" t="n">
-        <v>257.3</v>
+        <v>354.69</v>
       </c>
       <c r="L88" t="n">
-        <v>278.01</v>
+        <v>383.24</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-21.xlsx
+++ b/output/2025-09-21.xlsx
@@ -640,13 +640,13 @@
         <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-53.86</v>
+        <v>-64.28</v>
       </c>
       <c r="K14" t="n">
-        <v>65.98999999999999</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>85.18000000000001</v>
+        <v>101.66</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>74.17</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.41</v>
+        <v>-2.84</v>
       </c>
       <c r="L15" t="n">
-        <v>74.20999999999999</v>
+        <v>87.31</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.28</v>
+        <v>-47.2</v>
       </c>
       <c r="K16" t="n">
-        <v>64.8</v>
+        <v>75.92</v>
       </c>
       <c r="L16" t="n">
-        <v>76.3</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>24.11</v>
+        <v>24.91</v>
       </c>
       <c r="K17" t="n">
-        <v>3.16</v>
+        <v>3.27</v>
       </c>
       <c r="L17" t="n">
-        <v>24.31</v>
+        <v>25.12</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>73.04000000000001</v>
+        <v>77.38</v>
       </c>
       <c r="K18" t="n">
-        <v>19.52</v>
+        <v>20.68</v>
       </c>
       <c r="L18" t="n">
-        <v>75.59999999999999</v>
+        <v>80.09</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-41.02</v>
+        <v>-43.52</v>
       </c>
       <c r="K19" t="n">
-        <v>63.62</v>
+        <v>67.5</v>
       </c>
       <c r="L19" t="n">
-        <v>75.7</v>
+        <v>80.31</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>9.289999999999999</v>
+        <v>11.22</v>
       </c>
       <c r="K29" t="n">
-        <v>-73.86</v>
+        <v>-89.23999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>74.44</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-59.78</v>
+        <v>-70.05</v>
       </c>
       <c r="K30" t="n">
-        <v>28.54</v>
+        <v>33.44</v>
       </c>
       <c r="L30" t="n">
-        <v>66.23999999999999</v>
+        <v>77.62</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-80.23</v>
+        <v>-103.69</v>
       </c>
       <c r="K31" t="n">
-        <v>6.83</v>
+        <v>8.82</v>
       </c>
       <c r="L31" t="n">
-        <v>80.52</v>
+        <v>104.07</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>38.29</v>
+        <v>48.78</v>
       </c>
       <c r="K32" t="n">
-        <v>102.71</v>
+        <v>130.85</v>
       </c>
       <c r="L32" t="n">
-        <v>109.62</v>
+        <v>139.65</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>18.68</v>
+        <v>20.02</v>
       </c>
       <c r="K33" t="n">
-        <v>-122.86</v>
+        <v>-131.67</v>
       </c>
       <c r="L33" t="n">
-        <v>124.27</v>
+        <v>133.18</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>26.58</v>
+        <v>33.55</v>
       </c>
       <c r="K34" t="n">
-        <v>103.65</v>
+        <v>130.83</v>
       </c>
       <c r="L34" t="n">
-        <v>107</v>
+        <v>135.06</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-35.02</v>
+        <v>-46.37</v>
       </c>
       <c r="K44" t="n">
-        <v>-58.36</v>
+        <v>-77.28</v>
       </c>
       <c r="L44" t="n">
-        <v>68.06</v>
+        <v>90.12</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-77</v>
+        <v>-85.76000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.050000000000001</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>77.42</v>
+        <v>86.22</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-51.81</v>
+        <v>-69.56999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>44.73</v>
+        <v>60.06</v>
       </c>
       <c r="L46" t="n">
-        <v>68.45</v>
+        <v>91.91</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-87.59</v>
+        <v>-109.21</v>
       </c>
       <c r="K47" t="n">
-        <v>-42.86</v>
+        <v>-53.43</v>
       </c>
       <c r="L47" t="n">
-        <v>97.51000000000001</v>
+        <v>121.58</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-111.88</v>
+        <v>-139.07</v>
       </c>
       <c r="K48" t="n">
-        <v>-36.19</v>
+        <v>-44.98</v>
       </c>
       <c r="L48" t="n">
-        <v>117.59</v>
+        <v>146.16</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-33.1</v>
+        <v>-39.58</v>
       </c>
       <c r="K49" t="n">
-        <v>-40.62</v>
+        <v>-48.57</v>
       </c>
       <c r="L49" t="n">
-        <v>52.4</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>63.21</v>
+        <v>84.53</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.68</v>
+        <v>-11.61</v>
       </c>
       <c r="L59" t="n">
-        <v>63.8</v>
+        <v>85.33</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-68.43000000000001</v>
+        <v>-99.42</v>
       </c>
       <c r="K60" t="n">
-        <v>66.08</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>95.12</v>
+        <v>138.22</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-63.78</v>
+        <v>-88.23999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-34.42</v>
+        <v>-47.63</v>
       </c>
       <c r="L61" t="n">
-        <v>72.48</v>
+        <v>100.27</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-5.19</v>
+        <v>-5.76</v>
       </c>
       <c r="K62" t="n">
-        <v>-74.91</v>
+        <v>-83.20999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>75.09</v>
+        <v>83.41</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-25.72</v>
+        <v>-27.93</v>
       </c>
       <c r="K63" t="n">
-        <v>-98.28</v>
+        <v>-106.73</v>
       </c>
       <c r="L63" t="n">
-        <v>101.59</v>
+        <v>110.33</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-33.49</v>
+        <v>-40.74</v>
       </c>
       <c r="K64" t="n">
-        <v>-67.16</v>
+        <v>-81.69</v>
       </c>
       <c r="L64" t="n">
-        <v>75.04000000000001</v>
+        <v>91.28</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>71.72</v>
+        <v>114.35</v>
       </c>
       <c r="K74" t="n">
-        <v>-64.40000000000001</v>
+        <v>-102.68</v>
       </c>
       <c r="L74" t="n">
-        <v>96.39</v>
+        <v>153.68</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-52.85</v>
+        <v>-69.28</v>
       </c>
       <c r="K75" t="n">
-        <v>80.22</v>
+        <v>105.16</v>
       </c>
       <c r="L75" t="n">
-        <v>96.06999999999999</v>
+        <v>125.93</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>77.91</v>
+        <v>110.16</v>
       </c>
       <c r="K76" t="n">
-        <v>-40.14</v>
+        <v>-56.76</v>
       </c>
       <c r="L76" t="n">
-        <v>87.65000000000001</v>
+        <v>123.92</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>112.06</v>
+        <v>140.36</v>
       </c>
       <c r="K77" t="n">
-        <v>27.22</v>
+        <v>34.1</v>
       </c>
       <c r="L77" t="n">
-        <v>115.32</v>
+        <v>144.44</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>35.82</v>
+        <v>47.48</v>
       </c>
       <c r="K78" t="n">
-        <v>-85.93000000000001</v>
+        <v>-113.92</v>
       </c>
       <c r="L78" t="n">
-        <v>93.09999999999999</v>
+        <v>123.41</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>21.53</v>
+        <v>28.07</v>
       </c>
       <c r="K79" t="n">
-        <v>-115.19</v>
+        <v>-150.16</v>
       </c>
       <c r="L79" t="n">
-        <v>117.19</v>
+        <v>152.76</v>
       </c>
     </row>
     <row r="80">
